--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="252">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,6 +535,15 @@
     <t>['12']</t>
   </si>
   <si>
+    <t>['14', '45+4', '88']</t>
+  </si>
+  <si>
+    <t>['27', '45+5', '90+14']</t>
+  </si>
+  <si>
+    <t>['4', '25', '49', '61', '72', '78', '87']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -746,6 +755,21 @@
   </si>
   <si>
     <t>['52']</t>
+  </si>
+  <si>
+    <t>['39', '74']</t>
+  </si>
+  <si>
+    <t>['23', '28', '55']</t>
+  </si>
+  <si>
+    <t>['3', '25', '72', '87', '90+1']</t>
+  </si>
+  <si>
+    <t>['64', '82']</t>
+  </si>
+  <si>
+    <t>['7', '52']</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1363,7 +1387,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1647,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ3">
         <v>1.43</v>
@@ -1775,7 +1799,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1981,7 +2005,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2187,7 +2211,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2393,7 +2417,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2474,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3089,10 +3113,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3629,7 +3653,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3710,7 +3734,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ13">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4041,7 +4065,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4119,10 +4143,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AQ15">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4247,7 +4271,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4325,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>0.71</v>
@@ -4453,7 +4477,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4534,7 +4558,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ17">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4737,10 +4761,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ18">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR18">
         <v>0.92</v>
@@ -4865,7 +4889,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -5071,7 +5095,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5152,7 +5176,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ20">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR20">
         <v>1.82</v>
@@ -5277,7 +5301,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5483,7 +5507,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5689,7 +5713,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5895,7 +5919,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6101,7 +6125,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6179,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ25">
         <v>0.43</v>
@@ -6307,7 +6331,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6513,7 +6537,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6594,7 +6618,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ27">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR27">
         <v>1.57</v>
@@ -6719,7 +6743,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7209,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ30">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR30">
         <v>2.59</v>
@@ -7337,7 +7361,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7621,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AQ32">
         <v>0.86</v>
@@ -7749,7 +7773,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7827,10 +7851,10 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR33">
         <v>1.87</v>
@@ -8036,7 +8060,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>2.49</v>
@@ -8161,7 +8185,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8242,7 +8266,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ35">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR35">
         <v>1.51</v>
@@ -8367,7 +8391,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8573,7 +8597,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8779,7 +8803,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9066,7 +9090,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ39">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
         <v>1.22</v>
@@ -9191,7 +9215,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9478,7 +9502,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ41">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR41">
         <v>2.65</v>
@@ -9603,7 +9627,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9809,7 +9833,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10633,7 +10657,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10839,7 +10863,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11123,7 +11147,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
         <v>0.86</v>
@@ -11251,7 +11275,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11332,7 +11356,7 @@
         <v>3</v>
       </c>
       <c r="AQ50">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11538,7 +11562,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ51">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11663,7 +11687,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11741,7 +11765,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AQ52">
         <v>2</v>
@@ -11869,7 +11893,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12487,7 +12511,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12693,7 +12717,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12899,7 +12923,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -12980,7 +13004,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ58">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR58">
         <v>1.94</v>
@@ -13183,10 +13207,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ59">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR59">
         <v>1.16</v>
@@ -13311,7 +13335,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13392,7 +13416,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ60">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>2.1</v>
@@ -13517,7 +13541,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13801,7 +13825,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ62">
         <v>1.38</v>
@@ -13929,7 +13953,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14341,7 +14365,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14419,7 +14443,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ65">
         <v>2</v>
@@ -14547,7 +14571,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14628,7 +14652,7 @@
         <v>3</v>
       </c>
       <c r="AQ66">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR66">
         <v>1.95</v>
@@ -14753,7 +14777,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14831,7 +14855,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AQ67">
         <v>1.43</v>
@@ -14959,7 +14983,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15040,7 +15064,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR68">
         <v>1.1</v>
@@ -15165,7 +15189,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15243,7 +15267,7 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ69">
         <v>1.38</v>
@@ -15371,7 +15395,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15449,7 +15473,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ70">
         <v>2</v>
@@ -15577,7 +15601,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15783,7 +15807,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15864,7 +15888,7 @@
         <v>0</v>
       </c>
       <c r="AQ72">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -15989,7 +16013,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16070,7 +16094,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ73">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -16195,7 +16219,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16273,10 +16297,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ74">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR74">
         <v>1.11</v>
@@ -16401,7 +16425,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16607,7 +16631,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16813,7 +16837,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16891,7 +16915,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AQ77">
         <v>2</v>
@@ -17019,7 +17043,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17100,7 +17124,7 @@
         <v>2</v>
       </c>
       <c r="AQ78">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR78">
         <v>2.33</v>
@@ -17225,7 +17249,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17509,7 +17533,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ80">
         <v>1.43</v>
@@ -17637,7 +17661,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -18049,7 +18073,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18127,7 +18151,7 @@
         <v>2</v>
       </c>
       <c r="AP83">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>1.38</v>
@@ -18255,7 +18279,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18461,7 +18485,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18748,7 +18772,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ86">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -19079,7 +19103,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19363,7 +19387,7 @@
         <v>1.43</v>
       </c>
       <c r="AP89">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AQ89">
         <v>1.22</v>
@@ -19491,7 +19515,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19569,10 +19593,10 @@
         <v>1.8</v>
       </c>
       <c r="AP90">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ90">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR90">
         <v>2.02</v>
@@ -19697,7 +19721,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19778,7 +19802,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -19903,7 +19927,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -19981,7 +20005,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ92">
         <v>2.29</v>
@@ -20109,7 +20133,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20190,7 +20214,7 @@
         <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR93">
         <v>1.62</v>
@@ -20315,7 +20339,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20396,7 +20420,7 @@
         <v>0</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20727,7 +20751,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21014,7 +21038,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ97">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR97">
         <v>2.35</v>
@@ -21139,7 +21163,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21345,7 +21369,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21423,7 +21447,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>2</v>
@@ -21963,7 +21987,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22169,7 +22193,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22453,7 +22477,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ104">
         <v>0.43</v>
@@ -22581,7 +22605,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
@@ -22659,7 +22683,7 @@
         <v>1.43</v>
       </c>
       <c r="AP105">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ105">
         <v>1.25</v>
@@ -22868,7 +22892,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ106">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR106">
         <v>1.58</v>
@@ -22993,7 +23017,7 @@
         <v>91</v>
       </c>
       <c r="P107" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23071,10 +23095,10 @@
         <v>0.83</v>
       </c>
       <c r="AP107">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AQ107">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR107">
         <v>1.3</v>
@@ -23277,10 +23301,10 @@
         <v>2</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ108">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR108">
         <v>1.44</v>
@@ -23486,7 +23510,7 @@
         <v>2</v>
       </c>
       <c r="AQ109">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>2.17</v>
@@ -23611,7 +23635,7 @@
         <v>163</v>
       </c>
       <c r="P110" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23817,7 +23841,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24023,7 +24047,7 @@
         <v>91</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q112">
         <v>5</v>
@@ -24101,7 +24125,7 @@
         <v>1.6</v>
       </c>
       <c r="AP112">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ112">
         <v>2</v>
@@ -24229,7 +24253,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q113">
         <v>2.9</v>
@@ -24722,7 +24746,7 @@
         <v>1</v>
       </c>
       <c r="AQ115">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>1.6</v>
@@ -24847,7 +24871,7 @@
         <v>168</v>
       </c>
       <c r="P116" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>3.3</v>
@@ -25259,7 +25283,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q118">
         <v>2.2</v>
@@ -25671,7 +25695,7 @@
         <v>172</v>
       </c>
       <c r="P120" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q120">
         <v>3.4</v>
@@ -25828,6 +25852,1036 @@
       </c>
       <c r="BP120">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7785296</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45863.58333333334</v>
+      </c>
+      <c r="F121">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s">
+        <v>71</v>
+      </c>
+      <c r="H121" t="s">
+        <v>70</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>3</v>
+      </c>
+      <c r="L121">
+        <v>3</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>5</v>
+      </c>
+      <c r="O121" t="s">
+        <v>173</v>
+      </c>
+      <c r="P121" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q121">
+        <v>2.1</v>
+      </c>
+      <c r="R121">
+        <v>2.25</v>
+      </c>
+      <c r="S121">
+        <v>5</v>
+      </c>
+      <c r="T121">
+        <v>1.3</v>
+      </c>
+      <c r="U121">
+        <v>3.2</v>
+      </c>
+      <c r="V121">
+        <v>2.4</v>
+      </c>
+      <c r="W121">
+        <v>1.5</v>
+      </c>
+      <c r="X121">
+        <v>5.7</v>
+      </c>
+      <c r="Y121">
+        <v>1.08</v>
+      </c>
+      <c r="Z121">
+        <v>1.64</v>
+      </c>
+      <c r="AA121">
+        <v>3.68</v>
+      </c>
+      <c r="AB121">
+        <v>4.2</v>
+      </c>
+      <c r="AC121">
+        <v>1.04</v>
+      </c>
+      <c r="AD121">
+        <v>10</v>
+      </c>
+      <c r="AE121">
+        <v>1.22</v>
+      </c>
+      <c r="AF121">
+        <v>4.2</v>
+      </c>
+      <c r="AG121">
+        <v>1.59</v>
+      </c>
+      <c r="AH121">
+        <v>2.2</v>
+      </c>
+      <c r="AI121">
+        <v>1.62</v>
+      </c>
+      <c r="AJ121">
+        <v>2.1</v>
+      </c>
+      <c r="AK121">
+        <v>1.17</v>
+      </c>
+      <c r="AL121">
+        <v>1.2</v>
+      </c>
+      <c r="AM121">
+        <v>2.2</v>
+      </c>
+      <c r="AN121">
+        <v>1.78</v>
+      </c>
+      <c r="AO121">
+        <v>0.86</v>
+      </c>
+      <c r="AP121">
+        <v>1.9</v>
+      </c>
+      <c r="AQ121">
+        <v>0.75</v>
+      </c>
+      <c r="AR121">
+        <v>1.32</v>
+      </c>
+      <c r="AS121">
+        <v>1.3</v>
+      </c>
+      <c r="AT121">
+        <v>2.62</v>
+      </c>
+      <c r="AU121">
+        <v>10</v>
+      </c>
+      <c r="AV121">
+        <v>5</v>
+      </c>
+      <c r="AW121">
+        <v>10</v>
+      </c>
+      <c r="AX121">
+        <v>8</v>
+      </c>
+      <c r="AY121">
+        <v>20</v>
+      </c>
+      <c r="AZ121">
+        <v>13</v>
+      </c>
+      <c r="BA121">
+        <v>7</v>
+      </c>
+      <c r="BB121">
+        <v>1</v>
+      </c>
+      <c r="BC121">
+        <v>8</v>
+      </c>
+      <c r="BD121">
+        <v>1.49</v>
+      </c>
+      <c r="BE121">
+        <v>7</v>
+      </c>
+      <c r="BF121">
+        <v>2.9</v>
+      </c>
+      <c r="BG121">
+        <v>1.08</v>
+      </c>
+      <c r="BH121">
+        <v>5.8</v>
+      </c>
+      <c r="BI121">
+        <v>1.17</v>
+      </c>
+      <c r="BJ121">
+        <v>4.35</v>
+      </c>
+      <c r="BK121">
+        <v>1.3</v>
+      </c>
+      <c r="BL121">
+        <v>3.15</v>
+      </c>
+      <c r="BM121">
+        <v>1.49</v>
+      </c>
+      <c r="BN121">
+        <v>2.4</v>
+      </c>
+      <c r="BO121">
+        <v>1.76</v>
+      </c>
+      <c r="BP121">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7785297</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45864.45833333334</v>
+      </c>
+      <c r="F122">
+        <v>15</v>
+      </c>
+      <c r="G122" t="s">
+        <v>83</v>
+      </c>
+      <c r="H122" t="s">
+        <v>73</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>3</v>
+      </c>
+      <c r="N122">
+        <v>3</v>
+      </c>
+      <c r="O122" t="s">
+        <v>91</v>
+      </c>
+      <c r="P122" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q122">
+        <v>3.45</v>
+      </c>
+      <c r="R122">
+        <v>2.05</v>
+      </c>
+      <c r="S122">
+        <v>2.88</v>
+      </c>
+      <c r="T122">
+        <v>1.38</v>
+      </c>
+      <c r="U122">
+        <v>2.8</v>
+      </c>
+      <c r="V122">
+        <v>2.65</v>
+      </c>
+      <c r="W122">
+        <v>1.42</v>
+      </c>
+      <c r="X122">
+        <v>6.45</v>
+      </c>
+      <c r="Y122">
+        <v>1.05</v>
+      </c>
+      <c r="Z122">
+        <v>2.89</v>
+      </c>
+      <c r="AA122">
+        <v>3.23</v>
+      </c>
+      <c r="AB122">
+        <v>2.15</v>
+      </c>
+      <c r="AC122">
+        <v>1.05</v>
+      </c>
+      <c r="AD122">
+        <v>9</v>
+      </c>
+      <c r="AE122">
+        <v>1.28</v>
+      </c>
+      <c r="AF122">
+        <v>3.6</v>
+      </c>
+      <c r="AG122">
+        <v>1.76</v>
+      </c>
+      <c r="AH122">
+        <v>1.94</v>
+      </c>
+      <c r="AI122">
+        <v>1.62</v>
+      </c>
+      <c r="AJ122">
+        <v>2.1</v>
+      </c>
+      <c r="AK122">
+        <v>1.62</v>
+      </c>
+      <c r="AL122">
+        <v>1.25</v>
+      </c>
+      <c r="AM122">
+        <v>1.35</v>
+      </c>
+      <c r="AN122">
+        <v>0.29</v>
+      </c>
+      <c r="AO122">
+        <v>0.71</v>
+      </c>
+      <c r="AP122">
+        <v>0.25</v>
+      </c>
+      <c r="AQ122">
+        <v>1</v>
+      </c>
+      <c r="AR122">
+        <v>1.26</v>
+      </c>
+      <c r="AS122">
+        <v>1.18</v>
+      </c>
+      <c r="AT122">
+        <v>2.44</v>
+      </c>
+      <c r="AU122">
+        <v>5</v>
+      </c>
+      <c r="AV122">
+        <v>5</v>
+      </c>
+      <c r="AW122">
+        <v>6</v>
+      </c>
+      <c r="AX122">
+        <v>6</v>
+      </c>
+      <c r="AY122">
+        <v>11</v>
+      </c>
+      <c r="AZ122">
+        <v>11</v>
+      </c>
+      <c r="BA122">
+        <v>5</v>
+      </c>
+      <c r="BB122">
+        <v>8</v>
+      </c>
+      <c r="BC122">
+        <v>13</v>
+      </c>
+      <c r="BD122">
+        <v>2.2</v>
+      </c>
+      <c r="BE122">
+        <v>6.5</v>
+      </c>
+      <c r="BF122">
+        <v>1.79</v>
+      </c>
+      <c r="BG122">
+        <v>1.11</v>
+      </c>
+      <c r="BH122">
+        <v>5.3</v>
+      </c>
+      <c r="BI122">
+        <v>1.23</v>
+      </c>
+      <c r="BJ122">
+        <v>3.7</v>
+      </c>
+      <c r="BK122">
+        <v>1.4</v>
+      </c>
+      <c r="BL122">
+        <v>2.7</v>
+      </c>
+      <c r="BM122">
+        <v>1.65</v>
+      </c>
+      <c r="BN122">
+        <v>2.1</v>
+      </c>
+      <c r="BO122">
+        <v>1.98</v>
+      </c>
+      <c r="BP122">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7785298</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45864.45833333334</v>
+      </c>
+      <c r="F123">
+        <v>15</v>
+      </c>
+      <c r="G123" t="s">
+        <v>84</v>
+      </c>
+      <c r="H123" t="s">
+        <v>74</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>5</v>
+      </c>
+      <c r="N123">
+        <v>5</v>
+      </c>
+      <c r="O123" t="s">
+        <v>91</v>
+      </c>
+      <c r="P123" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q123">
+        <v>3.55</v>
+      </c>
+      <c r="R123">
+        <v>2.1</v>
+      </c>
+      <c r="S123">
+        <v>2.8</v>
+      </c>
+      <c r="T123">
+        <v>1.38</v>
+      </c>
+      <c r="U123">
+        <v>2.8</v>
+      </c>
+      <c r="V123">
+        <v>2.7</v>
+      </c>
+      <c r="W123">
+        <v>1.4</v>
+      </c>
+      <c r="X123">
+        <v>7.4</v>
+      </c>
+      <c r="Y123">
+        <v>1.03</v>
+      </c>
+      <c r="Z123">
+        <v>3.01</v>
+      </c>
+      <c r="AA123">
+        <v>3.11</v>
+      </c>
+      <c r="AB123">
+        <v>2.14</v>
+      </c>
+      <c r="AC123">
+        <v>1.06</v>
+      </c>
+      <c r="AD123">
+        <v>8.5</v>
+      </c>
+      <c r="AE123">
+        <v>1.33</v>
+      </c>
+      <c r="AF123">
+        <v>3.25</v>
+      </c>
+      <c r="AG123">
+        <v>1.92</v>
+      </c>
+      <c r="AH123">
+        <v>1.78</v>
+      </c>
+      <c r="AI123">
+        <v>1.73</v>
+      </c>
+      <c r="AJ123">
+        <v>1.95</v>
+      </c>
+      <c r="AK123">
+        <v>1.62</v>
+      </c>
+      <c r="AL123">
+        <v>1.28</v>
+      </c>
+      <c r="AM123">
+        <v>1.33</v>
+      </c>
+      <c r="AN123">
+        <v>1.14</v>
+      </c>
+      <c r="AO123">
+        <v>1.14</v>
+      </c>
+      <c r="AP123">
+        <v>1</v>
+      </c>
+      <c r="AQ123">
+        <v>1.38</v>
+      </c>
+      <c r="AR123">
+        <v>1.36</v>
+      </c>
+      <c r="AS123">
+        <v>1.15</v>
+      </c>
+      <c r="AT123">
+        <v>2.51</v>
+      </c>
+      <c r="AU123">
+        <v>2</v>
+      </c>
+      <c r="AV123">
+        <v>9</v>
+      </c>
+      <c r="AW123">
+        <v>4</v>
+      </c>
+      <c r="AX123">
+        <v>3</v>
+      </c>
+      <c r="AY123">
+        <v>6</v>
+      </c>
+      <c r="AZ123">
+        <v>12</v>
+      </c>
+      <c r="BA123">
+        <v>3</v>
+      </c>
+      <c r="BB123">
+        <v>3</v>
+      </c>
+      <c r="BC123">
+        <v>6</v>
+      </c>
+      <c r="BD123">
+        <v>2.63</v>
+      </c>
+      <c r="BE123">
+        <v>6.4</v>
+      </c>
+      <c r="BF123">
+        <v>1.6</v>
+      </c>
+      <c r="BG123">
+        <v>1.19</v>
+      </c>
+      <c r="BH123">
+        <v>4.1</v>
+      </c>
+      <c r="BI123">
+        <v>1.33</v>
+      </c>
+      <c r="BJ123">
+        <v>2.95</v>
+      </c>
+      <c r="BK123">
+        <v>1.56</v>
+      </c>
+      <c r="BL123">
+        <v>2.23</v>
+      </c>
+      <c r="BM123">
+        <v>1.9</v>
+      </c>
+      <c r="BN123">
+        <v>1.79</v>
+      </c>
+      <c r="BO123">
+        <v>2.38</v>
+      </c>
+      <c r="BP123">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7785300</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45864.45833333334</v>
+      </c>
+      <c r="F124">
+        <v>15</v>
+      </c>
+      <c r="G124" t="s">
+        <v>82</v>
+      </c>
+      <c r="H124" t="s">
+        <v>81</v>
+      </c>
+      <c r="I124">
+        <v>2</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>2</v>
+      </c>
+      <c r="L124">
+        <v>3</v>
+      </c>
+      <c r="M124">
+        <v>2</v>
+      </c>
+      <c r="N124">
+        <v>5</v>
+      </c>
+      <c r="O124" t="s">
+        <v>174</v>
+      </c>
+      <c r="P124" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q124">
+        <v>2.6</v>
+      </c>
+      <c r="R124">
+        <v>2.3</v>
+      </c>
+      <c r="S124">
+        <v>3.35</v>
+      </c>
+      <c r="T124">
+        <v>1.25</v>
+      </c>
+      <c r="U124">
+        <v>3.45</v>
+      </c>
+      <c r="V124">
+        <v>2.2</v>
+      </c>
+      <c r="W124">
+        <v>1.6</v>
+      </c>
+      <c r="X124">
+        <v>4.7</v>
+      </c>
+      <c r="Y124">
+        <v>1.12</v>
+      </c>
+      <c r="Z124">
+        <v>2.23</v>
+      </c>
+      <c r="AA124">
+        <v>3.56</v>
+      </c>
+      <c r="AB124">
+        <v>2.57</v>
+      </c>
+      <c r="AC124">
+        <v>1.01</v>
+      </c>
+      <c r="AD124">
+        <v>17</v>
+      </c>
+      <c r="AE124">
+        <v>1.18</v>
+      </c>
+      <c r="AF124">
+        <v>4.75</v>
+      </c>
+      <c r="AG124">
+        <v>1.52</v>
+      </c>
+      <c r="AH124">
+        <v>2.43</v>
+      </c>
+      <c r="AI124">
+        <v>1.45</v>
+      </c>
+      <c r="AJ124">
+        <v>2.5</v>
+      </c>
+      <c r="AK124">
+        <v>1.36</v>
+      </c>
+      <c r="AL124">
+        <v>1.22</v>
+      </c>
+      <c r="AM124">
+        <v>1.7</v>
+      </c>
+      <c r="AN124">
+        <v>3</v>
+      </c>
+      <c r="AO124">
+        <v>1.86</v>
+      </c>
+      <c r="AP124">
+        <v>3</v>
+      </c>
+      <c r="AQ124">
+        <v>1.63</v>
+      </c>
+      <c r="AR124">
+        <v>2.01</v>
+      </c>
+      <c r="AS124">
+        <v>1.81</v>
+      </c>
+      <c r="AT124">
+        <v>3.82</v>
+      </c>
+      <c r="AU124">
+        <v>11</v>
+      </c>
+      <c r="AV124">
+        <v>7</v>
+      </c>
+      <c r="AW124">
+        <v>11</v>
+      </c>
+      <c r="AX124">
+        <v>4</v>
+      </c>
+      <c r="AY124">
+        <v>22</v>
+      </c>
+      <c r="AZ124">
+        <v>11</v>
+      </c>
+      <c r="BA124">
+        <v>4</v>
+      </c>
+      <c r="BB124">
+        <v>5</v>
+      </c>
+      <c r="BC124">
+        <v>9</v>
+      </c>
+      <c r="BD124">
+        <v>1.89</v>
+      </c>
+      <c r="BE124">
+        <v>6.5</v>
+      </c>
+      <c r="BF124">
+        <v>2.1</v>
+      </c>
+      <c r="BG124">
+        <v>1.15</v>
+      </c>
+      <c r="BH124">
+        <v>4.6</v>
+      </c>
+      <c r="BI124">
+        <v>1.28</v>
+      </c>
+      <c r="BJ124">
+        <v>3.3</v>
+      </c>
+      <c r="BK124">
+        <v>1.48</v>
+      </c>
+      <c r="BL124">
+        <v>2.45</v>
+      </c>
+      <c r="BM124">
+        <v>1.75</v>
+      </c>
+      <c r="BN124">
+        <v>1.95</v>
+      </c>
+      <c r="BO124">
+        <v>2.18</v>
+      </c>
+      <c r="BP124">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7785294</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45864.54166666666</v>
+      </c>
+      <c r="F125">
+        <v>15</v>
+      </c>
+      <c r="G125" t="s">
+        <v>78</v>
+      </c>
+      <c r="H125" t="s">
+        <v>72</v>
+      </c>
+      <c r="I125">
+        <v>2</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+      <c r="K125">
+        <v>3</v>
+      </c>
+      <c r="L125">
+        <v>7</v>
+      </c>
+      <c r="M125">
+        <v>2</v>
+      </c>
+      <c r="N125">
+        <v>9</v>
+      </c>
+      <c r="O125" t="s">
+        <v>175</v>
+      </c>
+      <c r="P125" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q125">
+        <v>1.55</v>
+      </c>
+      <c r="R125">
+        <v>3.1</v>
+      </c>
+      <c r="S125">
+        <v>6.5</v>
+      </c>
+      <c r="T125">
+        <v>1.15</v>
+      </c>
+      <c r="U125">
+        <v>4.75</v>
+      </c>
+      <c r="V125">
+        <v>1.8</v>
+      </c>
+      <c r="W125">
+        <v>1.91</v>
+      </c>
+      <c r="X125">
+        <v>3.42</v>
+      </c>
+      <c r="Y125">
+        <v>1.23</v>
+      </c>
+      <c r="Z125">
+        <v>1.23</v>
+      </c>
+      <c r="AA125">
+        <v>5.7</v>
+      </c>
+      <c r="AB125">
+        <v>7.8</v>
+      </c>
+      <c r="AC125">
+        <v>1.01</v>
+      </c>
+      <c r="AD125">
+        <v>29</v>
+      </c>
+      <c r="AE125">
+        <v>1.07</v>
+      </c>
+      <c r="AF125">
+        <v>8</v>
+      </c>
+      <c r="AG125">
+        <v>1.25</v>
+      </c>
+      <c r="AH125">
+        <v>3.71</v>
+      </c>
+      <c r="AI125">
+        <v>1.57</v>
+      </c>
+      <c r="AJ125">
+        <v>2.2</v>
+      </c>
+      <c r="AK125">
+        <v>1.05</v>
+      </c>
+      <c r="AL125">
+        <v>1.1</v>
+      </c>
+      <c r="AM125">
+        <v>3.95</v>
+      </c>
+      <c r="AN125">
+        <v>2.14</v>
+      </c>
+      <c r="AO125">
+        <v>1.25</v>
+      </c>
+      <c r="AP125">
+        <v>2.25</v>
+      </c>
+      <c r="AQ125">
+        <v>1.11</v>
+      </c>
+      <c r="AR125">
+        <v>2.51</v>
+      </c>
+      <c r="AS125">
+        <v>1.27</v>
+      </c>
+      <c r="AT125">
+        <v>3.78</v>
+      </c>
+      <c r="AU125">
+        <v>14</v>
+      </c>
+      <c r="AV125">
+        <v>3</v>
+      </c>
+      <c r="AW125">
+        <v>6</v>
+      </c>
+      <c r="AX125">
+        <v>6</v>
+      </c>
+      <c r="AY125">
+        <v>20</v>
+      </c>
+      <c r="AZ125">
+        <v>9</v>
+      </c>
+      <c r="BA125">
+        <v>6</v>
+      </c>
+      <c r="BB125">
+        <v>1</v>
+      </c>
+      <c r="BC125">
+        <v>7</v>
+      </c>
+      <c r="BD125">
+        <v>1.25</v>
+      </c>
+      <c r="BE125">
+        <v>7.5</v>
+      </c>
+      <c r="BF125">
+        <v>4.3</v>
+      </c>
+      <c r="BG125">
+        <v>1.16</v>
+      </c>
+      <c r="BH125">
+        <v>4.4</v>
+      </c>
+      <c r="BI125">
+        <v>1.29</v>
+      </c>
+      <c r="BJ125">
+        <v>3.15</v>
+      </c>
+      <c r="BK125">
+        <v>1.49</v>
+      </c>
+      <c r="BL125">
+        <v>2.4</v>
+      </c>
+      <c r="BM125">
+        <v>1.77</v>
+      </c>
+      <c r="BN125">
+        <v>1.93</v>
+      </c>
+      <c r="BO125">
+        <v>2.18</v>
+      </c>
+      <c r="BP125">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="254">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -544,6 +544,9 @@
     <t>['4', '25', '49', '61', '72', '78', '87']</t>
   </si>
   <si>
+    <t>['29', '38', '54', '90+2']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -770,6 +773,9 @@
   </si>
   <si>
     <t>['7', '52']</t>
+  </si>
+  <si>
+    <t>['3', '50', '64']</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1387,7 +1393,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1799,7 +1805,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1880,7 +1886,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2005,7 +2011,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2211,7 +2217,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2417,7 +2423,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2907,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ9">
         <v>2</v>
@@ -3319,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ11">
         <v>0.86</v>
@@ -3528,7 +3534,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ12">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3653,7 +3659,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4065,7 +4071,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4271,7 +4277,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4477,7 +4483,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4889,7 +4895,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -5095,7 +5101,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5301,7 +5307,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5507,7 +5513,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5713,7 +5719,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5919,7 +5925,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5997,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ24">
         <v>0</v>
@@ -6125,7 +6131,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6331,7 +6337,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6412,7 +6418,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR26">
         <v>1.31</v>
@@ -6537,7 +6543,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6743,7 +6749,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7027,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ29">
         <v>1.25</v>
@@ -7361,7 +7367,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7773,7 +7779,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8185,7 +8191,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8391,7 +8397,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8472,7 +8478,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ36">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>2</v>
@@ -8597,7 +8603,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8803,7 +8809,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8881,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ38">
         <v>1.22</v>
@@ -9215,7 +9221,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9627,7 +9633,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9833,7 +9839,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10323,7 +10329,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ45">
         <v>0.71</v>
@@ -10657,7 +10663,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10735,7 +10741,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ47">
         <v>1.25</v>
@@ -10863,7 +10869,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10944,7 +10950,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ48">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11275,7 +11281,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11687,7 +11693,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11768,7 +11774,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR52">
         <v>1.29</v>
@@ -11893,7 +11899,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12383,7 +12389,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ55">
         <v>0</v>
@@ -12511,7 +12517,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12717,7 +12723,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12923,7 +12929,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13335,7 +13341,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13541,7 +13547,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13619,7 +13625,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ61">
         <v>0.86</v>
@@ -13953,7 +13959,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14240,7 +14246,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ64">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR64">
         <v>1.85</v>
@@ -14365,7 +14371,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14446,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="AQ65">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR65">
         <v>1.38</v>
@@ -14571,7 +14577,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14777,7 +14783,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14983,7 +14989,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15189,7 +15195,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15395,7 +15401,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15476,7 +15482,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ70">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR70">
         <v>2.02</v>
@@ -15601,7 +15607,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15807,7 +15813,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -16013,7 +16019,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16219,7 +16225,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16425,7 +16431,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16631,7 +16637,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16709,7 +16715,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ76">
         <v>0.43</v>
@@ -16837,7 +16843,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -17043,7 +17049,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17121,7 +17127,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ78">
         <v>1.38</v>
@@ -17249,7 +17255,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17330,7 +17336,7 @@
         <v>1</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR79">
         <v>1.62</v>
@@ -17661,7 +17667,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -18073,7 +18079,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18279,7 +18285,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18485,7 +18491,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18566,7 +18572,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ85">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -19103,7 +19109,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19181,10 +19187,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ88">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR88">
         <v>2.33</v>
@@ -19515,7 +19521,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19721,7 +19727,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19799,7 +19805,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -19927,7 +19933,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20008,7 +20014,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ92">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR92">
         <v>1.11</v>
@@ -20133,7 +20139,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20339,7 +20345,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20751,7 +20757,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21163,7 +21169,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21369,7 +21375,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21987,7 +21993,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22193,7 +22199,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22605,7 +22611,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
@@ -22889,7 +22895,7 @@
         <v>1.43</v>
       </c>
       <c r="AP106">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ106">
         <v>1.11</v>
@@ -23017,7 +23023,7 @@
         <v>91</v>
       </c>
       <c r="P107" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23507,7 +23513,7 @@
         <v>0.83</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23635,7 +23641,7 @@
         <v>163</v>
       </c>
       <c r="P110" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23716,7 +23722,7 @@
         <v>0</v>
       </c>
       <c r="AQ110">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR110">
         <v>1.45</v>
@@ -23841,7 +23847,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -23922,7 +23928,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ111">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR111">
         <v>2.11</v>
@@ -24047,7 +24053,7 @@
         <v>91</v>
       </c>
       <c r="P112" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q112">
         <v>5</v>
@@ -24253,7 +24259,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q113">
         <v>2.9</v>
@@ -24871,7 +24877,7 @@
         <v>168</v>
       </c>
       <c r="P116" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q116">
         <v>3.3</v>
@@ -25283,7 +25289,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q118">
         <v>2.2</v>
@@ -25695,7 +25701,7 @@
         <v>172</v>
       </c>
       <c r="P120" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q120">
         <v>3.4</v>
@@ -25901,7 +25907,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26107,7 +26113,7 @@
         <v>91</v>
       </c>
       <c r="P122" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26313,7 +26319,7 @@
         <v>91</v>
       </c>
       <c r="P123" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q123">
         <v>3.55</v>
@@ -26519,7 +26525,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q124">
         <v>2.6</v>
@@ -26725,7 +26731,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q125">
         <v>1.55</v>
@@ -26882,6 +26888,418 @@
       </c>
       <c r="BP125">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7785295</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45865.39583333334</v>
+      </c>
+      <c r="F126">
+        <v>15</v>
+      </c>
+      <c r="G126" t="s">
+        <v>77</v>
+      </c>
+      <c r="H126" t="s">
+        <v>85</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>3</v>
+      </c>
+      <c r="N126">
+        <v>4</v>
+      </c>
+      <c r="O126" t="s">
+        <v>108</v>
+      </c>
+      <c r="P126" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q126">
+        <v>4.33</v>
+      </c>
+      <c r="R126">
+        <v>2.4</v>
+      </c>
+      <c r="S126">
+        <v>2.3</v>
+      </c>
+      <c r="T126">
+        <v>1.29</v>
+      </c>
+      <c r="U126">
+        <v>3.5</v>
+      </c>
+      <c r="V126">
+        <v>2.25</v>
+      </c>
+      <c r="W126">
+        <v>1.57</v>
+      </c>
+      <c r="X126">
+        <v>5.5</v>
+      </c>
+      <c r="Y126">
+        <v>1.14</v>
+      </c>
+      <c r="Z126">
+        <v>3.82</v>
+      </c>
+      <c r="AA126">
+        <v>3.55</v>
+      </c>
+      <c r="AB126">
+        <v>1.73</v>
+      </c>
+      <c r="AC126">
+        <v>1.04</v>
+      </c>
+      <c r="AD126">
+        <v>10</v>
+      </c>
+      <c r="AE126">
+        <v>1.22</v>
+      </c>
+      <c r="AF126">
+        <v>4.2</v>
+      </c>
+      <c r="AG126">
+        <v>1.61</v>
+      </c>
+      <c r="AH126">
+        <v>2.1</v>
+      </c>
+      <c r="AI126">
+        <v>1.57</v>
+      </c>
+      <c r="AJ126">
+        <v>2.25</v>
+      </c>
+      <c r="AK126">
+        <v>1.95</v>
+      </c>
+      <c r="AL126">
+        <v>1.22</v>
+      </c>
+      <c r="AM126">
+        <v>1.22</v>
+      </c>
+      <c r="AN126">
+        <v>1.86</v>
+      </c>
+      <c r="AO126">
+        <v>2</v>
+      </c>
+      <c r="AP126">
+        <v>1.63</v>
+      </c>
+      <c r="AQ126">
+        <v>2.11</v>
+      </c>
+      <c r="AR126">
+        <v>1.63</v>
+      </c>
+      <c r="AS126">
+        <v>1.73</v>
+      </c>
+      <c r="AT126">
+        <v>3.36</v>
+      </c>
+      <c r="AU126">
+        <v>4</v>
+      </c>
+      <c r="AV126">
+        <v>6</v>
+      </c>
+      <c r="AW126">
+        <v>9</v>
+      </c>
+      <c r="AX126">
+        <v>4</v>
+      </c>
+      <c r="AY126">
+        <v>13</v>
+      </c>
+      <c r="AZ126">
+        <v>10</v>
+      </c>
+      <c r="BA126">
+        <v>2</v>
+      </c>
+      <c r="BB126">
+        <v>5</v>
+      </c>
+      <c r="BC126">
+        <v>7</v>
+      </c>
+      <c r="BD126">
+        <v>3.2</v>
+      </c>
+      <c r="BE126">
+        <v>7.5</v>
+      </c>
+      <c r="BF126">
+        <v>1.41</v>
+      </c>
+      <c r="BG126">
+        <v>1.13</v>
+      </c>
+      <c r="BH126">
+        <v>4.9</v>
+      </c>
+      <c r="BI126">
+        <v>1.24</v>
+      </c>
+      <c r="BJ126">
+        <v>3.55</v>
+      </c>
+      <c r="BK126">
+        <v>1.43</v>
+      </c>
+      <c r="BL126">
+        <v>2.6</v>
+      </c>
+      <c r="BM126">
+        <v>1.68</v>
+      </c>
+      <c r="BN126">
+        <v>2.05</v>
+      </c>
+      <c r="BO126">
+        <v>2.07</v>
+      </c>
+      <c r="BP126">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7785299</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45865.39583333334</v>
+      </c>
+      <c r="F127">
+        <v>15</v>
+      </c>
+      <c r="G127" t="s">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s">
+        <v>76</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>2</v>
+      </c>
+      <c r="L127">
+        <v>4</v>
+      </c>
+      <c r="M127">
+        <v>1</v>
+      </c>
+      <c r="N127">
+        <v>5</v>
+      </c>
+      <c r="O127" t="s">
+        <v>176</v>
+      </c>
+      <c r="P127" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q127">
+        <v>2.75</v>
+      </c>
+      <c r="R127">
+        <v>2.2</v>
+      </c>
+      <c r="S127">
+        <v>3.75</v>
+      </c>
+      <c r="T127">
+        <v>1.36</v>
+      </c>
+      <c r="U127">
+        <v>3</v>
+      </c>
+      <c r="V127">
+        <v>2.75</v>
+      </c>
+      <c r="W127">
+        <v>1.4</v>
+      </c>
+      <c r="X127">
+        <v>7</v>
+      </c>
+      <c r="Y127">
+        <v>1.1</v>
+      </c>
+      <c r="Z127">
+        <v>2</v>
+      </c>
+      <c r="AA127">
+        <v>3.26</v>
+      </c>
+      <c r="AB127">
+        <v>3.2</v>
+      </c>
+      <c r="AC127">
+        <v>1.06</v>
+      </c>
+      <c r="AD127">
+        <v>8.5</v>
+      </c>
+      <c r="AE127">
+        <v>1.3</v>
+      </c>
+      <c r="AF127">
+        <v>3.35</v>
+      </c>
+      <c r="AG127">
+        <v>1.86</v>
+      </c>
+      <c r="AH127">
+        <v>1.84</v>
+      </c>
+      <c r="AI127">
+        <v>1.7</v>
+      </c>
+      <c r="AJ127">
+        <v>2.05</v>
+      </c>
+      <c r="AK127">
+        <v>1.3</v>
+      </c>
+      <c r="AL127">
+        <v>1.25</v>
+      </c>
+      <c r="AM127">
+        <v>1.67</v>
+      </c>
+      <c r="AN127">
+        <v>2</v>
+      </c>
+      <c r="AO127">
+        <v>2.29</v>
+      </c>
+      <c r="AP127">
+        <v>2.11</v>
+      </c>
+      <c r="AQ127">
+        <v>2</v>
+      </c>
+      <c r="AR127">
+        <v>2.11</v>
+      </c>
+      <c r="AS127">
+        <v>1.28</v>
+      </c>
+      <c r="AT127">
+        <v>3.39</v>
+      </c>
+      <c r="AU127">
+        <v>6</v>
+      </c>
+      <c r="AV127">
+        <v>3</v>
+      </c>
+      <c r="AW127">
+        <v>5</v>
+      </c>
+      <c r="AX127">
+        <v>4</v>
+      </c>
+      <c r="AY127">
+        <v>11</v>
+      </c>
+      <c r="AZ127">
+        <v>7</v>
+      </c>
+      <c r="BA127">
+        <v>4</v>
+      </c>
+      <c r="BB127">
+        <v>7</v>
+      </c>
+      <c r="BC127">
+        <v>11</v>
+      </c>
+      <c r="BD127">
+        <v>1.46</v>
+      </c>
+      <c r="BE127">
+        <v>6.75</v>
+      </c>
+      <c r="BF127">
+        <v>3.05</v>
+      </c>
+      <c r="BG127">
+        <v>1.19</v>
+      </c>
+      <c r="BH127">
+        <v>4.1</v>
+      </c>
+      <c r="BI127">
+        <v>1.34</v>
+      </c>
+      <c r="BJ127">
+        <v>2.9</v>
+      </c>
+      <c r="BK127">
+        <v>1.57</v>
+      </c>
+      <c r="BL127">
+        <v>2.23</v>
+      </c>
+      <c r="BM127">
+        <v>1.92</v>
+      </c>
+      <c r="BN127">
+        <v>1.78</v>
+      </c>
+      <c r="BO127">
+        <v>2.4</v>
+      </c>
+      <c r="BP127">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ9" t="n">
         <v>2</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.38</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR26" t="n">
         <v>1.31</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.43</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.25</v>
@@ -11814,7 +11814,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR52" t="n">
         <v>1.29</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -13773,7 +13773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.86</v>
@@ -14648,7 +14648,7 @@
         <v>1</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR65" t="n">
         <v>1.38</v>
@@ -15738,7 +15738,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ70" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR70" t="n">
         <v>2.02</v>
@@ -17043,7 +17043,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.43</v>
@@ -17700,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR79" t="n">
         <v>1.62</v>
@@ -18133,7 +18133,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.25</v>
@@ -19662,7 +19662,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR88" t="n">
         <v>2.33</v>
@@ -20313,7 +20313,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.86</v>
@@ -23583,7 +23583,7 @@
         <v>1.43</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.11</v>
@@ -24676,7 +24676,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR111" t="n">
         <v>2.11</v>
@@ -25849,7 +25849,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>7785291</v>
+        <v>7785293</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -25862,204 +25862,204 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>45858.5</v>
+        <v>45858.39583333334</v>
       </c>
       <c r="F117" t="n">
         <v>14</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>3</v>
       </c>
       <c r="M117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
+        <v>3</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>['64', '84', '90+1']</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R117" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S117" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U117" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V117" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X117" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV117" t="n">
         <v>4</v>
       </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>['45+1', '55', '58']</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="Q117" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R117" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S117" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T117" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U117" t="n">
+      <c r="AW117" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX117" t="n">
         <v>3</v>
       </c>
-      <c r="V117" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W117" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X117" t="n">
+      <c r="AY117" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ117" t="n">
         <v>7</v>
       </c>
-      <c r="Y117" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA117" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AC117" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE117" t="n">
+      <c r="BA117" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI117" t="n">
         <v>1.28</v>
       </c>
-      <c r="AF117" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AG117" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH117" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI117" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ117" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK117" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AL117" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM117" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN117" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO117" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP117" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ117" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AR117" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AS117" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AT117" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU117" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV117" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW117" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX117" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY117" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ117" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA117" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB117" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC117" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD117" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BE117" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF117" t="n">
+      <c r="BJ117" t="n">
         <v>3.3</v>
       </c>
-      <c r="BG117" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BH117" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI117" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ117" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BK117" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="BL117" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="BM117" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="BN117" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="BO117" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="BP117" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="118">
@@ -26067,7 +26067,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>7785289</v>
+        <v>7785291</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -26087,197 +26087,197 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" t="n">
+        <v>3</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" t="n">
         <v>4</v>
       </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>['45+1', '55', '58']</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R118" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U118" t="n">
+        <v>3</v>
+      </c>
+      <c r="V118" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X118" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX118" t="n">
         <v>4</v>
       </c>
-      <c r="L118" t="n">
-        <v>6</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>6</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>['8', '22', '39', '45', '67', '86']</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q118" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R118" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S118" t="n">
+      <c r="AY118" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA118" t="n">
         <v>5</v>
       </c>
-      <c r="T118" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U118" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V118" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W118" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X118" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI118" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK118" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AL118" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM118" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AN118" t="n">
+      <c r="BB118" t="n">
         <v>3</v>
       </c>
-      <c r="AO118" t="n">
+      <c r="BC118" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD118" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AP118" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ118" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR118" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS118" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT118" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AU118" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV118" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW118" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX118" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY118" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ118" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA118" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB118" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD118" t="n">
-        <v>1.42</v>
       </c>
       <c r="BE118" t="n">
         <v>7</v>
       </c>
       <c r="BF118" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BG118" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BH118" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BI118" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BJ118" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BK118" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="BL118" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BM118" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="BN118" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BO118" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BP118" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="119">
@@ -26285,7 +26285,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>7785286</v>
+        <v>7785289</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -26298,204 +26298,204 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>45858.59375</v>
+        <v>45858.5</v>
       </c>
       <c r="F119" t="n">
         <v>14</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['8', '22', '39', '45', '67', '86']</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U119" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V119" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X119" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH119" t="n">
         <v>2.1</v>
       </c>
-      <c r="S119" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T119" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U119" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V119" t="n">
+      <c r="AI119" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN119" t="n">
         <v>3</v>
       </c>
-      <c r="W119" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X119" t="n">
+      <c r="AO119" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU119" t="n">
         <v>8</v>
       </c>
-      <c r="Y119" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z119" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA119" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC119" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE119" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF119" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG119" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH119" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI119" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ119" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK119" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL119" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM119" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN119" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO119" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP119" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ119" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AR119" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AS119" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AT119" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AU119" t="n">
-        <v>3</v>
-      </c>
       <c r="AV119" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW119" t="n">
         <v>9</v>
       </c>
       <c r="AX119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY119" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ119" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA119" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BB119" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC119" t="n">
         <v>13</v>
       </c>
       <c r="BD119" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="BE119" t="n">
         <v>7</v>
       </c>
       <c r="BF119" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="BG119" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="BH119" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BI119" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BJ119" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="BK119" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="BL119" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="BM119" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="BN119" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="BO119" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="BP119" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="120">
@@ -26503,7 +26503,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>7785296</v>
+        <v>7785286</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -26516,204 +26516,204 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>45863.58333333334</v>
+        <v>45858.59375</v>
       </c>
       <c r="F120" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>Fredrikstad</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Strømsgodset</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" t="n">
+        <v>2</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U120" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V120" t="n">
         <v>3</v>
       </c>
-      <c r="L120" t="n">
-        <v>3</v>
-      </c>
-      <c r="M120" t="n">
-        <v>2</v>
-      </c>
-      <c r="N120" t="n">
-        <v>5</v>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>['14', '45+4', '88']</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>['39', '74']</t>
-        </is>
-      </c>
-      <c r="Q120" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R120" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S120" t="n">
-        <v>5</v>
-      </c>
-      <c r="T120" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U120" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V120" t="n">
-        <v>2.4</v>
-      </c>
       <c r="W120" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X120" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="Y120" t="n">
         <v>1.08</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.64</v>
+        <v>2.78</v>
       </c>
       <c r="AA120" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AB120" t="n">
-        <v>4.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AD120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF120" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AG120" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AH120" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AI120" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ120" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AK120" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AL120" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AM120" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AO120" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ120" t="n">
         <v>0.86</v>
       </c>
-      <c r="AP120" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ120" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AR120" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AS120" t="n">
         <v>1.3</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AU120" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AV120" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX120" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY120" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ120" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC120" t="n">
         <v>13</v>
       </c>
-      <c r="BA120" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC120" t="n">
-        <v>8</v>
-      </c>
       <c r="BD120" t="n">
-        <v>1.49</v>
+        <v>2.07</v>
       </c>
       <c r="BE120" t="n">
         <v>7</v>
       </c>
       <c r="BF120" t="n">
-        <v>2.9</v>
+        <v>1.88</v>
       </c>
       <c r="BG120" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BH120" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BI120" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BJ120" t="n">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="BK120" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="BL120" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="BM120" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="BN120" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="BO120" t="n">
-        <v>1.76</v>
+        <v>2.17</v>
       </c>
       <c r="BP120" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="121">
@@ -26721,7 +26721,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>7785297</v>
+        <v>7785296</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -26734,102 +26734,102 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>45864.45833333334</v>
+        <v>45863.58333333334</v>
       </c>
       <c r="F121" t="n">
         <v>15</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '45+4', '88']</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>['23', '28', '55']</t>
+          <t>['39', '74']</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="R121" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S121" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="T121" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="U121" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V121" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="W121" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X121" t="n">
-        <v>6.45</v>
+        <v>5.7</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.89</v>
+        <v>1.64</v>
       </c>
       <c r="AA121" t="n">
-        <v>3.23</v>
+        <v>3.68</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF121" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG121" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AH121" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AI121" t="n">
         <v>1.62</v>
@@ -26838,100 +26838,100 @@
         <v>2.1</v>
       </c>
       <c r="AK121" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AL121" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM121" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="AN121" t="n">
-        <v>0.29</v>
+        <v>1.78</v>
       </c>
       <c r="AO121" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="AP121" t="n">
-        <v>0.25</v>
+        <v>1.9</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="AU121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AV121" t="n">
         <v>5</v>
       </c>
       <c r="AW121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY121" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AZ121" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC121" t="n">
         <v>8</v>
       </c>
-      <c r="BC121" t="n">
-        <v>13</v>
-      </c>
       <c r="BD121" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="BE121" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BF121" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="BG121" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BH121" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BI121" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BJ121" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="BK121" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="BL121" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="BM121" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="BN121" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="BO121" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="BP121" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="122">
@@ -26939,7 +26939,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>7785298</v>
+        <v>7785297</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -26959,12 +26959,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -26980,10 +26980,10 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N122" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -26992,17 +26992,17 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>['3', '25', '72', '87', '90+1']</t>
+          <t>['23', '28', '55']</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="R122" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S122" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T122" t="n">
         <v>1.38</v>
@@ -27011,145 +27011,145 @@
         <v>2.8</v>
       </c>
       <c r="V122" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="W122" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X122" t="n">
-        <v>7.4</v>
+        <v>6.45</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z122" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="AA122" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD122" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF122" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AG122" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AI122" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AJ122" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AK122" t="n">
         <v>1.62</v>
       </c>
       <c r="AL122" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM122" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN122" t="n">
-        <v>1.14</v>
+        <v>0.29</v>
       </c>
       <c r="AO122" t="n">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="AP122" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="AU122" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV122" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AW122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX122" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY122" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BC122" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BD122" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="BE122" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF122" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="BG122" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="BH122" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BI122" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BJ122" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="BK122" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="BL122" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="BM122" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="BN122" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="BO122" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="BP122" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="123">
@@ -27157,7 +27157,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>7785300</v>
+        <v>7785298</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -27177,197 +27177,197 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K123" t="n">
         <v>2</v>
       </c>
       <c r="L123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N123" t="n">
         <v>5</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>['27', '45+5', '90+14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>['64', '82']</t>
+          <t>['3', '25', '72', '87', '90+1']</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="R123" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S123" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="T123" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="U123" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="V123" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="W123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X123" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF123" t="n">
         <v>1.6</v>
       </c>
-      <c r="X123" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z123" t="n">
+      <c r="BG123" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL123" t="n">
         <v>2.23</v>
       </c>
-      <c r="AA123" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF123" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AG123" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AK123" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL123" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM123" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AN123" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO123" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AP123" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ123" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR123" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT123" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU123" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV123" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW123" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX123" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY123" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB123" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BE123" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BF123" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BG123" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BH123" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI123" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BJ123" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BK123" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BL123" t="n">
-        <v>2.45</v>
-      </c>
       <c r="BM123" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="BN123" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="BO123" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="BP123" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="124">
@@ -27375,7 +27375,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>7785294</v>
+        <v>7785300</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -27388,198 +27388,198 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>45864.54166666666</v>
+        <v>45864.45833333334</v>
       </c>
       <c r="F124" t="n">
         <v>15</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="I124" t="n">
         <v>2</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
+        <v>2</v>
+      </c>
+      <c r="L124" t="n">
         <v>3</v>
       </c>
-      <c r="L124" t="n">
-        <v>7</v>
-      </c>
       <c r="M124" t="n">
         <v>2</v>
       </c>
       <c r="N124" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>['4', '25', '49', '61', '72', '78', '87']</t>
+          <t>['27', '45+5', '90+14']</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>['7', '52']</t>
+          <t>['64', '82']</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="R124" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="S124" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="T124" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="U124" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="V124" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="W124" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="X124" t="n">
-        <v>3.42</v>
+        <v>4.7</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.23</v>
+        <v>2.23</v>
       </c>
       <c r="AA124" t="n">
-        <v>5.7</v>
+        <v>3.56</v>
       </c>
       <c r="AB124" t="n">
-        <v>7.8</v>
+        <v>2.57</v>
       </c>
       <c r="AC124" t="n">
         <v>1.01</v>
       </c>
       <c r="AD124" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF124" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AG124" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AH124" t="n">
-        <v>3.71</v>
+        <v>2.43</v>
       </c>
       <c r="AI124" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AJ124" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK124" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL124" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AM124" t="n">
-        <v>3.95</v>
+        <v>1.7</v>
       </c>
       <c r="AN124" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AO124" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="AR124" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AU124" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AV124" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW124" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY124" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ124" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC124" t="n">
         <v>9</v>
       </c>
-      <c r="BA124" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC124" t="n">
-        <v>7</v>
-      </c>
       <c r="BD124" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="BE124" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="BF124" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="BG124" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BH124" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI124" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BJ124" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BK124" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BL124" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BM124" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BN124" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BO124" t="n">
         <v>2.18</v>
@@ -27593,7 +27593,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>7785299</v>
+        <v>7785294</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -27606,204 +27606,204 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>45865.39583333334</v>
+        <v>45864.54166666666</v>
       </c>
       <c r="F125" t="n">
         <v>15</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L125" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N125" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>['29', '38', '54', '90+2']</t>
+          <t>['4', '25', '49', '61', '72', '78', '87']</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['7', '52']</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="R125" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S125" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U125" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W125" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X125" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ125" t="n">
         <v>2.2</v>
       </c>
-      <c r="S125" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T125" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U125" t="n">
-        <v>3</v>
-      </c>
-      <c r="V125" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W125" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X125" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y125" t="n">
+      <c r="AK125" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL125" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL125" t="n">
+      <c r="AM125" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO125" t="n">
         <v>1.25</v>
       </c>
-      <c r="AM125" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AP125" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="AQ125" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="AR125" t="n">
-        <v>2.11</v>
+        <v>2.51</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.39</v>
+        <v>3.78</v>
       </c>
       <c r="AU125" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AV125" t="n">
         <v>3</v>
       </c>
       <c r="AW125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY125" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AZ125" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC125" t="n">
         <v>7</v>
       </c>
-      <c r="BA125" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB125" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC125" t="n">
-        <v>11</v>
-      </c>
       <c r="BD125" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="BE125" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF125" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="BG125" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BH125" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BI125" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="BJ125" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BK125" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="BL125" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="BM125" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="BN125" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="BO125" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BP125" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="126">
@@ -27811,7 +27811,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>7785219</v>
+        <v>7785295</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -27824,26 +27824,26 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>45868.58333333334</v>
+        <v>45865.39583333334</v>
       </c>
       <c r="F126" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
         <v>1</v>
@@ -27852,175 +27852,611 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '50', '64']</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>1.39</v>
+        <v>4.33</v>
       </c>
       <c r="R126" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U126" t="n">
         <v>3.5</v>
       </c>
-      <c r="S126" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="T126" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="U126" t="n">
-        <v>5.25</v>
-      </c>
       <c r="V126" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="W126" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="X126" t="n">
-        <v>2.87</v>
+        <v>5.5</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA126" t="n">
-        <v>8</v>
+        <v>3.55</v>
       </c>
       <c r="AB126" t="n">
-        <v>11</v>
+        <v>1.73</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AF126" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AG126" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AH126" t="n">
-        <v>4.66</v>
+        <v>2.1</v>
       </c>
       <c r="AI126" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS126" t="n">
         <v>1.73</v>
       </c>
-      <c r="AJ126" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AO126" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP126" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ126" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AR126" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AS126" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AT126" t="n">
-        <v>3.87</v>
+        <v>3.36</v>
       </c>
       <c r="AU126" t="n">
         <v>4</v>
       </c>
       <c r="AV126" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW126" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>7785299</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>45865.39583333334</v>
+      </c>
+      <c r="F127" t="n">
+        <v>15</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2</v>
+      </c>
+      <c r="L127" t="n">
+        <v>4</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>5</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>['29', '38', '54', '90+2']</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R127" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U127" t="n">
+        <v>3</v>
+      </c>
+      <c r="V127" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X127" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>7785219</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>45868.58333333334</v>
+      </c>
+      <c r="F128" t="n">
+        <v>6</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R128" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S128" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="U128" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V128" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W128" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X128" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW128" t="n">
         <v>14</v>
       </c>
-      <c r="AX126" t="n">
+      <c r="AX128" t="n">
         <v>6</v>
       </c>
-      <c r="AY126" t="n">
+      <c r="AY128" t="n">
         <v>18</v>
       </c>
-      <c r="AZ126" t="n">
+      <c r="AZ128" t="n">
         <v>8</v>
       </c>
-      <c r="BA126" t="n">
+      <c r="BA128" t="n">
         <v>8</v>
       </c>
-      <c r="BB126" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC126" t="n">
+      <c r="BB128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC128" t="n">
         <v>9</v>
       </c>
-      <c r="BD126" t="n">
+      <c r="BD128" t="n">
         <v>1.18</v>
       </c>
-      <c r="BE126" t="n">
+      <c r="BE128" t="n">
         <v>9</v>
       </c>
-      <c r="BF126" t="n">
+      <c r="BF128" t="n">
         <v>5.1</v>
       </c>
-      <c r="BG126" t="n">
+      <c r="BG128" t="n">
         <v>1.11</v>
       </c>
-      <c r="BH126" t="n">
+      <c r="BH128" t="n">
         <v>5.3</v>
       </c>
-      <c r="BI126" t="n">
+      <c r="BI128" t="n">
         <v>1.22</v>
       </c>
-      <c r="BJ126" t="n">
+      <c r="BJ128" t="n">
         <v>3.8</v>
       </c>
-      <c r="BK126" t="n">
+      <c r="BK128" t="n">
         <v>1.38</v>
       </c>
-      <c r="BL126" t="n">
+      <c r="BL128" t="n">
         <v>2.8</v>
       </c>
-      <c r="BM126" t="n">
+      <c r="BM128" t="n">
         <v>1.61</v>
       </c>
-      <c r="BN126" t="n">
+      <c r="BN128" t="n">
         <v>2.15</v>
       </c>
-      <c r="BO126" t="n">
+      <c r="BO128" t="n">
         <v>1.94</v>
       </c>
-      <c r="BP126" t="n">
+      <c r="BP128" t="n">
         <v>1.76</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP128"/>
+  <dimension ref="A1:BP129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.22</v>
@@ -7454,7 +7454,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR32" t="n">
         <v>1.53</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.43</v>
@@ -11160,7 +11160,7 @@
         <v>1</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR49" t="n">
         <v>1.56</v>
@@ -12247,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ54" t="n">
         <v>2</v>
@@ -13776,7 +13776,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR61" t="n">
         <v>1.27</v>
@@ -16389,7 +16389,7 @@
         <v>1.4</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.11</v>
@@ -19444,7 +19444,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR87" t="n">
         <v>2.49</v>
@@ -21842,7 +21842,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR98" t="n">
         <v>2.13</v>
@@ -22275,7 +22275,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.25</v>
@@ -26199,7 +26199,7 @@
         <v>0.83</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.71</v>
@@ -26638,7 +26638,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR120" t="n">
         <v>1.36</v>
@@ -28458,6 +28458,224 @@
       </c>
       <c r="BP128" t="n">
         <v>1.76</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>7785306</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>45871.45833333334</v>
+      </c>
+      <c r="F129" t="n">
+        <v>16</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U129" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V129" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W129" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X129" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP129"/>
+  <dimension ref="A1:BP130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -938,10 +938,10 @@
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>2</v>
@@ -1132,7 +1132,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA3" t="n">
         <v>3</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
         <v>8</v>
       </c>
       <c r="AY4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>8</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
@@ -1592,10 +1592,10 @@
         <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>1</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1810,10 +1810,10 @@
         <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
         <v>4</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW7" t="n">
         <v>5</v>
@@ -2028,10 +2028,10 @@
         <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA7" t="n">
         <v>8</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
@@ -2246,10 +2246,10 @@
         <v>2</v>
       </c>
       <c r="AY8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
         <v>8</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV9" t="n">
         <v>3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
       </c>
       <c r="AW9" t="n">
         <v>9</v>
@@ -2464,10 +2464,10 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
         <v>15</v>
@@ -2682,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="AY10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA10" t="n">
         <v>6</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW11" t="n">
         <v>10</v>
@@ -2900,10 +2900,10 @@
         <v>1</v>
       </c>
       <c r="AY11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
         <v>8</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
         <v>7</v>
@@ -3118,10 +3118,10 @@
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA12" t="n">
         <v>5</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.11</v>
@@ -3324,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
         <v>6</v>
@@ -3336,10 +3336,10 @@
         <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA13" t="n">
         <v>9</v>
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
         <v>15</v>
@@ -3554,10 +3554,10 @@
         <v>12</v>
       </c>
       <c r="AY14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>1</v>
@@ -3760,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW15" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
         <v>14</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -3978,10 +3978,10 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3990,10 +3990,10 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>8</v>
@@ -4196,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
         <v>14</v>
@@ -4208,10 +4208,10 @@
         <v>4</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
         <v>5</v>
@@ -4405,19 +4405,19 @@
         <v>1.11</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="AU18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW18" t="n">
         <v>8</v>
@@ -4426,10 +4426,10 @@
         <v>5</v>
       </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
         <v>6</v>
@@ -4623,19 +4623,19 @@
         <v>1.22</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW19" t="n">
         <v>11</v>
@@ -4644,10 +4644,10 @@
         <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>11</v>
@@ -4841,19 +4841,19 @@
         <v>0.67</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
         <v>14</v>
@@ -4862,10 +4862,10 @@
         <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA20" t="n">
         <v>9</v>
@@ -5059,19 +5059,19 @@
         <v>1.22</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="AU21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
         <v>3</v>
       </c>
       <c r="AY21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA21" t="n">
         <v>9</v>
@@ -5277,19 +5277,19 @@
         <v>1.38</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW22" t="n">
         <v>9</v>
@@ -5298,10 +5298,10 @@
         <v>7</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>4</v>
@@ -5492,22 +5492,22 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AU23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -5516,10 +5516,10 @@
         <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA23" t="n">
         <v>10</v>
@@ -5713,19 +5713,19 @@
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
         <v>7</v>
@@ -5734,10 +5734,10 @@
         <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -5931,19 +5931,19 @@
         <v>0.43</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
         <v>4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -5952,10 +5952,10 @@
         <v>16</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
         <v>1</v>
@@ -6149,19 +6149,19 @@
         <v>2.11</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
         <v>6</v>
@@ -6170,10 +6170,10 @@
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA26" t="n">
         <v>4</v>
@@ -6367,19 +6367,19 @@
         <v>1.63</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW27" t="n">
         <v>3</v>
@@ -6388,10 +6388,10 @@
         <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>2</v>
@@ -6585,19 +6585,19 @@
         <v>2</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW28" t="n">
         <v>9</v>
@@ -6606,10 +6606,10 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>15</v>
       </c>
       <c r="BA28" t="n">
         <v>4</v>
@@ -6803,16 +6803,16 @@
         <v>1.25</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="AU29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV29" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>9</v>
       </c>
       <c r="AX29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -7021,19 +7021,19 @@
         <v>1.38</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="AU30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -7042,10 +7042,10 @@
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA30" t="n">
         <v>11</v>
@@ -7239,19 +7239,19 @@
         <v>0.71</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
@@ -7260,10 +7260,10 @@
         <v>5</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
         <v>10</v>
@@ -7457,19 +7457,19 @@
         <v>0.88</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="AU32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW32" t="n">
         <v>9</v>
@@ -7478,10 +7478,10 @@
         <v>10</v>
       </c>
       <c r="AY32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA32" t="n">
         <v>2</v>
@@ -7675,19 +7675,19 @@
         <v>1.11</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="AU33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW33" t="n">
         <v>10</v>
@@ -7696,10 +7696,10 @@
         <v>7</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA33" t="n">
         <v>6</v>
@@ -7893,19 +7893,19 @@
         <v>1</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.96</v>
+        <v>0.83</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="AU34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW34" t="n">
         <v>10</v>
@@ -7914,10 +7914,10 @@
         <v>11</v>
       </c>
       <c r="AY34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA34" t="n">
         <v>5</v>
@@ -8105,25 +8105,25 @@
         <v>1.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.67</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW35" t="n">
         <v>6</v>
@@ -8132,10 +8132,10 @@
         <v>5</v>
       </c>
       <c r="AY35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA35" t="n">
         <v>7</v>
@@ -8329,19 +8329,19 @@
         <v>2</v>
       </c>
       <c r="AR36" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.57</v>
+        <v>0.44</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="AU36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW36" t="n">
         <v>13</v>
@@ -8350,10 +8350,10 @@
         <v>4</v>
       </c>
       <c r="AY36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA36" t="n">
         <v>11</v>
@@ -8547,19 +8547,19 @@
         <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AU37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW37" t="n">
         <v>23</v>
@@ -8568,10 +8568,10 @@
         <v>5</v>
       </c>
       <c r="AY37" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AZ37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA37" t="n">
         <v>14</v>
@@ -8765,19 +8765,19 @@
         <v>1.22</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="AU38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW38" t="n">
         <v>22</v>
@@ -8786,10 +8786,10 @@
         <v>1</v>
       </c>
       <c r="AY38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA38" t="n">
         <v>15</v>
@@ -8983,19 +8983,19 @@
         <v>1.38</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AU39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
         <v>6</v>
@@ -9004,10 +9004,10 @@
         <v>12</v>
       </c>
       <c r="AY39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA39" t="n">
         <v>0</v>
@@ -9198,22 +9198,22 @@
         <v>1.14</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.86</v>
+        <v>3.63</v>
       </c>
       <c r="AU40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV40" t="n">
         <v>6</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>7</v>
       </c>
       <c r="AW40" t="n">
         <v>14</v>
@@ -9222,10 +9222,10 @@
         <v>4</v>
       </c>
       <c r="AY40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA40" t="n">
         <v>4</v>
@@ -9419,19 +9419,19 @@
         <v>1.63</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT41" t="n">
-        <v>4.35</v>
+        <v>4.09</v>
       </c>
       <c r="AU41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW41" t="n">
         <v>11</v>
@@ -9440,10 +9440,10 @@
         <v>6</v>
       </c>
       <c r="AY41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA41" t="n">
         <v>11</v>
@@ -9637,31 +9637,31 @@
         <v>0.43</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="AU42" t="n">
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX42" t="n">
         <v>14</v>
       </c>
       <c r="AY42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA42" t="n">
         <v>3</v>
@@ -9855,19 +9855,19 @@
         <v>1.22</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW43" t="n">
         <v>8</v>
@@ -9876,10 +9876,10 @@
         <v>9</v>
       </c>
       <c r="AY43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA43" t="n">
         <v>9</v>
@@ -10073,19 +10073,19 @@
         <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS44" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AU44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW44" t="n">
         <v>7</v>
@@ -10094,10 +10094,10 @@
         <v>4</v>
       </c>
       <c r="AY44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA44" t="n">
         <v>5</v>
@@ -10291,19 +10291,19 @@
         <v>0.71</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="AU45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW45" t="n">
         <v>14</v>
@@ -10312,10 +10312,10 @@
         <v>6</v>
       </c>
       <c r="AY45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA45" t="n">
         <v>5</v>
@@ -10509,19 +10509,19 @@
         <v>1.38</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="AU46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW46" t="n">
         <v>11</v>
@@ -10530,10 +10530,10 @@
         <v>4</v>
       </c>
       <c r="AY46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA46" t="n">
         <v>8</v>
@@ -10727,31 +10727,31 @@
         <v>1.25</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="AU47" t="n">
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX47" t="n">
         <v>6</v>
       </c>
       <c r="AY47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA47" t="n">
         <v>4</v>
@@ -10945,19 +10945,19 @@
         <v>2</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AS48" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="AU48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW48" t="n">
         <v>3</v>
@@ -10966,10 +10966,10 @@
         <v>6</v>
       </c>
       <c r="AY48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA48" t="n">
         <v>2</v>
@@ -11163,19 +11163,19 @@
         <v>0.88</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AU49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW49" t="n">
         <v>6</v>
@@ -11184,10 +11184,10 @@
         <v>6</v>
       </c>
       <c r="AY49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA49" t="n">
         <v>2</v>
@@ -11381,19 +11381,19 @@
         <v>1.11</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="AU50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW50" t="n">
         <v>9</v>
@@ -11402,10 +11402,10 @@
         <v>5</v>
       </c>
       <c r="AY50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA50" t="n">
         <v>4</v>
@@ -11593,25 +11593,25 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ51" t="n">
         <v>1</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AU51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW51" t="n">
         <v>10</v>
@@ -11620,10 +11620,10 @@
         <v>4</v>
       </c>
       <c r="AY51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA51" t="n">
         <v>4</v>
@@ -11817,19 +11817,19 @@
         <v>2.11</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AT52" t="n">
-        <v>3.59</v>
+        <v>3.33</v>
       </c>
       <c r="AU52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW52" t="n">
         <v>5</v>
@@ -11838,10 +11838,10 @@
         <v>8</v>
       </c>
       <c r="AY52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA52" t="n">
         <v>3</v>
@@ -12035,19 +12035,19 @@
         <v>0.43</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AT53" t="n">
-        <v>4.34</v>
+        <v>4.07</v>
       </c>
       <c r="AU53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW53" t="n">
         <v>16</v>
@@ -12056,10 +12056,10 @@
         <v>8</v>
       </c>
       <c r="AY53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA53" t="n">
         <v>13</v>
@@ -12253,19 +12253,19 @@
         <v>2</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AU54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW54" t="n">
         <v>9</v>
@@ -12274,10 +12274,10 @@
         <v>7</v>
       </c>
       <c r="AY54" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA54" t="n">
         <v>4</v>
@@ -12471,19 +12471,19 @@
         <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AS55" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW55" t="n">
         <v>11</v>
@@ -12492,10 +12492,10 @@
         <v>5</v>
       </c>
       <c r="AY55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA55" t="n">
         <v>6</v>
@@ -12689,19 +12689,19 @@
         <v>1.22</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT56" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU56" t="n">
         <v>3</v>
       </c>
-      <c r="AU56" t="n">
-        <v>4</v>
-      </c>
       <c r="AV56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW56" t="n">
         <v>6</v>
@@ -12710,10 +12710,10 @@
         <v>1</v>
       </c>
       <c r="AY56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA56" t="n">
         <v>7</v>
@@ -12907,19 +12907,19 @@
         <v>0.71</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW57" t="n">
         <v>3</v>
@@ -12928,10 +12928,10 @@
         <v>1</v>
       </c>
       <c r="AY57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA57" t="n">
         <v>14</v>
@@ -13125,19 +13125,19 @@
         <v>1.63</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="AU58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW58" t="n">
         <v>10</v>
@@ -13146,10 +13146,10 @@
         <v>8</v>
       </c>
       <c r="AY58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA58" t="n">
         <v>10</v>
@@ -13343,19 +13343,19 @@
         <v>1.38</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AU59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW59" t="n">
         <v>6</v>
@@ -13364,10 +13364,10 @@
         <v>6</v>
       </c>
       <c r="AY59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA59" t="n">
         <v>4</v>
@@ -13561,19 +13561,19 @@
         <v>1</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.31</v>
+        <v>3.03</v>
       </c>
       <c r="AU60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW60" t="n">
         <v>15</v>
@@ -13582,10 +13582,10 @@
         <v>5</v>
       </c>
       <c r="AY60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA60" t="n">
         <v>3</v>
@@ -13779,19 +13779,19 @@
         <v>0.88</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT61" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AU61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW61" t="n">
         <v>9</v>
@@ -13800,10 +13800,10 @@
         <v>7</v>
       </c>
       <c r="AY61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA61" t="n">
         <v>7</v>
@@ -13997,19 +13997,19 @@
         <v>1.38</v>
       </c>
       <c r="AR62" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.49</v>
+        <v>3.23</v>
       </c>
       <c r="AU62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW62" t="n">
         <v>5</v>
@@ -14018,10 +14018,10 @@
         <v>1</v>
       </c>
       <c r="AY62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA62" t="n">
         <v>5</v>
@@ -14215,19 +14215,19 @@
         <v>1.25</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="AU63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW63" t="n">
         <v>10</v>
@@ -14236,10 +14236,10 @@
         <v>13</v>
       </c>
       <c r="AY63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA63" t="n">
         <v>6</v>
@@ -14427,25 +14427,25 @@
         <v>1.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ64" t="n">
         <v>2</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AU64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW64" t="n">
         <v>7</v>
@@ -14454,10 +14454,10 @@
         <v>4</v>
       </c>
       <c r="AY64" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA64" t="n">
         <v>2</v>
@@ -14651,19 +14651,19 @@
         <v>2.11</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS65" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="AU65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW65" t="n">
         <v>5</v>
@@ -14672,10 +14672,10 @@
         <v>5</v>
       </c>
       <c r="AY65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA65" t="n">
         <v>5</v>
@@ -14869,19 +14869,19 @@
         <v>0.67</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT66" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AU66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW66" t="n">
         <v>16</v>
@@ -14890,10 +14890,10 @@
         <v>7</v>
       </c>
       <c r="AY66" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA66" t="n">
         <v>4</v>
@@ -15084,22 +15084,22 @@
         <v>0.25</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="AU67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW67" t="n">
         <v>7</v>
@@ -15108,10 +15108,10 @@
         <v>11</v>
       </c>
       <c r="AY67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ67" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA67" t="n">
         <v>6</v>
@@ -15305,19 +15305,19 @@
         <v>1.11</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="AU68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW68" t="n">
         <v>11</v>
@@ -15326,10 +15326,10 @@
         <v>9</v>
       </c>
       <c r="AY68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA68" t="n">
         <v>5</v>
@@ -15523,31 +15523,31 @@
         <v>1.38</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AU69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX69" t="n">
         <v>5</v>
       </c>
       <c r="AY69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA69" t="n">
         <v>5</v>
@@ -15741,31 +15741,31 @@
         <v>2.11</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.88</v>
+        <v>3.62</v>
       </c>
       <c r="AU70" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV70" t="n">
         <v>8</v>
       </c>
-      <c r="AV70" t="n">
+      <c r="AW70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX70" t="n">
         <v>9</v>
       </c>
-      <c r="AW70" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX70" t="n">
-        <v>5</v>
-      </c>
       <c r="AY70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ70" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA70" t="n">
         <v>4</v>
@@ -15959,28 +15959,28 @@
         <v>1.25</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AT71" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AU71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW71" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY71" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ71" t="n">
         <v>4</v>
@@ -16177,31 +16177,31 @@
         <v>1</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AU72" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV72" t="n">
         <v>7</v>
       </c>
-      <c r="AV72" t="n">
-        <v>8</v>
-      </c>
       <c r="AW72" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX72" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY72" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ72" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA72" t="n">
         <v>5</v>
@@ -16395,31 +16395,31 @@
         <v>1.11</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="AU73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV73" t="n">
         <v>4</v>
       </c>
-      <c r="AV73" t="n">
-        <v>5</v>
-      </c>
       <c r="AW73" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY73" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA73" t="n">
         <v>5</v>
@@ -16613,31 +16613,31 @@
         <v>1.63</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AU74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX74" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ74" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BA74" t="n">
         <v>6</v>
@@ -16831,31 +16831,31 @@
         <v>1.22</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT75" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU75" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ75" t="n">
         <v>9</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>8</v>
       </c>
       <c r="BA75" t="n">
         <v>3</v>
@@ -17049,31 +17049,31 @@
         <v>0.43</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT76" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="AU76" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW76" t="n">
         <v>7</v>
       </c>
-      <c r="AV76" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>4</v>
-      </c>
       <c r="AX76" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY76" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ76" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA76" t="n">
         <v>5</v>
@@ -17267,31 +17267,31 @@
         <v>2</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="AU77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW77" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ77" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA77" t="n">
         <v>3</v>
@@ -17485,28 +17485,28 @@
         <v>1.38</v>
       </c>
       <c r="AR78" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AS78" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="AT78" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AU78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV78" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ78" t="n">
         <v>13</v>
@@ -17703,31 +17703,31 @@
         <v>2.11</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT79" t="n">
-        <v>3.48</v>
+        <v>3.21</v>
       </c>
       <c r="AU79" t="n">
         <v>0</v>
       </c>
       <c r="AV79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX79" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AY79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AZ79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA79" t="n">
         <v>7</v>
@@ -17918,34 +17918,34 @@
         <v>2.33</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.81</v>
+        <v>3.57</v>
       </c>
       <c r="AU80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV80" t="n">
         <v>0</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY80" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BA80" t="n">
         <v>9</v>
@@ -18139,31 +18139,31 @@
         <v>1.25</v>
       </c>
       <c r="AR81" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AT81" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AU81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX81" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY81" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ81" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA81" t="n">
         <v>5</v>
@@ -18357,19 +18357,19 @@
         <v>0</v>
       </c>
       <c r="AR82" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AS82" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW82" t="n">
         <v>2</v>
@@ -18378,10 +18378,10 @@
         <v>11</v>
       </c>
       <c r="AY82" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ82" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA82" t="n">
         <v>3</v>
@@ -18575,31 +18575,31 @@
         <v>1.38</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AU83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW83" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX83" t="n">
         <v>7</v>
       </c>
       <c r="AY83" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA83" t="n">
         <v>3</v>
@@ -18787,34 +18787,34 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.71</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AU84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY84" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ84" t="n">
         <v>10</v>
@@ -19011,31 +19011,31 @@
         <v>2</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="AU85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY85" t="n">
         <v>11</v>
       </c>
       <c r="AZ85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA85" t="n">
         <v>6</v>
@@ -19229,19 +19229,19 @@
         <v>0.67</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="AU86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW86" t="n">
         <v>8</v>
@@ -19250,10 +19250,10 @@
         <v>8</v>
       </c>
       <c r="AY86" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA86" t="n">
         <v>6</v>
@@ -19447,31 +19447,31 @@
         <v>0.88</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.66</v>
+        <v>3.39</v>
       </c>
       <c r="AU87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX87" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY87" t="n">
         <v>14</v>
       </c>
       <c r="AZ87" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA87" t="n">
         <v>6</v>
@@ -19665,31 +19665,31 @@
         <v>2.11</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT88" t="n">
-        <v>4.19</v>
+        <v>3.93</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW88" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX88" t="n">
         <v>6</v>
       </c>
       <c r="AY88" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA88" t="n">
         <v>9</v>
@@ -19883,31 +19883,31 @@
         <v>1.22</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="AU89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW89" t="n">
         <v>4</v>
       </c>
       <c r="AX89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY89" t="n">
         <v>8</v>
       </c>
-      <c r="AY89" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ89" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA89" t="n">
         <v>5</v>
@@ -20101,31 +20101,31 @@
         <v>1.63</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AU90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW90" t="n">
         <v>23</v>
       </c>
       <c r="AX90" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ90" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA90" t="n">
         <v>10</v>
@@ -20319,31 +20319,31 @@
         <v>1</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AU91" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW91" t="n">
         <v>8</v>
       </c>
-      <c r="AV91" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW91" t="n">
-        <v>6</v>
-      </c>
       <c r="AX91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY91" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ91" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ91" t="n">
-        <v>13</v>
       </c>
       <c r="BA91" t="n">
         <v>10</v>
@@ -20537,31 +20537,31 @@
         <v>2</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AU92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW92" t="n">
         <v>5</v>
-      </c>
-      <c r="AW92" t="n">
-        <v>8</v>
       </c>
       <c r="AX92" t="n">
         <v>3</v>
       </c>
       <c r="AY92" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA92" t="n">
         <v>8</v>
@@ -20755,31 +20755,31 @@
         <v>1.38</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS93" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="AU93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW93" t="n">
         <v>8</v>
       </c>
       <c r="AX93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ93" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA93" t="n">
         <v>4</v>
@@ -20973,31 +20973,31 @@
         <v>1.11</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW94" t="n">
         <v>2</v>
       </c>
       <c r="AX94" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA94" t="n">
         <v>4</v>
@@ -21191,31 +21191,31 @@
         <v>0.43</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT95" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="AU95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW95" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX95" t="n">
         <v>5</v>
       </c>
       <c r="AY95" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA95" t="n">
         <v>9</v>
@@ -21406,34 +21406,34 @@
         <v>1.29</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AU96" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW96" t="n">
         <v>5</v>
       </c>
-      <c r="AV96" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW96" t="n">
-        <v>4</v>
-      </c>
       <c r="AX96" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY96" t="n">
         <v>9</v>
       </c>
       <c r="AZ96" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA96" t="n">
         <v>1</v>
@@ -21627,22 +21627,22 @@
         <v>0.67</v>
       </c>
       <c r="AR97" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.88</v>
+        <v>3.63</v>
       </c>
       <c r="AU97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX97" t="n">
         <v>1</v>
@@ -21651,7 +21651,7 @@
         <v>20</v>
       </c>
       <c r="AZ97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA97" t="n">
         <v>16</v>
@@ -21845,31 +21845,31 @@
         <v>0.88</v>
       </c>
       <c r="AR98" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="AU98" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV98" t="n">
         <v>8</v>
       </c>
-      <c r="AV98" t="n">
+      <c r="AW98" t="n">
         <v>9</v>
       </c>
-      <c r="AW98" t="n">
-        <v>3</v>
-      </c>
       <c r="AX98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY98" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ98" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA98" t="n">
         <v>5</v>
@@ -22063,19 +22063,19 @@
         <v>2</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AU99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW99" t="n">
         <v>6</v>
@@ -22084,10 +22084,10 @@
         <v>15</v>
       </c>
       <c r="AY99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ99" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA99" t="n">
         <v>4</v>
@@ -22281,31 +22281,31 @@
         <v>1.25</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AT100" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="AU100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV100" t="n">
         <v>0</v>
       </c>
       <c r="AW100" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY100" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA100" t="n">
         <v>2</v>
@@ -22499,25 +22499,25 @@
         <v>1.38</v>
       </c>
       <c r="AR101" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AU101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY101" t="n">
         <v>14</v>
@@ -22711,28 +22711,28 @@
         <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ102" t="n">
         <v>0</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="AU102" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW102" t="n">
         <v>9</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>8</v>
       </c>
       <c r="AX102" t="n">
         <v>8</v>
@@ -22741,7 +22741,7 @@
         <v>17</v>
       </c>
       <c r="AZ102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA102" t="n">
         <v>19</v>
@@ -22935,19 +22935,19 @@
         <v>0.71</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW103" t="n">
         <v>10</v>
@@ -22956,10 +22956,10 @@
         <v>2</v>
       </c>
       <c r="AY103" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA103" t="n">
         <v>7</v>
@@ -23153,28 +23153,28 @@
         <v>0.43</v>
       </c>
       <c r="AR104" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AT104" t="n">
-        <v>3.91</v>
+        <v>3.64</v>
       </c>
       <c r="AU104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW104" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AX104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY104" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AZ104" t="n">
         <v>4</v>
@@ -23371,19 +23371,19 @@
         <v>1.25</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AU105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW105" t="n">
         <v>7</v>
@@ -23392,10 +23392,10 @@
         <v>4</v>
       </c>
       <c r="AY105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ105" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA105" t="n">
         <v>7</v>
@@ -23589,28 +23589,28 @@
         <v>1.11</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="AU106" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW106" t="n">
         <v>9</v>
       </c>
       <c r="AX106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY106" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ106" t="n">
         <v>11</v>
@@ -23807,31 +23807,31 @@
         <v>1.38</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS107" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX107" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY107" t="n">
         <v>9</v>
       </c>
       <c r="AZ107" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA107" t="n">
         <v>3</v>
@@ -24025,31 +24025,31 @@
         <v>1.63</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.93</v>
+        <v>2.76</v>
       </c>
       <c r="AU108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX108" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AY108" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ108" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BA108" t="n">
         <v>4</v>
@@ -24243,31 +24243,31 @@
         <v>1</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AT109" t="n">
-        <v>3.35</v>
+        <v>3.09</v>
       </c>
       <c r="AU109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV109" t="n">
         <v>0</v>
       </c>
       <c r="AW109" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX109" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY109" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ109" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA109" t="n">
         <v>9</v>
@@ -24461,25 +24461,25 @@
         <v>2</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="AU110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY110" t="n">
         <v>10</v>
@@ -24679,31 +24679,31 @@
         <v>2.11</v>
       </c>
       <c r="AR111" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT111" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="AU111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY111" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ111" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA111" t="n">
         <v>5</v>
@@ -24897,28 +24897,28 @@
         <v>2</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.07</v>
+        <v>2.77</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV112" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW112" t="n">
         <v>7</v>
       </c>
-      <c r="AW112" t="n">
-        <v>5</v>
-      </c>
       <c r="AX112" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ112" t="n">
         <v>25</v>
@@ -25109,34 +25109,34 @@
         <v>1.43</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.38</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU113" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX113" t="n">
         <v>7</v>
       </c>
-      <c r="AV113" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW113" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX113" t="n">
-        <v>6</v>
-      </c>
       <c r="AY113" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ113" t="n">
         <v>12</v>
@@ -25330,34 +25330,34 @@
         <v>1.43</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AT114" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="AU114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW114" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX114" t="n">
         <v>13</v>
       </c>
       <c r="AY114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ114" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA114" t="n">
         <v>4</v>
@@ -25551,31 +25551,31 @@
         <v>0.67</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="AU115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW115" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY115" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ115" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA115" t="n">
         <v>6</v>
@@ -25769,31 +25769,31 @@
         <v>2</v>
       </c>
       <c r="AR116" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AT116" t="n">
-        <v>4.28</v>
+        <v>4.04</v>
       </c>
       <c r="AU116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW116" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX116" t="n">
         <v>7</v>
       </c>
       <c r="AY116" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ116" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA116" t="n">
         <v>4</v>
@@ -25987,28 +25987,28 @@
         <v>0</v>
       </c>
       <c r="AR117" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT117" t="n">
-        <v>3.23</v>
+        <v>3.01</v>
       </c>
       <c r="AU117" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX117" t="n">
         <v>4</v>
       </c>
-      <c r="AW117" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX117" t="n">
-        <v>3</v>
-      </c>
       <c r="AY117" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AZ117" t="n">
         <v>7</v>
@@ -26205,19 +26205,19 @@
         <v>0.71</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AU118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW118" t="n">
         <v>7</v>
@@ -26226,10 +26226,10 @@
         <v>4</v>
       </c>
       <c r="AY118" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ118" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA118" t="n">
         <v>5</v>
@@ -26423,28 +26423,28 @@
         <v>1.22</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="AU119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW119" t="n">
         <v>9</v>
       </c>
       <c r="AX119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY119" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ119" t="n">
         <v>9</v>
@@ -26641,22 +26641,22 @@
         <v>0.88</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="AU120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX120" t="n">
         <v>4</v>
@@ -26665,7 +26665,7 @@
         <v>12</v>
       </c>
       <c r="AZ120" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA120" t="n">
         <v>9</v>
@@ -26859,22 +26859,22 @@
         <v>0.67</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="AU121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX121" t="n">
         <v>8</v>
@@ -26883,7 +26883,7 @@
         <v>20</v>
       </c>
       <c r="AZ121" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA121" t="n">
         <v>7</v>
@@ -27077,22 +27077,22 @@
         <v>1</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="AU122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX122" t="n">
         <v>6</v>
@@ -27101,7 +27101,7 @@
         <v>11</v>
       </c>
       <c r="AZ122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA122" t="n">
         <v>5</v>
@@ -27295,31 +27295,31 @@
         <v>1.38</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.15</v>
+        <v>0.97</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.51</v>
+        <v>2.21</v>
       </c>
       <c r="AU123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV123" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX123" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY123" t="n">
         <v>6</v>
       </c>
       <c r="AZ123" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA123" t="n">
         <v>3</v>
@@ -27513,31 +27513,31 @@
         <v>1.63</v>
       </c>
       <c r="AR124" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="AU124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV124" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX124" t="n">
         <v>7</v>
       </c>
-      <c r="AW124" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX124" t="n">
-        <v>4</v>
-      </c>
       <c r="AY124" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ124" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA124" t="n">
         <v>4</v>
@@ -27731,31 +27731,31 @@
         <v>1.11</v>
       </c>
       <c r="AR125" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.78</v>
+        <v>3.49</v>
       </c>
       <c r="AU125" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX125" t="n">
         <v>3</v>
       </c>
-      <c r="AW125" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX125" t="n">
-        <v>6</v>
-      </c>
       <c r="AY125" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ125" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA125" t="n">
         <v>6</v>
@@ -27949,22 +27949,22 @@
         <v>2.11</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.36</v>
+        <v>3.09</v>
       </c>
       <c r="AU126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW126" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX126" t="n">
         <v>4</v>
@@ -27973,7 +27973,7 @@
         <v>13</v>
       </c>
       <c r="AZ126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA126" t="n">
         <v>2</v>
@@ -28167,31 +28167,31 @@
         <v>2</v>
       </c>
       <c r="AR127" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.39</v>
+        <v>3.11</v>
       </c>
       <c r="AU127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW127" t="n">
         <v>6</v>
       </c>
-      <c r="AV127" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW127" t="n">
-        <v>5</v>
-      </c>
       <c r="AX127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY127" t="n">
         <v>11</v>
       </c>
       <c r="AZ127" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA127" t="n">
         <v>4</v>
@@ -28385,28 +28385,28 @@
         <v>0.67</v>
       </c>
       <c r="AR128" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.87</v>
+        <v>3.59</v>
       </c>
       <c r="AU128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW128" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX128" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY128" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ128" t="n">
         <v>8</v>
@@ -28603,31 +28603,31 @@
         <v>0.88</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="AU129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX129" t="n">
         <v>7</v>
       </c>
-      <c r="AX129" t="n">
-        <v>8</v>
-      </c>
       <c r="AY129" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ129" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA129" t="n">
         <v>1</v>
@@ -28675,6 +28675,224 @@
         <v>0</v>
       </c>
       <c r="BP129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>7785304</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>45871.54166666666</v>
+      </c>
+      <c r="F130" t="n">
+        <v>16</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>4</v>
+      </c>
+      <c r="N130" t="n">
+        <v>5</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>['42', '65', '79', '84']</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U130" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V130" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W130" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X130" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>31</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP130" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP130"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.11</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.22</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.63</v>
@@ -2440,7 +2440,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR22" t="n">
         <v>1.57</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.63</v>
@@ -5928,7 +5928,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR25" t="n">
         <v>1.08</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ26" t="n">
         <v>2.11</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.63</v>
@@ -6579,10 +6579,10 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR28" t="n">
         <v>1.22</v>
@@ -7236,7 +7236,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR31" t="n">
         <v>1.65</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.38</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.63</v>
@@ -9634,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR42" t="n">
         <v>1.77</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.22</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ44" t="n">
         <v>0</v>
@@ -10288,7 +10288,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR45" t="n">
         <v>2.14</v>
@@ -10506,7 +10506,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR46" t="n">
         <v>1.82</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ48" t="n">
         <v>2</v>
@@ -12032,7 +12032,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR53" t="n">
         <v>2.42</v>
@@ -12250,7 +12250,7 @@
         <v>2</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR54" t="n">
         <v>1.48</v>
@@ -12683,7 +12683,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.22</v>
@@ -12901,10 +12901,10 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR57" t="n">
         <v>1.64</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -13994,7 +13994,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR62" t="n">
         <v>2</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.25</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.11</v>
@@ -15520,7 +15520,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR69" t="n">
         <v>0.97</v>
@@ -16171,7 +16171,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -17046,7 +17046,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR76" t="n">
         <v>1.41</v>
@@ -17264,7 +17264,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ77" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR77" t="n">
         <v>1.17</v>
@@ -17697,7 +17697,7 @@
         <v>2.4</v>
       </c>
       <c r="AP79" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ79" t="n">
         <v>2.11</v>
@@ -18133,7 +18133,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.25</v>
@@ -18572,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR83" t="n">
         <v>1.31</v>
@@ -18790,7 +18790,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR84" t="n">
         <v>1.61</v>
@@ -19005,7 +19005,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ85" t="n">
         <v>2</v>
@@ -19223,7 +19223,7 @@
         <v>1.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.67</v>
@@ -20749,7 +20749,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.38</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.11</v>
@@ -21188,7 +21188,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR95" t="n">
         <v>1.86</v>
@@ -21403,7 +21403,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.63</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.88</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR99" t="n">
         <v>1.41</v>
@@ -22496,7 +22496,7 @@
         <v>3</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR101" t="n">
         <v>1.92</v>
@@ -22929,10 +22929,10 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR103" t="n">
         <v>1.14</v>
@@ -23150,7 +23150,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR104" t="n">
         <v>2.25</v>
@@ -24455,7 +24455,7 @@
         <v>2.17</v>
       </c>
       <c r="AP110" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AQ110" t="n">
         <v>2</v>
@@ -24894,7 +24894,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR112" t="n">
         <v>1.2</v>
@@ -25112,7 +25112,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR113" t="n">
         <v>1.63</v>
@@ -25327,7 +25327,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.63</v>
@@ -25545,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.67</v>
@@ -25766,7 +25766,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AR116" t="n">
         <v>2.25</v>
@@ -25981,7 +25981,7 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ117" t="n">
         <v>0</v>
@@ -26202,7 +26202,7 @@
         <v>2</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR118" t="n">
         <v>1.38</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.88</v>
@@ -28894,6 +28894,1096 @@
       </c>
       <c r="BP130" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>7785301</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>45872.39583333334</v>
+      </c>
+      <c r="F131" t="n">
+        <v>16</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2</v>
+      </c>
+      <c r="K131" t="n">
+        <v>2</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="n">
+        <v>3</v>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>['2', '44', '66']</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R131" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T131" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U131" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V131" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W131" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X131" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>7785307</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>45872.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>16</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>2</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>3</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>['53', '81']</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S132" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U132" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X132" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>7785305</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>45872.5</v>
+      </c>
+      <c r="F133" t="n">
+        <v>16</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" t="n">
+        <v>2</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>['31', '76']</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S133" t="n">
+        <v>4</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U133" t="n">
+        <v>4</v>
+      </c>
+      <c r="V133" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>7785303</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>45872.5</v>
+      </c>
+      <c r="F134" t="n">
+        <v>16</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>2</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>['60', '74']</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>2</v>
+      </c>
+      <c r="R134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U134" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W134" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X134" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>7785302</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>45872.5</v>
+      </c>
+      <c r="F135" t="n">
+        <v>16</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" t="n">
+        <v>4</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>5</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>['16', '73', '76', '90']</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>3</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S135" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U135" t="n">
+        <v>3</v>
+      </c>
+      <c r="V135" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X135" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -29484,13 +29484,13 @@
         <v>2.32</v>
       </c>
       <c r="AU133" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV133" t="n">
         <v>3</v>
       </c>
       <c r="AW133" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX133" t="n">
         <v>3</v>
@@ -29720,13 +29720,13 @@
         <v>8</v>
       </c>
       <c r="BA134" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB134" t="n">
         <v>2</v>
       </c>
       <c r="BC134" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD134" t="n">
         <v>1.36</v>
@@ -29923,13 +29923,13 @@
         <v>5</v>
       </c>
       <c r="AV135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW135" t="n">
         <v>8</v>
       </c>
       <c r="AX135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY135" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.63</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ28" t="n">
         <v>2.13</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.38</v>
@@ -7890,7 +7890,7 @@
         <v>3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR34" t="n">
         <v>2.36</v>
@@ -8326,7 +8326,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR36" t="n">
         <v>1.87</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ44" t="n">
         <v>0</v>
@@ -10942,7 +10942,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR48" t="n">
         <v>1.08</v>
@@ -11596,7 +11596,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR51" t="n">
         <v>1.5</v>
@@ -12683,7 +12683,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.22</v>
@@ -13558,7 +13558,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR60" t="n">
         <v>1.96</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.22</v>
@@ -14430,7 +14430,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ64" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR64" t="n">
         <v>1.72</v>
@@ -15735,7 +15735,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.11</v>
@@ -16174,7 +16174,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR72" t="n">
         <v>1.5</v>
@@ -17697,7 +17697,7 @@
         <v>2.4</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
         <v>2.11</v>
@@ -17915,7 +17915,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.63</v>
@@ -19008,7 +19008,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ85" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR85" t="n">
         <v>1.24</v>
@@ -20095,7 +20095,7 @@
         <v>1.8</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.63</v>
@@ -20316,7 +20316,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR91" t="n">
         <v>1.41</v>
@@ -20534,7 +20534,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ92" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR92" t="n">
         <v>0.97</v>
@@ -20749,7 +20749,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.38</v>
@@ -23147,7 +23147,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.38</v>
@@ -24240,7 +24240,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR109" t="n">
         <v>2.02</v>
@@ -24458,7 +24458,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ110" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR110" t="n">
         <v>1.32</v>
@@ -25545,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.67</v>
@@ -27074,7 +27074,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR122" t="n">
         <v>1.14</v>
@@ -27725,7 +27725,7 @@
         <v>1.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.11</v>
@@ -28164,7 +28164,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AR127" t="n">
         <v>1.93</v>
@@ -28379,7 +28379,7 @@
         <v>0.75</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.67</v>
@@ -29687,7 +29687,7 @@
         <v>0.71</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.63</v>
@@ -29984,6 +29984,442 @@
       </c>
       <c r="BP135" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>7785311</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>45878.45833333334</v>
+      </c>
+      <c r="F136" t="n">
+        <v>17</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U136" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V136" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X136" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>7785308</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>45878.59375</v>
+      </c>
+      <c r="F137" t="n">
+        <v>17</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R137" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S137" t="n">
+        <v>7</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U137" t="n">
+        <v>4</v>
+      </c>
+      <c r="V137" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X137" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ9" t="n">
         <v>2.13</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.25</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.67</v>
@@ -4184,7 +4184,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR26" t="n">
         <v>1.18</v>
@@ -6364,7 +6364,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR27" t="n">
         <v>1.44</v>
@@ -7018,7 +7018,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR30" t="n">
         <v>2.46</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.88</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.89</v>
@@ -8980,7 +8980,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR39" t="n">
         <v>1.09</v>
@@ -9416,7 +9416,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR41" t="n">
         <v>2.52</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.25</v>
@@ -11375,7 +11375,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.11</v>
@@ -11811,10 +11811,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR52" t="n">
         <v>1.16</v>
@@ -13122,7 +13122,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR58" t="n">
         <v>1.81</v>
@@ -13340,7 +13340,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR59" t="n">
         <v>1.03</v>
@@ -13773,7 +13773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.88</v>
@@ -14648,7 +14648,7 @@
         <v>1</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR65" t="n">
         <v>1.25</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.67</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.63</v>
@@ -15738,7 +15738,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ70" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR70" t="n">
         <v>1.89</v>
@@ -16610,7 +16610,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR74" t="n">
         <v>0.97</v>
@@ -17043,7 +17043,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.38</v>
@@ -17261,7 +17261,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ77" t="n">
         <v>2.13</v>
@@ -17482,7 +17482,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR78" t="n">
         <v>2.2</v>
@@ -17700,7 +17700,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR79" t="n">
         <v>1.48</v>
@@ -18351,7 +18351,7 @@
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ82" t="n">
         <v>0</v>
@@ -19662,7 +19662,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR88" t="n">
         <v>2.2</v>
@@ -19877,7 +19877,7 @@
         <v>1.43</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.22</v>
@@ -20098,7 +20098,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR90" t="n">
         <v>1.89</v>
@@ -20313,7 +20313,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.89</v>
@@ -20752,7 +20752,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR93" t="n">
         <v>1.48</v>
@@ -22493,7 +22493,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.22</v>
@@ -23583,7 +23583,7 @@
         <v>1.43</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.11</v>
@@ -23801,10 +23801,10 @@
         <v>0.83</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR107" t="n">
         <v>1.17</v>
@@ -24022,7 +24022,7 @@
         <v>1</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR108" t="n">
         <v>1.34</v>
@@ -24676,7 +24676,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR111" t="n">
         <v>2</v>
@@ -26417,7 +26417,7 @@
         <v>1.38</v>
       </c>
       <c r="AP119" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.22</v>
@@ -27071,7 +27071,7 @@
         <v>0.71</v>
       </c>
       <c r="AP122" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.89</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR123" t="n">
         <v>1.24</v>
@@ -27507,10 +27507,10 @@
         <v>1.86</v>
       </c>
       <c r="AP124" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR124" t="n">
         <v>1.88</v>
@@ -27943,10 +27943,10 @@
         <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ126" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AR126" t="n">
         <v>1.53</v>
@@ -30420,6 +30420,660 @@
       </c>
       <c r="BP137" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>7785309</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>45879.5</v>
+      </c>
+      <c r="F138" t="n">
+        <v>17</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S138" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U138" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V138" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X138" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>7785310</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>45879.5</v>
+      </c>
+      <c r="F139" t="n">
+        <v>17</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>3</v>
+      </c>
+      <c r="M139" t="n">
+        <v>2</v>
+      </c>
+      <c r="N139" t="n">
+        <v>5</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>['51', '76', '90+1']</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>['84', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>5</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S139" t="n">
+        <v>2</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U139" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V139" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X139" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>7785312</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>45879.59375</v>
+      </c>
+      <c r="F140" t="n">
+        <v>17</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
+        <v>2</v>
+      </c>
+      <c r="N140" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>['50', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S140" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U140" t="n">
+        <v>4</v>
+      </c>
+      <c r="V140" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X140" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -30595,10 +30595,10 @@
         <v>2</v>
       </c>
       <c r="BB138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD138" t="n">
         <v>2.5</v>
@@ -30813,10 +30813,10 @@
         <v>2</v>
       </c>
       <c r="BB139" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC139" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD139" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP140"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.22</v>
@@ -2440,7 +2440,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.63</v>
@@ -6582,7 +6582,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR28" t="n">
         <v>1.22</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.22</v>
@@ -12250,7 +12250,7 @@
         <v>2</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR54" t="n">
         <v>1.48</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.63</v>
@@ -16171,7 +16171,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.89</v>
@@ -17264,7 +17264,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ77" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR77" t="n">
         <v>1.17</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.11</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR99" t="n">
         <v>1.41</v>
@@ -24455,7 +24455,7 @@
         <v>2.17</v>
       </c>
       <c r="AP110" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.89</v>
@@ -24894,7 +24894,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR112" t="n">
         <v>1.2</v>
@@ -25766,7 +25766,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR116" t="n">
         <v>2.25</v>
@@ -29036,7 +29036,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR131" t="n">
         <v>1.24</v>
@@ -29469,7 +29469,7 @@
         <v>0</v>
       </c>
       <c r="AP133" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ133" t="n">
         <v>0</v>
@@ -31074,6 +31074,224 @@
       </c>
       <c r="BP140" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>7785316</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>45884.58333333334</v>
+      </c>
+      <c r="F141" t="n">
+        <v>18</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>3</v>
+      </c>
+      <c r="K141" t="n">
+        <v>3</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>5</v>
+      </c>
+      <c r="N141" t="n">
+        <v>5</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>['10', '39', '45', '59', '84']</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="R141" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T141" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U141" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X141" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>31</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -29720,13 +29720,13 @@
         <v>8</v>
       </c>
       <c r="BA134" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB134" t="n">
         <v>2</v>
       </c>
       <c r="BC134" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD134" t="n">
         <v>1.36</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.22</v>
@@ -5492,7 +5492,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR23" t="n">
         <v>1.18</v>
@@ -9198,7 +9198,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR40" t="n">
         <v>1.95</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.38</v>
@@ -12247,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ54" t="n">
         <v>2.22</v>
@@ -15084,7 +15084,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR67" t="n">
         <v>1.22</v>
@@ -16389,7 +16389,7 @@
         <v>1.4</v>
       </c>
       <c r="AP73" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.11</v>
@@ -17918,7 +17918,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR80" t="n">
         <v>1.89</v>
@@ -21406,7 +21406,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR96" t="n">
         <v>1.27</v>
@@ -22275,7 +22275,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.25</v>
@@ -25330,7 +25330,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR114" t="n">
         <v>1.27</v>
@@ -26199,7 +26199,7 @@
         <v>0.83</v>
       </c>
       <c r="AP118" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.63</v>
@@ -28597,7 +28597,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.88</v>
@@ -28818,7 +28818,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR130" t="n">
         <v>1.66</v>
@@ -31292,6 +31292,224 @@
       </c>
       <c r="BP141" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>7785317</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45886.39583333334</v>
+      </c>
+      <c r="F142" t="n">
+        <v>18</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>2</v>
+      </c>
+      <c r="N142" t="n">
+        <v>3</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>['63', '75']</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>3</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U142" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X142" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP142"/>
+  <dimension ref="A1:BP146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.2</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.22</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.22</v>
@@ -5928,7 +5928,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR25" t="n">
         <v>1.08</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26" t="n">
         <v>2.2</v>
@@ -6361,10 +6361,10 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR27" t="n">
         <v>1.44</v>
@@ -6800,7 +6800,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR29" t="n">
         <v>1.86</v>
@@ -7236,7 +7236,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR31" t="n">
         <v>1.65</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.33</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.78</v>
@@ -9416,7 +9416,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR41" t="n">
         <v>2.52</v>
@@ -9634,7 +9634,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR42" t="n">
         <v>1.77</v>
@@ -10288,7 +10288,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR45" t="n">
         <v>2.14</v>
@@ -10724,7 +10724,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR47" t="n">
         <v>1.31</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.89</v>
@@ -12032,7 +12032,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR53" t="n">
         <v>2.42</v>
@@ -12904,7 +12904,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR57" t="n">
         <v>1.64</v>
@@ -13122,7 +13122,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR58" t="n">
         <v>1.81</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.89</v>
@@ -14209,10 +14209,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR63" t="n">
         <v>1.17</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.11</v>
@@ -15956,7 +15956,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR71" t="n">
         <v>1.86</v>
@@ -16610,7 +16610,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR74" t="n">
         <v>0.97</v>
@@ -17046,7 +17046,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR76" t="n">
         <v>1.41</v>
@@ -18133,10 +18133,10 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR81" t="n">
         <v>2.06</v>
@@ -18790,7 +18790,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR84" t="n">
         <v>1.61</v>
@@ -19005,7 +19005,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.89</v>
@@ -19223,7 +19223,7 @@
         <v>1.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.67</v>
@@ -20098,7 +20098,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR90" t="n">
         <v>1.89</v>
@@ -21188,7 +21188,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR95" t="n">
         <v>1.86</v>
@@ -21403,7 +21403,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.78</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.88</v>
@@ -22278,7 +22278,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR100" t="n">
         <v>1.43</v>
@@ -22929,10 +22929,10 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR103" t="n">
         <v>1.14</v>
@@ -23150,7 +23150,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR104" t="n">
         <v>2.25</v>
@@ -23368,7 +23368,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR105" t="n">
         <v>1.07</v>
@@ -24022,7 +24022,7 @@
         <v>1</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR108" t="n">
         <v>1.34</v>
@@ -25327,7 +25327,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.78</v>
@@ -25981,7 +25981,7 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ117" t="n">
         <v>0</v>
@@ -26202,7 +26202,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR118" t="n">
         <v>1.38</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.88</v>
@@ -27510,7 +27510,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR124" t="n">
         <v>1.88</v>
@@ -29033,7 +29033,7 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ131" t="n">
         <v>2.22</v>
@@ -29251,10 +29251,10 @@
         <v>0.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AR132" t="n">
         <v>2.12</v>
@@ -29690,7 +29690,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR134" t="n">
         <v>1.49</v>
@@ -29905,7 +29905,7 @@
         <v>1.38</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.22</v>
@@ -30780,7 +30780,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR139" t="n">
         <v>1.17</v>
@@ -31510,6 +31510,878 @@
       </c>
       <c r="BP142" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>7785313</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45886.5</v>
+      </c>
+      <c r="F143" t="n">
+        <v>18</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R143" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S143" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U143" t="n">
+        <v>3</v>
+      </c>
+      <c r="V143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X143" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>7785314</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45886.5</v>
+      </c>
+      <c r="F144" t="n">
+        <v>18</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S144" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U144" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V144" t="n">
+        <v>3</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X144" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>7785315</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45886.5</v>
+      </c>
+      <c r="F145" t="n">
+        <v>18</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>2</v>
+      </c>
+      <c r="M145" t="n">
+        <v>2</v>
+      </c>
+      <c r="N145" t="n">
+        <v>4</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>['81', '88']</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>['48', '53']</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S145" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U145" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X145" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>7785318</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>45886.59375</v>
+      </c>
+      <c r="F146" t="n">
+        <v>18</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>2</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" t="n">
+        <v>4</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>4</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>['18', '42', '75', '77']</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U146" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V146" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X146" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -31882,16 +31882,16 @@
         <v>2.62</v>
       </c>
       <c r="AU144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX144" t="n">
         <v>4</v>
-      </c>
-      <c r="AV144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW144" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX144" t="n">
-        <v>3</v>
       </c>
       <c r="AY144" t="n">
         <v>17</v>
@@ -32103,13 +32103,13 @@
         <v>7</v>
       </c>
       <c r="AV145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW145" t="n">
         <v>9</v>
       </c>
       <c r="AX145" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY145" t="n">
         <v>16</v>
@@ -32318,13 +32318,13 @@
         <v>3.9</v>
       </c>
       <c r="AU146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV146" t="n">
         <v>2</v>
       </c>
       <c r="AW146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX146" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -32318,13 +32318,13 @@
         <v>3.9</v>
       </c>
       <c r="AU146" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV146" t="n">
         <v>2</v>
       </c>
       <c r="AW146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX146" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -13788,19 +13788,19 @@
         <v>2.25</v>
       </c>
       <c r="AU61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW61" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY61" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ61" t="n">
         <v>9</v>
@@ -14006,22 +14006,22 @@
         <v>3.23</v>
       </c>
       <c r="AU62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ62" t="n">
         <v>5</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>2</v>
       </c>
       <c r="BA62" t="n">
         <v>5</v>
@@ -14224,22 +14224,22 @@
         <v>2.3</v>
       </c>
       <c r="AU63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV63" t="n">
         <v>4</v>
       </c>
       <c r="AW63" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AX63" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AY63" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AZ63" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA63" t="n">
         <v>6</v>
@@ -14445,7 +14445,7 @@
         <v>4</v>
       </c>
       <c r="AV64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW64" t="n">
         <v>7</v>
@@ -14457,7 +14457,7 @@
         <v>11</v>
       </c>
       <c r="AZ64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA64" t="n">
         <v>2</v>
@@ -14660,22 +14660,22 @@
         <v>3.22</v>
       </c>
       <c r="AU65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW65" t="n">
         <v>5</v>
       </c>
       <c r="AX65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY65" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA65" t="n">
         <v>5</v>
@@ -14881,19 +14881,19 @@
         <v>7</v>
       </c>
       <c r="AV66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AX66" t="n">
         <v>7</v>
       </c>
       <c r="AY66" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA66" t="n">
         <v>4</v>
@@ -15102,16 +15102,16 @@
         <v>6</v>
       </c>
       <c r="AW67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY67" t="n">
         <v>7</v>
       </c>
-      <c r="AX67" t="n">
+      <c r="AZ67" t="n">
         <v>11</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>17</v>
       </c>
       <c r="BA67" t="n">
         <v>6</v>
@@ -15317,19 +15317,19 @@
         <v>1</v>
       </c>
       <c r="AV68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW68" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY68" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA68" t="n">
         <v>5</v>
@@ -15526,10 +15526,10 @@
         <v>0.97</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AU69" t="n">
         <v>2</v>
@@ -15741,13 +15741,13 @@
         <v>2.2</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AS70" t="n">
         <v>1.73</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="AU70" t="n">
         <v>7</v>
@@ -15962,10 +15962,10 @@
         <v>1.86</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT71" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AU71" t="n">
         <v>7</v>
@@ -16398,10 +16398,10 @@
         <v>1.43</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AU73" t="n">
         <v>3</v>
@@ -16613,13 +16613,13 @@
         <v>1.3</v>
       </c>
       <c r="AR74" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="AS74" t="n">
         <v>1.53</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AU74" t="n">
         <v>8</v>
@@ -16831,13 +16831,13 @@
         <v>1.22</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AS75" t="n">
         <v>1.05</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="AU75" t="n">
         <v>8</v>
@@ -16858,13 +16858,13 @@
         <v>9</v>
       </c>
       <c r="BA75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB75" t="n">
         <v>9</v>
       </c>
       <c r="BC75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD75" t="n">
         <v>1.21</v>
@@ -17049,13 +17049,13 @@
         <v>0.44</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AS76" t="n">
         <v>1.54</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AU76" t="n">
         <v>6</v>
@@ -17267,13 +17267,13 @@
         <v>2.22</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AS77" t="n">
         <v>1.34</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AU77" t="n">
         <v>4</v>
@@ -17706,10 +17706,10 @@
         <v>1.48</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AT79" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="AU79" t="n">
         <v>0</v>
@@ -17921,25 +17921,25 @@
         <v>1.78</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="AU80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX80" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY80" t="n">
         <v>13</v>
@@ -18142,22 +18142,22 @@
         <v>2.06</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AT81" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="AU81" t="n">
         <v>7</v>
       </c>
       <c r="AV81" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW81" t="n">
         <v>5</v>
       </c>
       <c r="AX81" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AY81" t="n">
         <v>12</v>
@@ -18357,25 +18357,25 @@
         <v>0</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AS82" t="n">
         <v>0.82</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY82" t="n">
         <v>12</v>
@@ -18575,22 +18575,22 @@
         <v>1.22</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AU83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV83" t="n">
         <v>5</v>
       </c>
       <c r="AW83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX83" t="n">
         <v>7</v>
@@ -18802,16 +18802,16 @@
         <v>2.57</v>
       </c>
       <c r="AU84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV84" t="n">
         <v>4</v>
       </c>
-      <c r="AV84" t="n">
-        <v>2</v>
-      </c>
       <c r="AW84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX84" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY84" t="n">
         <v>6</v>
@@ -19011,13 +19011,13 @@
         <v>1.89</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="AU85" t="n">
         <v>4</v>
@@ -19229,25 +19229,25 @@
         <v>0.67</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AU86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY86" t="n">
         <v>13</v>
@@ -19450,22 +19450,22 @@
         <v>2.35</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="AU87" t="n">
         <v>4</v>
       </c>
       <c r="AV87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW87" t="n">
         <v>10</v>
       </c>
       <c r="AX87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY87" t="n">
         <v>14</v>
@@ -19665,22 +19665,22 @@
         <v>2.2</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.93</v>
+        <v>3.67</v>
       </c>
       <c r="AU88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV88" t="n">
         <v>4</v>
       </c>
       <c r="AW88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX88" t="n">
         <v>6</v>
@@ -19883,25 +19883,25 @@
         <v>1.22</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AU89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY89" t="n">
         <v>8</v>
@@ -20101,25 +20101,25 @@
         <v>1.3</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.42</v>
+        <v>3.51</v>
       </c>
       <c r="AU90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV90" t="n">
         <v>6</v>
       </c>
-      <c r="AV90" t="n">
-        <v>3</v>
-      </c>
       <c r="AW90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX90" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY90" t="n">
         <v>29</v>
@@ -20319,25 +20319,25 @@
         <v>0.89</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS91" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="AU91" t="n">
         <v>7</v>
       </c>
       <c r="AV91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW91" t="n">
         <v>8</v>
       </c>
       <c r="AX91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY91" t="n">
         <v>15</v>
@@ -20537,22 +20537,22 @@
         <v>1.89</v>
       </c>
       <c r="AR92" t="n">
-        <v>0.97</v>
+        <v>1.15</v>
       </c>
       <c r="AS92" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="AT92" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AU92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV92" t="n">
         <v>4</v>
       </c>
       <c r="AW92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX92" t="n">
         <v>3</v>
@@ -20755,22 +20755,22 @@
         <v>1.33</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AS93" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AU93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV93" t="n">
         <v>4</v>
       </c>
       <c r="AW93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX93" t="n">
         <v>2</v>
@@ -20973,25 +20973,25 @@
         <v>1.11</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="AU94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX94" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY94" t="n">
         <v>4</v>
@@ -21191,13 +21191,13 @@
         <v>0.44</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AT95" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="AU95" t="n">
         <v>9</v>
@@ -21409,25 +21409,25 @@
         <v>1.78</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AU96" t="n">
         <v>4</v>
       </c>
       <c r="AV96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW96" t="n">
         <v>5</v>
       </c>
       <c r="AX96" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY96" t="n">
         <v>9</v>
@@ -21630,10 +21630,10 @@
         <v>2.23</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="AU97" t="n">
         <v>5</v>
@@ -21848,22 +21848,22 @@
         <v>1.97</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="AU98" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV98" t="n">
         <v>7</v>
       </c>
-      <c r="AV98" t="n">
-        <v>8</v>
-      </c>
       <c r="AW98" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX98" t="n">
         <v>9</v>
-      </c>
-      <c r="AX98" t="n">
-        <v>8</v>
       </c>
       <c r="AY98" t="n">
         <v>16</v>
@@ -22063,25 +22063,25 @@
         <v>2.22</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AU99" t="n">
         <v>2</v>
       </c>
       <c r="AV99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW99" t="n">
         <v>6</v>
       </c>
       <c r="AX99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY99" t="n">
         <v>8</v>
@@ -22281,22 +22281,22 @@
         <v>1.22</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AU100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV100" t="n">
         <v>0</v>
       </c>
       <c r="AW100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX100" t="n">
         <v>2</v>
@@ -22499,25 +22499,25 @@
         <v>1.22</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AU101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY101" t="n">
         <v>14</v>
@@ -22717,25 +22717,25 @@
         <v>0</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AU102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW102" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX102" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY102" t="n">
         <v>17</v>
@@ -22935,25 +22935,25 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AS103" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AU103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY103" t="n">
         <v>14</v>
@@ -23153,22 +23153,22 @@
         <v>0.44</v>
       </c>
       <c r="AR104" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AT104" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AU104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV104" t="n">
         <v>1</v>
       </c>
       <c r="AW104" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX104" t="n">
         <v>3</v>
@@ -23371,25 +23371,25 @@
         <v>1.22</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AU105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY105" t="n">
         <v>14</v>
@@ -23589,25 +23589,25 @@
         <v>1.11</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AS106" t="n">
         <v>1.15</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AU106" t="n">
         <v>6</v>
       </c>
       <c r="AV106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW106" t="n">
         <v>9</v>
       </c>
       <c r="AX106" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY106" t="n">
         <v>15</v>
@@ -23807,22 +23807,22 @@
         <v>1.33</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AS107" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT107" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AU107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV107" t="n">
         <v>4</v>
       </c>
       <c r="AW107" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX107" t="n">
         <v>12</v>
@@ -24025,25 +24025,25 @@
         <v>1.3</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="AU108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX108" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY108" t="n">
         <v>6</v>
@@ -24243,22 +24243,22 @@
         <v>0.89</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AT109" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="AU109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV109" t="n">
         <v>0</v>
       </c>
       <c r="AW109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX109" t="n">
         <v>11</v>
@@ -24461,25 +24461,25 @@
         <v>1.89</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AS110" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AU110" t="n">
         <v>3</v>
       </c>
       <c r="AV110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW110" t="n">
         <v>7</v>
       </c>
       <c r="AX110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY110" t="n">
         <v>10</v>
@@ -24679,25 +24679,25 @@
         <v>2.2</v>
       </c>
       <c r="AR111" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AT111" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AU111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW111" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY111" t="n">
         <v>16</v>
@@ -24897,22 +24897,22 @@
         <v>2.22</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="AU112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV112" t="n">
         <v>6</v>
       </c>
       <c r="AW112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX112" t="n">
         <v>19</v>
@@ -25115,25 +25115,25 @@
         <v>1.22</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AU113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY113" t="n">
         <v>16</v>
@@ -25333,25 +25333,25 @@
         <v>1.78</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AU114" t="n">
         <v>3</v>
       </c>
       <c r="AV114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW114" t="n">
         <v>8</v>
       </c>
       <c r="AX114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY114" t="n">
         <v>11</v>
@@ -25551,25 +25551,25 @@
         <v>0.67</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AU115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY115" t="n">
         <v>14</v>
@@ -25772,22 +25772,22 @@
         <v>2.25</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AT116" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="AU116" t="n">
         <v>5</v>
       </c>
       <c r="AV116" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW116" t="n">
         <v>8</v>
       </c>
       <c r="AX116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY116" t="n">
         <v>13</v>
@@ -25987,25 +25987,25 @@
         <v>0</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AT117" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AU117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV117" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX117" t="n">
         <v>3</v>
-      </c>
-      <c r="AW117" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX117" t="n">
-        <v>4</v>
       </c>
       <c r="AY117" t="n">
         <v>30</v>
@@ -26205,13 +26205,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AS118" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AU118" t="n">
         <v>6</v>
@@ -26423,22 +26423,22 @@
         <v>1.22</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV119" t="n">
         <v>3</v>
       </c>
       <c r="AW119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX119" t="n">
         <v>6</v>
@@ -26641,25 +26641,25 @@
         <v>0.88</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AU120" t="n">
         <v>2</v>
       </c>
       <c r="AV120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW120" t="n">
         <v>10</v>
       </c>
       <c r="AX120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY120" t="n">
         <v>12</v>
@@ -26859,22 +26859,22 @@
         <v>0.67</v>
       </c>
       <c r="AR121" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS121" t="n">
         <v>1.18</v>
       </c>
-      <c r="AS121" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AT121" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AU121" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV121" t="n">
         <v>4</v>
       </c>
       <c r="AW121" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AX121" t="n">
         <v>8</v>
@@ -27077,13 +27077,13 @@
         <v>0.89</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AU122" t="n">
         <v>4</v>
@@ -27295,25 +27295,25 @@
         <v>1.33</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AS123" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AU123" t="n">
         <v>1</v>
       </c>
       <c r="AV123" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW123" t="n">
         <v>5</v>
       </c>
       <c r="AX123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY123" t="n">
         <v>6</v>
@@ -27513,25 +27513,25 @@
         <v>1.3</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="AU124" t="n">
         <v>10</v>
       </c>
       <c r="AV124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW124" t="n">
         <v>13</v>
       </c>
       <c r="AX124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY124" t="n">
         <v>23</v>
@@ -27731,13 +27731,13 @@
         <v>1.11</v>
       </c>
       <c r="AR125" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.49</v>
+        <v>3.39</v>
       </c>
       <c r="AU125" t="n">
         <v>13</v>
@@ -27949,22 +27949,22 @@
         <v>2.2</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AU126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV126" t="n">
         <v>5</v>
       </c>
       <c r="AW126" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX126" t="n">
         <v>4</v>
@@ -28167,13 +28167,13 @@
         <v>1.89</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="AU127" t="n">
         <v>5</v>
@@ -28340,10 +28340,10 @@
         <v>11</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE128" t="n">
         <v>1.01</v>
@@ -28385,25 +28385,25 @@
         <v>0.67</v>
       </c>
       <c r="AR128" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.59</v>
+        <v>3.49</v>
       </c>
       <c r="AU128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW128" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY128" t="n">
         <v>19</v>
@@ -28582,13 +28582,13 @@
         <v>1.91</v>
       </c>
       <c r="AK129" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL129" t="n">
         <v>0</v>
       </c>
       <c r="AM129" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AN129" t="n">
         <v>2.14</v>
@@ -28603,25 +28603,25 @@
         <v>0.88</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AS129" t="n">
         <v>1.28</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="AU129" t="n">
         <v>5</v>
       </c>
       <c r="AV129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW129" t="n">
         <v>5</v>
       </c>
       <c r="AX129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY129" t="n">
         <v>10</v>
@@ -28639,43 +28639,43 @@
         <v>6</v>
       </c>
       <c r="BD129" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BE129" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="BF129" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BG129" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BH129" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="BI129" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BJ129" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BK129" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BL129" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BM129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BN129" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BO129" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BP129" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="130">
@@ -28776,16 +28776,16 @@
         <v>2.44</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AG130" t="n">
         <v>1.47</v>
@@ -28800,13 +28800,13 @@
         <v>2.63</v>
       </c>
       <c r="AK130" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL130" t="n">
         <v>0</v>
       </c>
       <c r="AM130" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AN130" t="n">
         <v>1.29</v>
@@ -28821,25 +28821,25 @@
         <v>1.78</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AT130" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="AU130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX130" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY130" t="n">
         <v>13</v>
@@ -28857,43 +28857,43 @@
         <v>17</v>
       </c>
       <c r="BD130" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BE130" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BF130" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BG130" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BH130" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BI130" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BJ130" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BK130" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BL130" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BM130" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BN130" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BO130" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BP130" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="131">
@@ -29039,25 +29039,25 @@
         <v>2.22</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AT131" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="AU131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV131" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW131" t="n">
         <v>6</v>
       </c>
-      <c r="AW131" t="n">
+      <c r="AX131" t="n">
         <v>9</v>
-      </c>
-      <c r="AX131" t="n">
-        <v>8</v>
       </c>
       <c r="AY131" t="n">
         <v>10</v>
@@ -29257,25 +29257,25 @@
         <v>0.44</v>
       </c>
       <c r="AR132" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="AU132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV132" t="n">
         <v>6</v>
       </c>
-      <c r="AV132" t="n">
-        <v>5</v>
-      </c>
       <c r="AW132" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY132" t="n">
         <v>14</v>
@@ -29475,22 +29475,22 @@
         <v>0</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AU133" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV133" t="n">
         <v>3</v>
       </c>
       <c r="AW133" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX133" t="n">
         <v>3</v>
@@ -29693,13 +29693,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AS134" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="AU134" t="n">
         <v>6</v>
@@ -29720,13 +29720,13 @@
         <v>8</v>
       </c>
       <c r="BA134" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB134" t="n">
         <v>2</v>
       </c>
       <c r="BC134" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD134" t="n">
         <v>1.36</v>
@@ -29911,25 +29911,25 @@
         <v>1.22</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AU135" t="n">
         <v>5</v>
       </c>
       <c r="AV135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW135" t="n">
         <v>8</v>
       </c>
       <c r="AX135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY135" t="n">
         <v>13</v>
@@ -30084,10 +30084,10 @@
         <v>5.3</v>
       </c>
       <c r="AC136" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AD136" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE136" t="n">
         <v>1.15</v>
@@ -30129,25 +30129,25 @@
         <v>0.89</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AU136" t="n">
         <v>7</v>
       </c>
       <c r="AV136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW136" t="n">
         <v>16</v>
       </c>
       <c r="AX136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY136" t="n">
         <v>23</v>
@@ -30302,10 +30302,10 @@
         <v>6.3</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD137" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE137" t="n">
         <v>1.11</v>
@@ -30347,25 +30347,25 @@
         <v>1.89</v>
       </c>
       <c r="AR137" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="AU137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY137" t="n">
         <v>10</v>
@@ -30565,25 +30565,25 @@
         <v>1.33</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AU138" t="n">
         <v>2</v>
       </c>
       <c r="AV138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW138" t="n">
         <v>2</v>
       </c>
       <c r="AX138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY138" t="n">
         <v>4</v>
@@ -30786,22 +30786,22 @@
         <v>1.17</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AU139" t="n">
         <v>5</v>
       </c>
       <c r="AV139" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW139" t="n">
         <v>2</v>
       </c>
       <c r="AX139" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY139" t="n">
         <v>7</v>
@@ -31001,25 +31001,25 @@
         <v>2.2</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="AU140" t="n">
         <v>2</v>
       </c>
       <c r="AV140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW140" t="n">
         <v>6</v>
       </c>
       <c r="AX140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY140" t="n">
         <v>8</v>
@@ -31219,13 +31219,13 @@
         <v>2.22</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AS141" t="n">
         <v>1.82</v>
       </c>
       <c r="AT141" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="AU141" t="n">
         <v>1</v>
@@ -31437,13 +31437,13 @@
         <v>1.78</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="AU142" t="n">
         <v>4</v>
@@ -31655,13 +31655,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AS143" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AU143" t="n">
         <v>5</v>
@@ -31873,13 +31873,13 @@
         <v>1.22</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AU144" t="n">
         <v>5</v>
@@ -32091,13 +32091,13 @@
         <v>0.44</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AU145" t="n">
         <v>7</v>
@@ -32309,22 +32309,22 @@
         <v>1.3</v>
       </c>
       <c r="AR146" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AT146" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AU146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV146" t="n">
         <v>2</v>
       </c>
       <c r="AW146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX146" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP146"/>
+  <dimension ref="A1:BP147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.44</v>
@@ -2658,7 +2658,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.3</v>
@@ -7890,7 +7890,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR34" t="n">
         <v>2.36</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.89</v>
@@ -11596,7 +11596,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR51" t="n">
         <v>1.5</v>
@@ -13558,7 +13558,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR60" t="n">
         <v>1.96</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.11</v>
@@ -16174,7 +16174,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR72" t="n">
         <v>1.5</v>
@@ -19223,7 +19223,7 @@
         <v>1.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.67</v>
@@ -20316,7 +20316,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR91" t="n">
         <v>1.37</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5600000000000001</v>
@@ -24240,7 +24240,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR109" t="n">
         <v>1.85</v>
@@ -25327,7 +25327,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.78</v>
@@ -27074,7 +27074,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR122" t="n">
         <v>1.15</v>
@@ -29905,7 +29905,7 @@
         <v>1.38</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.22</v>
@@ -30126,7 +30126,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR136" t="n">
         <v>1.48</v>
@@ -31867,7 +31867,7 @@
         <v>1.25</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.22</v>
@@ -32382,6 +32382,224 @@
       </c>
       <c r="BP146" t="n">
         <v>1.62</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>7785322</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45891.58333333334</v>
+      </c>
+      <c r="F147" t="n">
+        <v>19</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="n">
+        <v>2</v>
+      </c>
+      <c r="N147" t="n">
+        <v>4</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['48', '64']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['14', '88']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X147" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -32542,13 +32542,13 @@
         <v>4</v>
       </c>
       <c r="AW147" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX147" t="n">
         <v>1</v>
       </c>
       <c r="AY147" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ147" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP147"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.3</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>2.22</v>
@@ -3094,7 +3094,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR18" t="n">
         <v>0.79</v>
@@ -4838,7 +4838,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR20" t="n">
         <v>1.69</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>2.22</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.88</v>
@@ -7672,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR33" t="n">
         <v>1.74</v>
@@ -8108,7 +8108,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR35" t="n">
         <v>1.38</v>
@@ -8326,7 +8326,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR36" t="n">
         <v>1.87</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>0</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.22</v>
@@ -10942,7 +10942,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR48" t="n">
         <v>1.08</v>
@@ -11378,7 +11378,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR50" t="n">
         <v>2.03</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ52" t="n">
         <v>2.2</v>
@@ -12683,7 +12683,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.22</v>
@@ -13773,7 +13773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.88</v>
@@ -14430,7 +14430,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR64" t="n">
         <v>1.72</v>
@@ -14866,7 +14866,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR66" t="n">
         <v>1.82</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.78</v>
@@ -15302,7 +15302,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR68" t="n">
         <v>0.97</v>
@@ -16392,7 +16392,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR73" t="n">
         <v>1.43</v>
@@ -17043,7 +17043,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.44</v>
@@ -17261,7 +17261,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ77" t="n">
         <v>2.22</v>
@@ -17697,7 +17697,7 @@
         <v>2.4</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ79" t="n">
         <v>2.2</v>
@@ -19008,7 +19008,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR85" t="n">
         <v>1.15</v>
@@ -19226,7 +19226,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR86" t="n">
         <v>0.96</v>
@@ -19877,7 +19877,7 @@
         <v>1.43</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.22</v>
@@ -20313,7 +20313,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.9</v>
@@ -20534,7 +20534,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR92" t="n">
         <v>1.15</v>
@@ -20749,7 +20749,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.33</v>
@@ -20970,7 +20970,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR94" t="n">
         <v>1.63</v>
@@ -21624,7 +21624,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR97" t="n">
         <v>2.23</v>
@@ -23583,10 +23583,10 @@
         <v>1.43</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR106" t="n">
         <v>1.44</v>
@@ -23801,7 +23801,7 @@
         <v>0.83</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.33</v>
@@ -24458,7 +24458,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR110" t="n">
         <v>1.44</v>
@@ -25545,10 +25545,10 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR115" t="n">
         <v>1.39</v>
@@ -26856,7 +26856,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR121" t="n">
         <v>1.24</v>
@@ -27071,7 +27071,7 @@
         <v>0.71</v>
       </c>
       <c r="AP122" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.9</v>
@@ -27728,7 +27728,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR125" t="n">
         <v>2.21</v>
@@ -27943,7 +27943,7 @@
         <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ126" t="n">
         <v>2.2</v>
@@ -28164,7 +28164,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR127" t="n">
         <v>1.79</v>
@@ -28382,7 +28382,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR128" t="n">
         <v>2.3</v>
@@ -29687,7 +29687,7 @@
         <v>0.71</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.5600000000000001</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.9</v>
@@ -30344,7 +30344,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR137" t="n">
         <v>2.3</v>
@@ -30559,7 +30559,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.33</v>
@@ -30777,7 +30777,7 @@
         <v>1.63</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.3</v>
@@ -32600,6 +32600,660 @@
       </c>
       <c r="BP147" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>7785321</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45893.39583333334</v>
+      </c>
+      <c r="F148" t="n">
+        <v>19</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="n">
+        <v>2</v>
+      </c>
+      <c r="L148" t="n">
+        <v>2</v>
+      </c>
+      <c r="M148" t="n">
+        <v>3</v>
+      </c>
+      <c r="N148" t="n">
+        <v>5</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>['11', '56']</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>['33', '68', '71']</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S148" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U148" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V148" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X148" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>7785320</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45893.5</v>
+      </c>
+      <c r="F149" t="n">
+        <v>19</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" t="n">
+        <v>2</v>
+      </c>
+      <c r="M149" t="n">
+        <v>2</v>
+      </c>
+      <c r="N149" t="n">
+        <v>4</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>['67', '72']</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>['18', '53']</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R149" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S149" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U149" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V149" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X149" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>7785323</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45893.59375</v>
+      </c>
+      <c r="F150" t="n">
+        <v>19</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>['27', '73']</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R150" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S150" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U150" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V150" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X150" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.3</v>
@@ -4620,7 +4620,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR19" t="n">
         <v>1.89</v>
@@ -5056,7 +5056,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR21" t="n">
         <v>1.81</v>
@@ -8105,7 +8105,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.7</v>
@@ -8762,7 +8762,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR38" t="n">
         <v>1.62</v>
@@ -9852,7 +9852,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR43" t="n">
         <v>1.5</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.9</v>
@@ -12686,7 +12686,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR56" t="n">
         <v>1.55</v>
@@ -14427,7 +14427,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.7</v>
@@ -16828,7 +16828,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR75" t="n">
         <v>1.93</v>
@@ -18787,7 +18787,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.5600000000000001</v>
@@ -19880,7 +19880,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR89" t="n">
         <v>1.15</v>
@@ -22711,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ102" t="n">
         <v>0</v>
@@ -25109,7 +25109,7 @@
         <v>1.43</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.22</v>
@@ -26420,7 +26420,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR119" t="n">
         <v>1.77</v>
@@ -28815,7 +28815,7 @@
         <v>1.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.78</v>
@@ -32763,13 +32763,13 @@
         <v>4</v>
       </c>
       <c r="AX148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY148" t="n">
         <v>9</v>
       </c>
       <c r="AZ148" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA148" t="n">
         <v>3</v>
@@ -33254,6 +33254,224 @@
       </c>
       <c r="BP150" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>7785325</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45894.58333333334</v>
+      </c>
+      <c r="F151" t="n">
+        <v>19</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R151" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S151" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U151" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="V151" t="n">
+        <v>2</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X151" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -32754,16 +32754,16 @@
         <v>2.28</v>
       </c>
       <c r="AU148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV148" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX148" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY148" t="n">
         <v>9</v>
@@ -32972,19 +32972,19 @@
         <v>2.53</v>
       </c>
       <c r="AU149" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV149" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW149" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX149" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY149" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ149" t="n">
         <v>12</v>
@@ -33199,13 +33199,13 @@
         <v>3</v>
       </c>
       <c r="AX150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY150" t="n">
         <v>6</v>
       </c>
       <c r="AZ150" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA150" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -33408,19 +33408,19 @@
         <v>2.66</v>
       </c>
       <c r="AU151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV151" t="n">
         <v>4</v>
-      </c>
-      <c r="AV151" t="n">
-        <v>5</v>
       </c>
       <c r="AW151" t="n">
         <v>7</v>
       </c>
       <c r="AX151" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY151" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ151" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.2</v>
@@ -3966,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.22</v>
@@ -7236,7 +7236,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR31" t="n">
         <v>1.65</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.78</v>
@@ -10288,7 +10288,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR45" t="n">
         <v>2.14</v>
@@ -12904,7 +12904,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR57" t="n">
         <v>1.64</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.9</v>
@@ -18133,7 +18133,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.22</v>
@@ -18790,7 +18790,7 @@
         <v>1</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR84" t="n">
         <v>1.61</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.88</v>
@@ -22932,7 +22932,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR103" t="n">
         <v>1.12</v>
@@ -25981,7 +25981,7 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ117" t="n">
         <v>0</v>
@@ -26202,7 +26202,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR118" t="n">
         <v>1.43</v>
@@ -29251,7 +29251,7 @@
         <v>0.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.44</v>
@@ -29690,7 +29690,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR134" t="n">
         <v>1.43</v>
@@ -31652,7 +31652,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR143" t="n">
         <v>1.17</v>
@@ -32303,7 +32303,7 @@
         <v>1.44</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.3</v>
@@ -33472,6 +33472,224 @@
       </c>
       <c r="BP151" t="n">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>7785333</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45899.54166666666</v>
+      </c>
+      <c r="F152" t="n">
+        <v>20</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="n">
+        <v>4</v>
+      </c>
+      <c r="L152" t="n">
+        <v>3</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
+      <c r="N152" t="n">
+        <v>5</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>['3', '8', '28']</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>['45+7', '52']</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S152" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U152" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V152" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X152" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -33629,13 +33629,13 @@
         <v>3</v>
       </c>
       <c r="AV152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW152" t="n">
         <v>14</v>
       </c>
       <c r="AX152" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY152" t="n">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -33635,13 +33635,13 @@
         <v>14</v>
       </c>
       <c r="AX152" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY152" t="n">
         <v>17</v>
       </c>
       <c r="AZ152" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA152" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP152"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.4</v>
@@ -2004,7 +2004,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.3</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.4</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.4</v>
@@ -5274,7 +5274,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR22" t="n">
         <v>1.57</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR23" t="n">
         <v>1.18</v>
@@ -5710,7 +5710,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR24" t="n">
         <v>1.25</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.44</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ26" t="n">
         <v>2.2</v>
@@ -6364,7 +6364,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR27" t="n">
         <v>1.44</v>
@@ -6582,7 +6582,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR28" t="n">
         <v>1.22</v>
@@ -6800,7 +6800,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR29" t="n">
         <v>1.86</v>
@@ -7018,7 +7018,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR30" t="n">
         <v>2.46</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.9</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.7</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR37" t="n">
         <v>2.12</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR39" t="n">
         <v>1.09</v>
@@ -9198,7 +9198,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR40" t="n">
         <v>1.95</v>
@@ -9413,10 +9413,10 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR41" t="n">
         <v>2.52</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.44</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.4</v>
@@ -10070,7 +10070,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR44" t="n">
         <v>1.33</v>
@@ -10506,7 +10506,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR46" t="n">
         <v>1.82</v>
@@ -10724,7 +10724,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR47" t="n">
         <v>1.31</v>
@@ -11375,7 +11375,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.3</v>
@@ -12029,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.44</v>
@@ -12247,10 +12247,10 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR54" t="n">
         <v>1.48</v>
@@ -12468,7 +12468,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR55" t="n">
         <v>2.09</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.5</v>
@@ -13122,7 +13122,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR58" t="n">
         <v>1.81</v>
@@ -13337,10 +13337,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR59" t="n">
         <v>1.03</v>
@@ -13994,7 +13994,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR62" t="n">
         <v>2</v>
@@ -14209,10 +14209,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR63" t="n">
         <v>1.17</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.7</v>
@@ -15084,7 +15084,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR67" t="n">
         <v>1.22</v>
@@ -15517,10 +15517,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR69" t="n">
         <v>0.97</v>
@@ -15956,7 +15956,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR71" t="n">
         <v>1.86</v>
@@ -16171,7 +16171,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.9</v>
@@ -16389,7 +16389,7 @@
         <v>1.4</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.3</v>
@@ -16607,10 +16607,10 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR74" t="n">
         <v>0.99</v>
@@ -17264,7 +17264,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR77" t="n">
         <v>1.14</v>
@@ -17482,7 +17482,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR78" t="n">
         <v>2.2</v>
@@ -17918,7 +17918,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR80" t="n">
         <v>1.87</v>
@@ -18136,7 +18136,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR81" t="n">
         <v>2.06</v>
@@ -18351,10 +18351,10 @@
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR82" t="n">
         <v>1.82</v>
@@ -18572,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR83" t="n">
         <v>1.24</v>
@@ -19005,7 +19005,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.7</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.88</v>
@@ -20098,7 +20098,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR90" t="n">
         <v>1.87</v>
@@ -20531,7 +20531,7 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.7</v>
@@ -20752,7 +20752,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR93" t="n">
         <v>1.4</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.3</v>
@@ -21403,10 +21403,10 @@
         <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR96" t="n">
         <v>1.2</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.7</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR99" t="n">
         <v>1.37</v>
@@ -22275,10 +22275,10 @@
         <v>1.67</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR100" t="n">
         <v>1.46</v>
@@ -22493,10 +22493,10 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR101" t="n">
         <v>1.8</v>
@@ -22714,7 +22714,7 @@
         <v>1</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR102" t="n">
         <v>1.49</v>
@@ -23365,10 +23365,10 @@
         <v>1.43</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR105" t="n">
         <v>1.18</v>
@@ -23804,7 +23804,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR107" t="n">
         <v>1.15</v>
@@ -24022,7 +24022,7 @@
         <v>1</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR108" t="n">
         <v>1.3</v>
@@ -24455,7 +24455,7 @@
         <v>2.17</v>
       </c>
       <c r="AP110" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.7</v>
@@ -24891,10 +24891,10 @@
         <v>1.6</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR112" t="n">
         <v>1.26</v>
@@ -25112,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR113" t="n">
         <v>1.59</v>
@@ -25330,7 +25330,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR114" t="n">
         <v>1.24</v>
@@ -25763,10 +25763,10 @@
         <v>1.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR116" t="n">
         <v>2.25</v>
@@ -25984,7 +25984,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR117" t="n">
         <v>1.93</v>
@@ -26199,7 +26199,7 @@
         <v>0.83</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.5</v>
@@ -26417,7 +26417,7 @@
         <v>1.38</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.4</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.88</v>
@@ -26853,7 +26853,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.7</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR123" t="n">
         <v>1.22</v>
@@ -27507,10 +27507,10 @@
         <v>1.86</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR124" t="n">
         <v>1.77</v>
@@ -28597,7 +28597,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.88</v>
@@ -28818,7 +28818,7 @@
         <v>1</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR130" t="n">
         <v>1.64</v>
@@ -29033,10 +29033,10 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR131" t="n">
         <v>1.19</v>
@@ -29469,10 +29469,10 @@
         <v>0</v>
       </c>
       <c r="AP133" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR133" t="n">
         <v>1.4</v>
@@ -29908,7 +29908,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR135" t="n">
         <v>1.24</v>
@@ -30562,7 +30562,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR138" t="n">
         <v>1.48</v>
@@ -30780,7 +30780,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR139" t="n">
         <v>1.17</v>
@@ -30995,7 +30995,7 @@
         <v>2.11</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ140" t="n">
         <v>2.2</v>
@@ -31213,10 +31213,10 @@
         <v>2.13</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR141" t="n">
         <v>1.54</v>
@@ -31431,10 +31431,10 @@
         <v>1.63</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR142" t="n">
         <v>1.45</v>
@@ -31649,7 +31649,7 @@
         <v>0.63</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.5</v>
@@ -31870,7 +31870,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR144" t="n">
         <v>1.28</v>
@@ -32306,7 +32306,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR146" t="n">
         <v>2.05</v>
@@ -33690,6 +33690,1532 @@
       </c>
       <c r="BP152" t="n">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>7785328</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45900.39583333334</v>
+      </c>
+      <c r="F153" t="n">
+        <v>20</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2</v>
+      </c>
+      <c r="M153" t="n">
+        <v>2</v>
+      </c>
+      <c r="N153" t="n">
+        <v>4</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>['75', '89']</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>['67', '69']</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R153" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S153" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U153" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V153" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W153" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X153" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>7785326</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>45900.5</v>
+      </c>
+      <c r="F154" t="n">
+        <v>20</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>2</v>
+      </c>
+      <c r="J154" t="n">
+        <v>2</v>
+      </c>
+      <c r="K154" t="n">
+        <v>4</v>
+      </c>
+      <c r="L154" t="n">
+        <v>2</v>
+      </c>
+      <c r="M154" t="n">
+        <v>2</v>
+      </c>
+      <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['2', '25']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>['8', '36']</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R154" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="S154" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U154" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X154" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>7785327</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45900.5</v>
+      </c>
+      <c r="F155" t="n">
+        <v>20</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3</v>
+      </c>
+      <c r="N155" t="n">
+        <v>4</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['37', '47', '54']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R155" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S155" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U155" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V155" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X155" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>7785329</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45900.5</v>
+      </c>
+      <c r="F156" t="n">
+        <v>20</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
+      <c r="N156" t="n">
+        <v>3</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>['51', '71']</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R156" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S156" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U156" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X156" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>7785331</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45900.5</v>
+      </c>
+      <c r="F157" t="n">
+        <v>20</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" t="n">
+        <v>2</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>2</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>['3', '68']</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S157" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X157" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>7785332</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45900.5</v>
+      </c>
+      <c r="F158" t="n">
+        <v>20</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1</v>
+      </c>
+      <c r="L158" t="n">
+        <v>2</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>3</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>['39', '56']</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R158" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S158" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U158" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V158" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X158" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>7785330</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45900.59375</v>
+      </c>
+      <c r="F159" t="n">
+        <v>20</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>2</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>2</v>
+      </c>
+      <c r="L159" t="n">
+        <v>3</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>4</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>['2', '3', '69']</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S159" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U159" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V159" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X159" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -33817,7 +33817,7 @@
         <v>1.22</v>
       </c>
       <c r="AL153" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM153" t="n">
         <v>1.2</v>
@@ -33844,7 +33844,7 @@
         <v>3.01</v>
       </c>
       <c r="AU153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV153" t="n">
         <v>6</v>
@@ -33856,7 +33856,7 @@
         <v>11</v>
       </c>
       <c r="AY153" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ153" t="n">
         <v>17</v>
@@ -33865,10 +33865,10 @@
         <v>2</v>
       </c>
       <c r="BB153" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC153" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD153" t="n">
         <v>3.9</v>
@@ -34065,7 +34065,7 @@
         <v>3</v>
       </c>
       <c r="AV154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW154" t="n">
         <v>16</v>
@@ -34077,7 +34077,7 @@
         <v>19</v>
       </c>
       <c r="AZ154" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA154" t="n">
         <v>5</v>
@@ -34289,13 +34289,13 @@
         <v>2</v>
       </c>
       <c r="AX155" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY155" t="n">
         <v>7</v>
       </c>
       <c r="AZ155" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA155" t="n">
         <v>6</v>
@@ -34504,13 +34504,13 @@
         <v>2</v>
       </c>
       <c r="AW156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX156" t="n">
         <v>12</v>
       </c>
       <c r="AY156" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ156" t="n">
         <v>14</v>
@@ -34934,19 +34934,19 @@
         <v>3.37</v>
       </c>
       <c r="AU158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV158" t="n">
         <v>2</v>
       </c>
       <c r="AW158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX158" t="n">
         <v>13</v>
       </c>
       <c r="AY158" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ158" t="n">
         <v>15</v>
@@ -35158,13 +35158,13 @@
         <v>3</v>
       </c>
       <c r="AW159" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX159" t="n">
         <v>11</v>
       </c>
       <c r="AY159" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ159" t="n">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -33629,13 +33629,13 @@
         <v>3</v>
       </c>
       <c r="AV152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW152" t="n">
         <v>14</v>
       </c>
       <c r="AX152" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY152" t="n">
         <v>17</v>
@@ -33844,13 +33844,13 @@
         <v>3.01</v>
       </c>
       <c r="AU153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV153" t="n">
         <v>6</v>
       </c>
       <c r="AW153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX153" t="n">
         <v>11</v>
@@ -33865,10 +33865,10 @@
         <v>2</v>
       </c>
       <c r="BB153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC153" t="n">
         <v>8</v>
-      </c>
-      <c r="BC153" t="n">
-        <v>10</v>
       </c>
       <c r="BD153" t="n">
         <v>3.9</v>
@@ -34065,13 +34065,13 @@
         <v>3</v>
       </c>
       <c r="AV154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW154" t="n">
         <v>16</v>
       </c>
       <c r="AX154" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY154" t="n">
         <v>19</v>
@@ -34280,13 +34280,13 @@
         <v>3.04</v>
       </c>
       <c r="AU155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV155" t="n">
         <v>6</v>
       </c>
       <c r="AW155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX155" t="n">
         <v>14</v>
@@ -34498,16 +34498,16 @@
         <v>3.81</v>
       </c>
       <c r="AU156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV156" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX156" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY156" t="n">
         <v>9</v>
@@ -34719,13 +34719,13 @@
         <v>2</v>
       </c>
       <c r="AV157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW157" t="n">
         <v>3</v>
       </c>
       <c r="AX157" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY157" t="n">
         <v>5</v>
@@ -34937,13 +34937,13 @@
         <v>3</v>
       </c>
       <c r="AV158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW158" t="n">
         <v>9</v>
       </c>
       <c r="AX158" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY158" t="n">
         <v>12</v>
@@ -35155,13 +35155,13 @@
         <v>7</v>
       </c>
       <c r="AV159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW159" t="n">
         <v>10</v>
       </c>
       <c r="AX159" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY159" t="n">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -33629,13 +33629,13 @@
         <v>3</v>
       </c>
       <c r="AV152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW152" t="n">
         <v>14</v>
       </c>
       <c r="AX152" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY152" t="n">
         <v>17</v>
@@ -33844,13 +33844,13 @@
         <v>3.01</v>
       </c>
       <c r="AU153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV153" t="n">
         <v>6</v>
       </c>
       <c r="AW153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX153" t="n">
         <v>11</v>
@@ -33865,10 +33865,10 @@
         <v>2</v>
       </c>
       <c r="BB153" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC153" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD153" t="n">
         <v>3.9</v>
@@ -34065,13 +34065,13 @@
         <v>3</v>
       </c>
       <c r="AV154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW154" t="n">
         <v>16</v>
       </c>
       <c r="AX154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY154" t="n">
         <v>19</v>
@@ -34280,13 +34280,13 @@
         <v>3.04</v>
       </c>
       <c r="AU155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV155" t="n">
         <v>6</v>
       </c>
       <c r="AW155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX155" t="n">
         <v>14</v>
@@ -34498,16 +34498,16 @@
         <v>3.81</v>
       </c>
       <c r="AU156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV156" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW156" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX156" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY156" t="n">
         <v>9</v>
@@ -34719,13 +34719,13 @@
         <v>2</v>
       </c>
       <c r="AV157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW157" t="n">
         <v>3</v>
       </c>
       <c r="AX157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY157" t="n">
         <v>5</v>
@@ -34937,13 +34937,13 @@
         <v>3</v>
       </c>
       <c r="AV158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW158" t="n">
         <v>9</v>
       </c>
       <c r="AX158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY158" t="n">
         <v>12</v>
@@ -35155,13 +35155,13 @@
         <v>7</v>
       </c>
       <c r="AV159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW159" t="n">
         <v>10</v>
       </c>
       <c r="AX159" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY159" t="n">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -34283,13 +34283,13 @@
         <v>5</v>
       </c>
       <c r="AV155" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW155" t="n">
         <v>2</v>
       </c>
       <c r="AX155" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY155" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -33844,13 +33844,13 @@
         <v>3.01</v>
       </c>
       <c r="AU153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV153" t="n">
         <v>6</v>
       </c>
       <c r="AW153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX153" t="n">
         <v>11</v>
@@ -33865,10 +33865,10 @@
         <v>2</v>
       </c>
       <c r="BB153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC153" t="n">
         <v>8</v>
-      </c>
-      <c r="BC153" t="n">
-        <v>10</v>
       </c>
       <c r="BD153" t="n">
         <v>3.9</v>
@@ -34065,13 +34065,13 @@
         <v>3</v>
       </c>
       <c r="AV154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW154" t="n">
         <v>16</v>
       </c>
       <c r="AX154" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY154" t="n">
         <v>19</v>
@@ -34280,16 +34280,16 @@
         <v>3.04</v>
       </c>
       <c r="AU155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV155" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX155" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY155" t="n">
         <v>7</v>
@@ -34498,16 +34498,16 @@
         <v>3.81</v>
       </c>
       <c r="AU156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV156" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX156" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY156" t="n">
         <v>9</v>
@@ -34719,13 +34719,13 @@
         <v>2</v>
       </c>
       <c r="AV157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW157" t="n">
         <v>3</v>
       </c>
       <c r="AX157" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY157" t="n">
         <v>5</v>
@@ -34937,13 +34937,13 @@
         <v>3</v>
       </c>
       <c r="AV158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW158" t="n">
         <v>9</v>
       </c>
       <c r="AX158" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY158" t="n">
         <v>12</v>
@@ -35155,13 +35155,13 @@
         <v>7</v>
       </c>
       <c r="AV159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW159" t="n">
         <v>10</v>
       </c>
       <c r="AX159" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY159" t="n">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -26067,7 +26067,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>7785291</v>
+        <v>7785289</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -26087,197 +26087,197 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L118" t="n">
+        <v>6</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>6</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>['8', '22', '39', '45', '67', '86']</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U118" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V118" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X118" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN118" t="n">
         <v>3</v>
       </c>
-      <c r="M118" t="n">
-        <v>1</v>
-      </c>
-      <c r="N118" t="n">
-        <v>4</v>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>['45+1', '55', '58']</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="Q118" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R118" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S118" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T118" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U118" t="n">
-        <v>3</v>
-      </c>
-      <c r="V118" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W118" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X118" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI118" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK118" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AL118" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM118" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN118" t="n">
-        <v>2</v>
-      </c>
       <c r="AO118" t="n">
-        <v>0.83</v>
+        <v>1.38</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="AS118" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.39</v>
+        <v>2.84</v>
       </c>
       <c r="AU118" t="n">
         <v>6</v>
       </c>
       <c r="AV118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX118" t="n">
         <v>6</v>
       </c>
-      <c r="AW118" t="n">
+      <c r="AY118" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB118" t="n">
         <v>7</v>
       </c>
-      <c r="AX118" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY118" t="n">
+      <c r="BC118" t="n">
         <v>13</v>
       </c>
-      <c r="AZ118" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA118" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB118" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>8</v>
-      </c>
       <c r="BD118" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BE118" t="n">
         <v>7</v>
       </c>
       <c r="BF118" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BG118" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BH118" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BI118" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BJ118" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="BK118" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="BL118" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BM118" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="BN118" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="BO118" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BP118" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="119">
@@ -26285,7 +26285,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>7785289</v>
+        <v>7785291</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -26305,197 +26305,197 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>3</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" t="n">
         <v>4</v>
       </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>4</v>
-      </c>
-      <c r="L119" t="n">
-        <v>6</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="n">
-        <v>6</v>
-      </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>['8', '22', '39', '45', '67', '86']</t>
+          <t>['45+1', '55', '58']</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R119" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T119" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="U119" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V119" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="W119" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="X119" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA119" t="n">
-        <v>3.69</v>
+        <v>3.29</v>
       </c>
       <c r="AB119" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD119" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AF119" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="AG119" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH119" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AI119" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AJ119" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL119" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM119" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AN119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO119" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.77</v>
+        <v>1.43</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.84</v>
+        <v>2.39</v>
       </c>
       <c r="AU119" t="n">
         <v>6</v>
       </c>
       <c r="AV119" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB119" t="n">
         <v>3</v>
       </c>
-      <c r="AW119" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX119" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY119" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ119" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA119" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB119" t="n">
-        <v>7</v>
-      </c>
       <c r="BC119" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BD119" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BE119" t="n">
         <v>7</v>
       </c>
       <c r="BF119" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BG119" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BH119" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BI119" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BJ119" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BK119" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="BL119" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="BM119" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="BN119" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BO119" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BP119" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="120">
@@ -33844,13 +33844,13 @@
         <v>3.01</v>
       </c>
       <c r="AU153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV153" t="n">
         <v>6</v>
       </c>
       <c r="AW153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX153" t="n">
         <v>11</v>
@@ -33865,10 +33865,10 @@
         <v>2</v>
       </c>
       <c r="BB153" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC153" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD153" t="n">
         <v>3.9</v>
@@ -34065,13 +34065,13 @@
         <v>3</v>
       </c>
       <c r="AV154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW154" t="n">
         <v>16</v>
       </c>
       <c r="AX154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY154" t="n">
         <v>19</v>
@@ -34280,16 +34280,16 @@
         <v>3.04</v>
       </c>
       <c r="AU155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV155" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX155" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY155" t="n">
         <v>7</v>
@@ -34498,16 +34498,16 @@
         <v>3.81</v>
       </c>
       <c r="AU156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV156" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW156" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX156" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY156" t="n">
         <v>9</v>
@@ -34719,13 +34719,13 @@
         <v>2</v>
       </c>
       <c r="AV157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW157" t="n">
         <v>3</v>
       </c>
       <c r="AX157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY157" t="n">
         <v>5</v>
@@ -34937,13 +34937,13 @@
         <v>3</v>
       </c>
       <c r="AV158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW158" t="n">
         <v>9</v>
       </c>
       <c r="AX158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY158" t="n">
         <v>12</v>
@@ -35152,19 +35152,19 @@
         <v>2.52</v>
       </c>
       <c r="AU159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW159" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX159" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY159" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ159" t="n">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.45</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
         <v>2.3</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.9</v>
@@ -2876,7 +2876,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR18" t="n">
         <v>0.79</v>
@@ -4620,7 +4620,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR19" t="n">
         <v>1.89</v>
@@ -4835,10 +4835,10 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR20" t="n">
         <v>1.69</v>
@@ -5056,7 +5056,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR21" t="n">
         <v>1.81</v>
@@ -5274,7 +5274,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR22" t="n">
         <v>1.57</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.1</v>
@@ -5928,7 +5928,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR25" t="n">
         <v>1.08</v>
@@ -6143,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR26" t="n">
         <v>1.18</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.45</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ28" t="n">
         <v>2.3</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.2</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.5</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR32" t="n">
         <v>1.39</v>
@@ -7672,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR33" t="n">
         <v>1.74</v>
@@ -8105,10 +8105,10 @@
         <v>1.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR35" t="n">
         <v>1.38</v>
@@ -8326,7 +8326,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR36" t="n">
         <v>1.87</v>
@@ -8762,7 +8762,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR38" t="n">
         <v>1.62</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.2</v>
@@ -9634,7 +9634,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR42" t="n">
         <v>1.77</v>
@@ -9852,7 +9852,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR43" t="n">
         <v>1.5</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.1</v>
@@ -10503,10 +10503,10 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR46" t="n">
         <v>1.82</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.1</v>
@@ -10939,10 +10939,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR48" t="n">
         <v>1.08</v>
@@ -11160,7 +11160,7 @@
         <v>1</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR49" t="n">
         <v>1.43</v>
@@ -11378,7 +11378,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR50" t="n">
         <v>2.03</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.9</v>
@@ -11811,10 +11811,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR52" t="n">
         <v>1.16</v>
@@ -12032,7 +12032,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR53" t="n">
         <v>2.42</v>
@@ -12683,10 +12683,10 @@
         <v>1.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR56" t="n">
         <v>1.55</v>
@@ -13119,7 +13119,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.45</v>
@@ -13773,10 +13773,10 @@
         <v>1.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR61" t="n">
         <v>1.17</v>
@@ -13991,10 +13991,10 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR62" t="n">
         <v>2</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.1</v>
@@ -14427,10 +14427,10 @@
         <v>1.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR64" t="n">
         <v>1.72</v>
@@ -14648,7 +14648,7 @@
         <v>1</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR65" t="n">
         <v>1.25</v>
@@ -14866,7 +14866,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR66" t="n">
         <v>1.82</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.7</v>
@@ -15299,10 +15299,10 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR68" t="n">
         <v>0.97</v>
@@ -15520,7 +15520,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR69" t="n">
         <v>0.97</v>
@@ -15735,10 +15735,10 @@
         <v>2.25</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ70" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR70" t="n">
         <v>1.96</v>
@@ -15953,7 +15953,7 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.1</v>
@@ -16392,7 +16392,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR73" t="n">
         <v>1.43</v>
@@ -16825,10 +16825,10 @@
         <v>1.67</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR75" t="n">
         <v>1.93</v>
@@ -17043,10 +17043,10 @@
         <v>0.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR76" t="n">
         <v>1.33</v>
@@ -17261,7 +17261,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ77" t="n">
         <v>2.3</v>
@@ -17697,10 +17697,10 @@
         <v>2.4</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ79" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR79" t="n">
         <v>1.48</v>
@@ -17915,7 +17915,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.7</v>
@@ -18572,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR83" t="n">
         <v>1.24</v>
@@ -18787,7 +18787,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.5</v>
@@ -19005,10 +19005,10 @@
         <v>1.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR85" t="n">
         <v>1.15</v>
@@ -19223,10 +19223,10 @@
         <v>1.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR86" t="n">
         <v>0.96</v>
@@ -19444,7 +19444,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR87" t="n">
         <v>2.35</v>
@@ -19662,7 +19662,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR88" t="n">
         <v>1.95</v>
@@ -19877,10 +19877,10 @@
         <v>1.43</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR89" t="n">
         <v>1.15</v>
@@ -20095,7 +20095,7 @@
         <v>1.8</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.45</v>
@@ -20313,7 +20313,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.9</v>
@@ -20534,7 +20534,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR92" t="n">
         <v>1.15</v>
@@ -20749,7 +20749,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.2</v>
@@ -20970,7 +20970,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR94" t="n">
         <v>1.63</v>
@@ -21185,10 +21185,10 @@
         <v>0.6</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR95" t="n">
         <v>1.89</v>
@@ -21403,7 +21403,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.7</v>
@@ -21624,7 +21624,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR97" t="n">
         <v>2.23</v>
@@ -21842,7 +21842,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR98" t="n">
         <v>1.97</v>
@@ -22496,7 +22496,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR101" t="n">
         <v>1.8</v>
@@ -22711,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.1</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5</v>
@@ -23147,10 +23147,10 @@
         <v>0.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR104" t="n">
         <v>2.14</v>
@@ -23583,10 +23583,10 @@
         <v>1.43</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR106" t="n">
         <v>1.44</v>
@@ -23801,7 +23801,7 @@
         <v>0.83</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.2</v>
@@ -24458,7 +24458,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR110" t="n">
         <v>1.44</v>
@@ -24673,10 +24673,10 @@
         <v>2.29</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR111" t="n">
         <v>1.99</v>
@@ -25109,10 +25109,10 @@
         <v>1.43</v>
       </c>
       <c r="AP113" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR113" t="n">
         <v>1.59</v>
@@ -25327,7 +25327,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.7</v>
@@ -25545,10 +25545,10 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR115" t="n">
         <v>1.39</v>
@@ -26202,7 +26202,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR118" t="n">
         <v>1.77</v>
@@ -26635,10 +26635,10 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR120" t="n">
         <v>1.19</v>
@@ -26856,7 +26856,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR121" t="n">
         <v>1.24</v>
@@ -27071,7 +27071,7 @@
         <v>0.71</v>
       </c>
       <c r="AP122" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.9</v>
@@ -27725,10 +27725,10 @@
         <v>1.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR125" t="n">
         <v>2.21</v>
@@ -27943,10 +27943,10 @@
         <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR126" t="n">
         <v>1.48</v>
@@ -28164,7 +28164,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR127" t="n">
         <v>1.79</v>
@@ -28379,10 +28379,10 @@
         <v>0.75</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR128" t="n">
         <v>2.3</v>
@@ -28600,7 +28600,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR129" t="n">
         <v>1.46</v>
@@ -28815,7 +28815,7 @@
         <v>1.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.7</v>
@@ -29033,7 +29033,7 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ131" t="n">
         <v>2.3</v>
@@ -29254,7 +29254,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR132" t="n">
         <v>2.11</v>
@@ -29687,7 +29687,7 @@
         <v>0.71</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.5</v>
@@ -29905,10 +29905,10 @@
         <v>1.38</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR135" t="n">
         <v>1.24</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.9</v>
@@ -30341,10 +30341,10 @@
         <v>2</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR137" t="n">
         <v>2.3</v>
@@ -30559,7 +30559,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.2</v>
@@ -30777,7 +30777,7 @@
         <v>1.63</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.45</v>
@@ -30998,7 +30998,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ140" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR140" t="n">
         <v>1.85</v>
@@ -31649,7 +31649,7 @@
         <v>0.63</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.5</v>
@@ -31867,7 +31867,7 @@
         <v>1.25</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.1</v>
@@ -32088,7 +32088,7 @@
         <v>1</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR145" t="n">
         <v>1.17</v>
@@ -32521,7 +32521,7 @@
         <v>0.89</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.9</v>
@@ -32739,10 +32739,10 @@
         <v>1.11</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR148" t="n">
         <v>1.15</v>
@@ -32957,10 +32957,10 @@
         <v>0.67</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR149" t="n">
         <v>1.39</v>
@@ -33175,10 +33175,10 @@
         <v>1.89</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -33393,10 +33393,10 @@
         <v>1.22</v>
       </c>
       <c r="AP151" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR151" t="n">
         <v>1.61</v>
@@ -34265,7 +34265,7 @@
         <v>1.3</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.45</v>
@@ -34922,7 +34922,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR158" t="n">
         <v>2.15</v>
@@ -35216,6 +35216,1750 @@
       </c>
       <c r="BP159" t="n">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>7785334</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45912.58333333334</v>
+      </c>
+      <c r="F160" t="n">
+        <v>21</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>3</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>3</v>
+      </c>
+      <c r="L160" t="n">
+        <v>7</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="n">
+        <v>8</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>['10', '40', '45', '66', '71', '77', '90']</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R160" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S160" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U160" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="V160" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W160" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X160" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>7785340</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45913.45833333334</v>
+      </c>
+      <c r="F161" t="n">
+        <v>21</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>2</v>
+      </c>
+      <c r="K161" t="n">
+        <v>2</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
+        <v>3</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['28', '45+6']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S161" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U161" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>7785335</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45913.54166666666</v>
+      </c>
+      <c r="F162" t="n">
+        <v>21</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>2</v>
+      </c>
+      <c r="L162" t="n">
+        <v>3</v>
+      </c>
+      <c r="M162" t="n">
+        <v>2</v>
+      </c>
+      <c r="N162" t="n">
+        <v>5</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['14', '57', '66']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>['8', '46']</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S162" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U162" t="n">
+        <v>4</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X162" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>7785336</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45914.39583333334</v>
+      </c>
+      <c r="F163" t="n">
+        <v>21</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>['9', '81']</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S163" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V163" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X163" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>7785337</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45914.5</v>
+      </c>
+      <c r="F164" t="n">
+        <v>21</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>3</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['59', '83']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S164" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U164" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X164" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>7785339</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45914.5</v>
+      </c>
+      <c r="F165" t="n">
+        <v>21</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>2</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>3</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="n">
+        <v>2</v>
+      </c>
+      <c r="N165" t="n">
+        <v>4</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>['1', '19']</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>['5', '73']</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S165" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U165" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="V165" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X165" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>7785341</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45914.5</v>
+      </c>
+      <c r="F166" t="n">
+        <v>21</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>2</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>2</v>
+      </c>
+      <c r="L166" t="n">
+        <v>2</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="n">
+        <v>3</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>['8', '28']</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S166" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U166" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X166" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>7785338</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45914.59375</v>
+      </c>
+      <c r="F167" t="n">
+        <v>21</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>2</v>
+      </c>
+      <c r="K167" t="n">
+        <v>2</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>3</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['4', '35', '59']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S167" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U167" t="n">
+        <v>4</v>
+      </c>
+      <c r="V167" t="n">
+        <v>2</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X167" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP167"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.27</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.7</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.09</v>
@@ -2004,7 +2004,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.11</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.18</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.27</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.27</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.27</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR23" t="n">
         <v>1.18</v>
@@ -5710,7 +5710,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR24" t="n">
         <v>1.25</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.4</v>
@@ -6364,7 +6364,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR27" t="n">
         <v>1.44</v>
@@ -6582,7 +6582,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR28" t="n">
         <v>1.22</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>1.86</v>
@@ -7018,7 +7018,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR30" t="n">
         <v>2.46</v>
@@ -7236,7 +7236,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR31" t="n">
         <v>1.65</v>
@@ -7669,7 +7669,7 @@
         <v>0.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.18</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR34" t="n">
         <v>2.36</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.82</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR37" t="n">
         <v>2.12</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.27</v>
@@ -8980,7 +8980,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR39" t="n">
         <v>1.09</v>
@@ -9195,10 +9195,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR40" t="n">
         <v>1.95</v>
@@ -9413,10 +9413,10 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR41" t="n">
         <v>2.52</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.4</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.27</v>
@@ -10070,7 +10070,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR44" t="n">
         <v>1.33</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR45" t="n">
         <v>2.14</v>
@@ -10724,7 +10724,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR47" t="n">
         <v>1.31</v>
@@ -11157,7 +11157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.11</v>
@@ -11375,7 +11375,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.18</v>
@@ -11596,7 +11596,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR51" t="n">
         <v>1.5</v>
@@ -12029,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.4</v>
@@ -12247,10 +12247,10 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR54" t="n">
         <v>1.48</v>
@@ -12465,10 +12465,10 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR55" t="n">
         <v>2.09</v>
@@ -12901,10 +12901,10 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR57" t="n">
         <v>1.64</v>
@@ -13122,7 +13122,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR58" t="n">
         <v>1.81</v>
@@ -13337,10 +13337,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR59" t="n">
         <v>1.03</v>
@@ -13555,10 +13555,10 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR60" t="n">
         <v>1.96</v>
@@ -14212,7 +14212,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR63" t="n">
         <v>1.17</v>
@@ -14645,7 +14645,7 @@
         <v>2</v>
       </c>
       <c r="AP65" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ65" t="n">
         <v>2.09</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.91</v>
@@ -15084,7 +15084,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR67" t="n">
         <v>1.22</v>
@@ -15517,7 +15517,7 @@
         <v>1.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.27</v>
@@ -15956,7 +15956,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR71" t="n">
         <v>1.86</v>
@@ -16171,10 +16171,10 @@
         <v>0.25</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR72" t="n">
         <v>1.5</v>
@@ -16389,7 +16389,7 @@
         <v>1.4</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.18</v>
@@ -16607,10 +16607,10 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR74" t="n">
         <v>0.99</v>
@@ -17264,7 +17264,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ77" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR77" t="n">
         <v>1.14</v>
@@ -17479,10 +17479,10 @@
         <v>0.25</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR78" t="n">
         <v>2.2</v>
@@ -17918,7 +17918,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR80" t="n">
         <v>1.87</v>
@@ -18133,10 +18133,10 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR81" t="n">
         <v>2.06</v>
@@ -18351,10 +18351,10 @@
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR82" t="n">
         <v>1.82</v>
@@ -18569,7 +18569,7 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.27</v>
@@ -18790,7 +18790,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR84" t="n">
         <v>1.61</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.11</v>
@@ -19659,7 +19659,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.09</v>
@@ -20098,7 +20098,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR90" t="n">
         <v>1.87</v>
@@ -20316,7 +20316,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR91" t="n">
         <v>1.37</v>
@@ -20531,7 +20531,7 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.82</v>
@@ -20752,7 +20752,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR93" t="n">
         <v>1.4</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.18</v>
@@ -21406,7 +21406,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR96" t="n">
         <v>1.2</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.91</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.11</v>
@@ -22057,10 +22057,10 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR99" t="n">
         <v>1.37</v>
@@ -22275,10 +22275,10 @@
         <v>1.67</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR100" t="n">
         <v>1.46</v>
@@ -22493,7 +22493,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.27</v>
@@ -22714,7 +22714,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR102" t="n">
         <v>1.49</v>
@@ -22932,7 +22932,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR103" t="n">
         <v>1.12</v>
@@ -23365,10 +23365,10 @@
         <v>1.43</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR105" t="n">
         <v>1.18</v>
@@ -23804,7 +23804,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR107" t="n">
         <v>1.15</v>
@@ -24019,10 +24019,10 @@
         <v>2</v>
       </c>
       <c r="AP108" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR108" t="n">
         <v>1.3</v>
@@ -24237,10 +24237,10 @@
         <v>0.83</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR109" t="n">
         <v>1.85</v>
@@ -24455,7 +24455,7 @@
         <v>2.17</v>
       </c>
       <c r="AP110" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.82</v>
@@ -24891,10 +24891,10 @@
         <v>1.6</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR112" t="n">
         <v>1.26</v>
@@ -25330,7 +25330,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR114" t="n">
         <v>1.24</v>
@@ -25763,10 +25763,10 @@
         <v>1.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR116" t="n">
         <v>2.25</v>
@@ -25981,10 +25981,10 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR117" t="n">
         <v>1.93</v>
@@ -26199,7 +26199,7 @@
         <v>1.38</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.27</v>
@@ -26417,10 +26417,10 @@
         <v>0.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR119" t="n">
         <v>1.43</v>
@@ -26853,7 +26853,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.91</v>
@@ -27074,7 +27074,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR122" t="n">
         <v>1.15</v>
@@ -27289,10 +27289,10 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR123" t="n">
         <v>1.22</v>
@@ -27507,10 +27507,10 @@
         <v>1.86</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR124" t="n">
         <v>1.77</v>
@@ -28161,7 +28161,7 @@
         <v>2.29</v>
       </c>
       <c r="AP127" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.82</v>
@@ -28597,7 +28597,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.11</v>
@@ -28818,7 +28818,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR130" t="n">
         <v>1.64</v>
@@ -29036,7 +29036,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR131" t="n">
         <v>1.19</v>
@@ -29251,7 +29251,7 @@
         <v>0.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.4</v>
@@ -29469,10 +29469,10 @@
         <v>0</v>
       </c>
       <c r="AP133" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR133" t="n">
         <v>1.4</v>
@@ -29690,7 +29690,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR134" t="n">
         <v>1.43</v>
@@ -30126,7 +30126,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR136" t="n">
         <v>1.48</v>
@@ -30562,7 +30562,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR138" t="n">
         <v>1.48</v>
@@ -30780,7 +30780,7 @@
         <v>0.45</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR139" t="n">
         <v>1.17</v>
@@ -30995,7 +30995,7 @@
         <v>2.11</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ140" t="n">
         <v>2.09</v>
@@ -31213,10 +31213,10 @@
         <v>2.13</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR141" t="n">
         <v>1.54</v>
@@ -31431,10 +31431,10 @@
         <v>1.63</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR142" t="n">
         <v>1.45</v>
@@ -31652,7 +31652,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR143" t="n">
         <v>1.17</v>
@@ -31870,7 +31870,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR144" t="n">
         <v>1.28</v>
@@ -32085,7 +32085,7 @@
         <v>0.38</v>
       </c>
       <c r="AP145" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.4</v>
@@ -32303,10 +32303,10 @@
         <v>1.44</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR146" t="n">
         <v>2.05</v>
@@ -32524,7 +32524,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR147" t="n">
         <v>1.34</v>
@@ -33611,10 +33611,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR152" t="n">
         <v>2.07</v>
@@ -33829,10 +33829,10 @@
         <v>1.78</v>
       </c>
       <c r="AP153" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR153" t="n">
         <v>1.24</v>
@@ -34047,10 +34047,10 @@
         <v>0</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR154" t="n">
         <v>1.34</v>
@@ -34268,7 +34268,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR155" t="n">
         <v>1.19</v>
@@ -34483,10 +34483,10 @@
         <v>2.22</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ156" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AR156" t="n">
         <v>1.74</v>
@@ -34701,10 +34701,10 @@
         <v>1.33</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR157" t="n">
         <v>1.44</v>
@@ -34919,7 +34919,7 @@
         <v>1.22</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.27</v>
@@ -35137,10 +35137,10 @@
         <v>1.22</v>
       </c>
       <c r="AP159" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR159" t="n">
         <v>1.39</v>
@@ -36960,6 +36960,1750 @@
       </c>
       <c r="BP167" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>7785342</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45920.375</v>
+      </c>
+      <c r="F168" t="n">
+        <v>22</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>2</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R168" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S168" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V168" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X168" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>7785345</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45920.45833333334</v>
+      </c>
+      <c r="F169" t="n">
+        <v>22</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>3</v>
+      </c>
+      <c r="N169" t="n">
+        <v>3</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>['13', '56', '66']</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S169" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U169" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V169" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X169" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>7785349</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45920.54166666666</v>
+      </c>
+      <c r="F170" t="n">
+        <v>22</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>['90+7']</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S170" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V170" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X170" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>7785344</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45921.39583333334</v>
+      </c>
+      <c r="F171" t="n">
+        <v>22</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>4</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S171" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U171" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X171" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>7785343</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45921.5</v>
+      </c>
+      <c r="F172" t="n">
+        <v>22</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['17', '71']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S172" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X172" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>7785346</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45921.5</v>
+      </c>
+      <c r="F173" t="n">
+        <v>22</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>2</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2</v>
+      </c>
+      <c r="M173" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" t="n">
+        <v>3</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>['10', '60']</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S173" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U173" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V173" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X173" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>7785347</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45921.5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>22</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>2</v>
+      </c>
+      <c r="R174" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S174" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U174" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V174" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X174" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>7785348</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45921.59375</v>
+      </c>
+      <c r="F175" t="n">
+        <v>22</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U175" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X175" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3748,7 +3748,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.17</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.15</v>
@@ -7454,7 +7454,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR32" t="n">
         <v>1.72</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.67</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.08</v>
@@ -9631,7 +9631,7 @@
         <v>3</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.46</v>
@@ -10288,7 +10288,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR45" t="n">
         <v>2.05</v>
@@ -12468,7 +12468,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR55" t="n">
         <v>1.66</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.83</v>
@@ -19008,7 +19008,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR85" t="n">
         <v>1.77</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.08</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.83</v>
@@ -22714,7 +22714,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR102" t="n">
         <v>1.22</v>
@@ -25763,7 +25763,7 @@
         <v>1.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ116" t="n">
         <v>2.25</v>
@@ -26420,7 +26420,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR119" t="n">
         <v>1.56</v>
@@ -29908,7 +29908,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR135" t="n">
         <v>1.54</v>
@@ -31870,7 +31870,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR144" t="n">
         <v>1.2</v>
@@ -33614,7 +33614,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR152" t="n">
         <v>2.06</v>
@@ -34701,7 +34701,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.15</v>
@@ -37102,7 +37102,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR168" t="n">
         <v>1.42</v>
@@ -38625,7 +38625,7 @@
         <v>1.1</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.92</v>
@@ -40808,7 +40808,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR185" t="n">
         <v>1.59</v>
@@ -41241,7 +41241,7 @@
         <v>1.82</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.67</v>
@@ -43936,6 +43936,224 @@
       </c>
       <c r="BP199" t="n">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>8306761</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45955.45833333334</v>
+      </c>
+      <c r="F200" t="n">
+        <v>26</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>2</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>2</v>
+      </c>
+      <c r="L200" t="n">
+        <v>5</v>
+      </c>
+      <c r="M200" t="n">
+        <v>1</v>
+      </c>
+      <c r="N200" t="n">
+        <v>6</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>['21', '45+1', '54', '62', '89']</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S200" t="n">
+        <v>7</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U200" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V200" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X200" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ14" t="n">
         <v>1</v>
@@ -4184,7 +4184,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.83</v>
@@ -7890,7 +7890,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR34" t="n">
         <v>2.73</v>
@@ -8980,7 +8980,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.83</v>
@@ -12686,7 +12686,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR56" t="n">
         <v>1.17</v>
@@ -14645,7 +14645,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.67</v>
@@ -17482,7 +17482,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR78" t="n">
         <v>2.11</v>
@@ -19005,7 +19005,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.46</v>
@@ -20752,7 +20752,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR93" t="n">
         <v>1.58</v>
@@ -22929,7 +22929,7 @@
         <v>0</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.08</v>
@@ -23804,7 +23804,7 @@
         <v>0.42</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR107" t="n">
         <v>1.13</v>
@@ -25109,7 +25109,7 @@
         <v>1.43</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.15</v>
@@ -27292,7 +27292,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR123" t="n">
         <v>1.28</v>
@@ -28815,7 +28815,7 @@
         <v>1.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.67</v>
@@ -30562,7 +30562,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR138" t="n">
         <v>1.54</v>
@@ -33393,7 +33393,7 @@
         <v>1.22</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.15</v>
@@ -34486,7 +34486,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR156" t="n">
         <v>1.54</v>
@@ -36445,7 +36445,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.83</v>
@@ -37538,7 +37538,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR170" t="n">
         <v>2.03</v>
@@ -38843,7 +38843,7 @@
         <v>2.09</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ176" t="n">
         <v>2.08</v>
@@ -41462,7 +41462,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR188" t="n">
         <v>1.51</v>
@@ -42331,7 +42331,7 @@
         <v>2.18</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ192" t="n">
         <v>2.25</v>
@@ -44154,6 +44154,224 @@
       </c>
       <c r="BP200" t="n">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>8306788</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45955.54166666666</v>
+      </c>
+      <c r="F201" t="n">
+        <v>26</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>2</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>2</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>3</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>['7', '20']</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S201" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U201" t="n">
+        <v>3</v>
+      </c>
+      <c r="V201" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X201" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -44090,7 +44090,7 @@
         <v>3.14</v>
       </c>
       <c r="AU200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV200" t="n">
         <v>3</v>
@@ -44102,7 +44102,7 @@
         <v>6</v>
       </c>
       <c r="AY200" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ200" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.08</v>
@@ -3094,7 +3094,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.46</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.83</v>
@@ -5710,7 +5710,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR24" t="n">
         <v>1.24</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR29" t="n">
         <v>1.92</v>
@@ -7233,7 +7233,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
@@ -7669,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
         <v>1.67</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.08</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.08</v>
@@ -8326,7 +8326,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR36" t="n">
         <v>1.91</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.15</v>
@@ -9198,7 +9198,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR40" t="n">
         <v>1.88</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.46</v>
@@ -10724,7 +10724,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR47" t="n">
         <v>1.08</v>
@@ -10942,7 +10942,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR48" t="n">
         <v>1.78</v>
@@ -11157,7 +11157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.08</v>
@@ -11378,7 +11378,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR50" t="n">
         <v>1.34</v>
@@ -11593,7 +11593,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ51" t="n">
         <v>1</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ52" t="n">
         <v>2.08</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.08</v>
@@ -13558,7 +13558,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR60" t="n">
         <v>1.96</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.15</v>
@@ -14212,7 +14212,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR63" t="n">
         <v>1.12</v>
@@ -14427,7 +14427,7 @@
         <v>2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ64" t="n">
         <v>2.08</v>
@@ -14648,7 +14648,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR65" t="n">
         <v>1.86</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.83</v>
@@ -15081,10 +15081,10 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR67" t="n">
         <v>1.13</v>
@@ -15735,7 +15735,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.08</v>
@@ -15956,7 +15956,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR71" t="n">
         <v>1.86</v>
@@ -16174,7 +16174,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR72" t="n">
         <v>1.75</v>
@@ -17261,7 +17261,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ77" t="n">
         <v>2.25</v>
@@ -17479,7 +17479,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.08</v>
@@ -17915,10 +17915,10 @@
         <v>2.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR80" t="n">
         <v>2.06</v>
@@ -18136,7 +18136,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR81" t="n">
         <v>2.04</v>
@@ -18569,7 +18569,7 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.15</v>
@@ -18787,7 +18787,7 @@
         <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.08</v>
@@ -19226,7 +19226,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR86" t="n">
         <v>1.23</v>
@@ -19659,7 +19659,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.08</v>
@@ -19877,7 +19877,7 @@
         <v>1.43</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.15</v>
@@ -20098,7 +20098,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR90" t="n">
         <v>1.47</v>
@@ -20313,7 +20313,7 @@
         <v>1.8</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.46</v>
@@ -20534,7 +20534,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR92" t="n">
         <v>1.2</v>
@@ -21406,7 +21406,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR96" t="n">
         <v>1.25</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ99" t="n">
         <v>2.25</v>
@@ -22278,7 +22278,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR100" t="n">
         <v>1.6</v>
@@ -22493,7 +22493,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.15</v>
@@ -23147,7 +23147,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.83</v>
@@ -23368,7 +23368,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR105" t="n">
         <v>1.24</v>
@@ -23801,7 +23801,7 @@
         <v>0.83</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.08</v>
@@ -24022,7 +24022,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR108" t="n">
         <v>1.59</v>
@@ -24237,7 +24237,7 @@
         <v>2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.46</v>
@@ -24455,10 +24455,10 @@
         <v>0.83</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR110" t="n">
         <v>1.79</v>
@@ -25330,7 +25330,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR114" t="n">
         <v>1.32</v>
@@ -26199,7 +26199,7 @@
         <v>1.38</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.15</v>
@@ -27071,7 +27071,7 @@
         <v>1.86</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.46</v>
@@ -27289,7 +27289,7 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.08</v>
@@ -27507,10 +27507,10 @@
         <v>0.71</v>
       </c>
       <c r="AP124" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR124" t="n">
         <v>1.14</v>
@@ -27725,7 +27725,7 @@
         <v>1.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ125" t="n">
         <v>1</v>
@@ -27943,10 +27943,10 @@
         <v>2.29</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR126" t="n">
         <v>1.74</v>
@@ -28379,7 +28379,7 @@
         <v>0.75</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.83</v>
@@ -28818,7 +28818,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR130" t="n">
         <v>1.75</v>
@@ -30126,7 +30126,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR136" t="n">
         <v>1.59</v>
@@ -30341,10 +30341,10 @@
         <v>2</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR137" t="n">
         <v>2.4</v>
@@ -30777,7 +30777,7 @@
         <v>1.63</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.46</v>
@@ -30995,7 +30995,7 @@
         <v>2.11</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ140" t="n">
         <v>2.08</v>
@@ -31434,7 +31434,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR142" t="n">
         <v>1.56</v>
@@ -31652,7 +31652,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR143" t="n">
         <v>1.32</v>
@@ -32085,7 +32085,7 @@
         <v>0.38</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.83</v>
@@ -32524,7 +32524,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR147" t="n">
         <v>1.38</v>
@@ -32739,7 +32739,7 @@
         <v>1.11</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ148" t="n">
         <v>1</v>
@@ -33178,7 +33178,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR150" t="n">
         <v>1.67</v>
@@ -33829,10 +33829,10 @@
         <v>1.78</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR153" t="n">
         <v>1.28</v>
@@ -34265,7 +34265,7 @@
         <v>2.22</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ155" t="n">
         <v>2.25</v>
@@ -35140,7 +35140,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR159" t="n">
         <v>1.49</v>
@@ -35355,7 +35355,7 @@
         <v>1.4</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.15</v>
@@ -36012,7 +36012,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR163" t="n">
         <v>1.56</v>
@@ -36881,7 +36881,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.15</v>
@@ -37317,10 +37317,10 @@
         <v>1.7</v>
       </c>
       <c r="AP169" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR169" t="n">
         <v>1.61</v>
@@ -37753,7 +37753,7 @@
         <v>2.3</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ171" t="n">
         <v>2.25</v>
@@ -37974,7 +37974,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR172" t="n">
         <v>1.48</v>
@@ -38407,7 +38407,7 @@
         <v>0.1</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.08</v>
@@ -38628,7 +38628,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR175" t="n">
         <v>2.08</v>
@@ -40151,7 +40151,7 @@
         <v>0.4</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.83</v>
@@ -40590,7 +40590,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR184" t="n">
         <v>1.92</v>
@@ -40805,7 +40805,7 @@
         <v>0.55</v>
       </c>
       <c r="AP185" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.46</v>
@@ -41023,10 +41023,10 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR186" t="n">
         <v>1.34</v>
@@ -41244,7 +41244,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR187" t="n">
         <v>2.14</v>
@@ -41677,7 +41677,7 @@
         <v>0.09</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.08</v>
@@ -41898,7 +41898,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR190" t="n">
         <v>1.41</v>
@@ -42113,7 +42113,7 @@
         <v>1.33</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.46</v>
@@ -44317,13 +44317,13 @@
         <v>2</v>
       </c>
       <c r="AX201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY201" t="n">
         <v>7</v>
       </c>
       <c r="AZ201" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA201" t="n">
         <v>2</v>
@@ -44372,6 +44372,1096 @@
       </c>
       <c r="BP201" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>8306714</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>45956.4375</v>
+      </c>
+      <c r="F202" t="n">
+        <v>26</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>2</v>
+      </c>
+      <c r="K202" t="n">
+        <v>3</v>
+      </c>
+      <c r="L202" t="n">
+        <v>2</v>
+      </c>
+      <c r="M202" t="n">
+        <v>3</v>
+      </c>
+      <c r="N202" t="n">
+        <v>5</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>['45+2', '52']</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>['20', '42', '78']</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S202" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U202" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V202" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X202" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>8306760</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45956.54166666666</v>
+      </c>
+      <c r="F203" t="n">
+        <v>26</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S203" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V203" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X203" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>8306759</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45956.54166666666</v>
+      </c>
+      <c r="F204" t="n">
+        <v>26</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>3</v>
+      </c>
+      <c r="N204" t="n">
+        <v>4</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>['64', '72', '77']</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S204" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U204" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X204" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>8306758</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45956.54166666666</v>
+      </c>
+      <c r="F205" t="n">
+        <v>26</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>2</v>
+      </c>
+      <c r="J205" t="n">
+        <v>2</v>
+      </c>
+      <c r="K205" t="n">
+        <v>4</v>
+      </c>
+      <c r="L205" t="n">
+        <v>2</v>
+      </c>
+      <c r="M205" t="n">
+        <v>3</v>
+      </c>
+      <c r="N205" t="n">
+        <v>5</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>['23', '43']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['21', '36', '51']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>9</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S205" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U205" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X205" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8306748</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45956.54166666666</v>
+      </c>
+      <c r="F206" t="n">
+        <v>26</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>2</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
+        <v>3</v>
+      </c>
+      <c r="L206" t="n">
+        <v>4</v>
+      </c>
+      <c r="M206" t="n">
+        <v>1</v>
+      </c>
+      <c r="N206" t="n">
+        <v>5</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['15', '38', '65', '83']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S206" t="n">
+        <v>7</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U206" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V206" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X206" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.08</v>
@@ -3966,7 +3966,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR20" t="n">
         <v>1.69</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.15</v>
@@ -7018,7 +7018,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR30" t="n">
         <v>1.62</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.77</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -14866,7 +14866,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR66" t="n">
         <v>1.54</v>
@@ -18133,7 +18133,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.85</v>
@@ -18354,7 +18354,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR82" t="n">
         <v>1.05</v>
@@ -21624,7 +21624,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR97" t="n">
         <v>2.24</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.08</v>
@@ -25548,7 +25548,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR115" t="n">
         <v>1.53</v>
@@ -25981,7 +25981,7 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.08</v>
@@ -26856,7 +26856,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR121" t="n">
         <v>1.28</v>
@@ -28382,7 +28382,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR128" t="n">
         <v>2.42</v>
@@ -29251,7 +29251,7 @@
         <v>0.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.83</v>
@@ -32303,7 +32303,7 @@
         <v>1.44</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.46</v>
@@ -32960,7 +32960,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR149" t="n">
         <v>1.46</v>
@@ -33611,7 +33611,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.46</v>
@@ -36666,7 +36666,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR166" t="n">
         <v>1.24</v>
@@ -37535,7 +37535,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.08</v>
@@ -39282,7 +39282,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR178" t="n">
         <v>1.48</v>
@@ -40587,7 +40587,7 @@
         <v>1.82</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.77</v>
@@ -45416,13 +45416,13 @@
         <v>6</v>
       </c>
       <c r="BA206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB206" t="n">
         <v>1</v>
       </c>
       <c r="BC206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD206" t="n">
         <v>1.11</v>
@@ -45462,6 +45462,224 @@
       </c>
       <c r="BP206" t="n">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>8306715</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45956.63541666666</v>
+      </c>
+      <c r="F207" t="n">
+        <v>26</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="n">
+        <v>1</v>
+      </c>
+      <c r="N207" t="n">
+        <v>3</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>['90+1', '90+7']</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="R207" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S207" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U207" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V207" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X207" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -45416,13 +45416,13 @@
         <v>6</v>
       </c>
       <c r="BA206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC206" t="n">
         <v>3</v>
-      </c>
-      <c r="BB206" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC206" t="n">
-        <v>4</v>
       </c>
       <c r="BD206" t="n">
         <v>1.11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -44750,16 +44750,16 @@
         <v>5</v>
       </c>
       <c r="AW203" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ203" t="n">
         <v>8</v>
-      </c>
-      <c r="AX203" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY203" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ203" t="n">
-        <v>9</v>
       </c>
       <c r="BA203" t="n">
         <v>5</v>
@@ -44971,13 +44971,13 @@
         <v>12</v>
       </c>
       <c r="AX204" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY204" t="n">
         <v>17</v>
       </c>
       <c r="AZ204" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA204" t="n">
         <v>5</v>
@@ -45398,13 +45398,13 @@
         <v>3.76</v>
       </c>
       <c r="AU206" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV206" t="n">
         <v>2</v>
       </c>
       <c r="AW206" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX206" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -44597,7 +44597,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>8306760</v>
+        <v>8306758</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -44617,197 +44617,197 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K203" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '43']</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '36', '51']</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>2.51</v>
+        <v>9</v>
       </c>
       <c r="R203" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S203" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="T203" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="U203" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="V203" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="W203" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="X203" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y203" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z203" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AG203" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA203" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB203" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC203" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD203" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE203" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF203" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AG203" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH203" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AI203" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="AJ203" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
       <c r="AK203" t="n">
-        <v>1.29</v>
+        <v>3.46</v>
       </c>
       <c r="AL203" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AM203" t="n">
-        <v>1.8</v>
+        <v>1.05</v>
       </c>
       <c r="AN203" t="n">
-        <v>2.25</v>
+        <v>0.42</v>
       </c>
       <c r="AO203" t="n">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.15</v>
+        <v>0.38</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.87</v>
+        <v>2.27</v>
       </c>
       <c r="AU203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV203" t="n">
         <v>5</v>
       </c>
       <c r="AW203" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX203" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA203" t="n">
         <v>3</v>
       </c>
-      <c r="AY203" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ203" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA203" t="n">
+      <c r="BB203" t="n">
         <v>5</v>
-      </c>
-      <c r="BB203" t="n">
-        <v>3</v>
       </c>
       <c r="BC203" t="n">
         <v>8</v>
       </c>
       <c r="BD203" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE203" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF203" t="n">
-        <v>2.35</v>
+        <v>1.27</v>
       </c>
       <c r="BG203" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BH203" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="BI203" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BJ203" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="BK203" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL203" t="n">
         <v>1.77</v>
       </c>
-      <c r="BL203" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BM203" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="BN203" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO203" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BP203" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="204">
@@ -44815,7 +44815,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>8306759</v>
+        <v>8306760</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -44835,12 +44835,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -44853,179 +44853,179 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>['64', '72', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="R204" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S204" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U204" t="n">
         <v>3.4</v>
-      </c>
-      <c r="T204" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U204" t="n">
-        <v>3.2</v>
       </c>
       <c r="V204" t="n">
         <v>2.45</v>
       </c>
       <c r="W204" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X204" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="Y204" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z204" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP204" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA204" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB204" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AC204" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD204" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE204" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF204" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AG204" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH204" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI204" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AJ204" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK204" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AL204" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM204" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AN204" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO204" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP204" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AQ204" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="AU204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV204" t="n">
         <v>5</v>
       </c>
-      <c r="AV204" t="n">
-        <v>6</v>
-      </c>
       <c r="AW204" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY204" t="n">
         <v>12</v>
       </c>
-      <c r="AX204" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY204" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ204" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA204" t="n">
         <v>5</v>
       </c>
       <c r="BB204" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC204" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BD204" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="BE204" t="n">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF204" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="BG204" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BH204" t="n">
-        <v>4.85</v>
+        <v>3.58</v>
       </c>
       <c r="BI204" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="BJ204" t="n">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="BK204" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BL204" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="BM204" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="BN204" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="BO204" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="BP204" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="205">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>8306758</v>
+        <v>8306748</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,197 +45053,197 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="I205" t="n">
         <v>2</v>
       </c>
       <c r="J205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K205" t="n">
+        <v>3</v>
+      </c>
+      <c r="L205" t="n">
         <v>4</v>
       </c>
-      <c r="L205" t="n">
-        <v>2</v>
-      </c>
       <c r="M205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N205" t="n">
         <v>5</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>['23', '43']</t>
+          <t>['15', '38', '65', '83']</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>['21', '36', '51']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="Q205" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S205" t="n">
+        <v>7</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U205" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V205" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X205" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW205" t="n">
         <v>9</v>
       </c>
-      <c r="R205" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S205" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T205" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U205" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V205" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W205" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X205" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Y205" t="n">
+      <c r="AX205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG205" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z205" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD205" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE205" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF205" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AG205" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH205" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI205" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AJ205" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK205" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AL205" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AM205" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN205" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AO205" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP205" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AQ205" t="n">
+      <c r="BH205" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BM205" t="n">
         <v>1.77</v>
       </c>
-      <c r="AR205" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS205" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT205" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AU205" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV205" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW205" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX205" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY205" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ205" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA205" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB205" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC205" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD205" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF205" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BG205" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH205" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BI205" t="n">
+      <c r="BN205" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BP205" t="n">
         <v>1.57</v>
-      </c>
-      <c r="BJ205" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BK205" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BL205" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM205" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BN205" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BO205" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP205" t="n">
-        <v>1.26</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>8306748</v>
+        <v>8306759</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="n">
         <v>3</v>
       </c>
-      <c r="L206" t="n">
+      <c r="N206" t="n">
         <v>4</v>
       </c>
-      <c r="M206" t="n">
-        <v>1</v>
-      </c>
-      <c r="N206" t="n">
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>['64', '72', '77']</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S206" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U206" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V206" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X206" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU206" t="n">
         <v>5</v>
       </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>['15', '38', '65', '83']</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="Q206" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R206" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="S206" t="n">
+      <c r="AV206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB206" t="n">
         <v>7</v>
       </c>
-      <c r="T206" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U206" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V206" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W206" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X206" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y206" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z206" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA206" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD206" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE206" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH206" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI206" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN206" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO206" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP206" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ206" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AR206" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS206" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT206" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU206" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV206" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW206" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX206" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ206" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA206" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB206" t="n">
-        <v>1</v>
-      </c>
       <c r="BC206" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BD206" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="BE206" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF206" t="n">
-        <v>6.4</v>
+        <v>2.12</v>
       </c>
       <c r="BG206" t="n">
         <v>1.15</v>
       </c>
       <c r="BH206" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="BI206" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BJ206" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="BL206" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BM206" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BO206" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="207">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -44597,7 +44597,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>8306758</v>
+        <v>8306760</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -44617,197 +44617,197 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S203" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V203" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X203" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU203" t="n">
         <v>4</v>
-      </c>
-      <c r="L203" t="n">
-        <v>2</v>
-      </c>
-      <c r="M203" t="n">
-        <v>3</v>
-      </c>
-      <c r="N203" t="n">
-        <v>5</v>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>['23', '43']</t>
-        </is>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>['21', '36', '51']</t>
-        </is>
-      </c>
-      <c r="Q203" t="n">
-        <v>9</v>
-      </c>
-      <c r="R203" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S203" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T203" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U203" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="V203" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W203" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X203" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Y203" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z203" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA203" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB203" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC203" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD203" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE203" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF203" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AG203" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH203" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI203" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AJ203" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK203" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AL203" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AM203" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AN203" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AO203" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP203" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AQ203" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR203" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS203" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT203" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AU203" t="n">
-        <v>3</v>
       </c>
       <c r="AV203" t="n">
         <v>5</v>
       </c>
       <c r="AW203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA203" t="n">
         <v>5</v>
       </c>
-      <c r="AX203" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY203" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ203" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA203" t="n">
+      <c r="BB203" t="n">
         <v>3</v>
-      </c>
-      <c r="BB203" t="n">
-        <v>5</v>
       </c>
       <c r="BC203" t="n">
         <v>8</v>
       </c>
       <c r="BD203" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="BE203" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF203" t="n">
-        <v>1.27</v>
+        <v>2.35</v>
       </c>
       <c r="BG203" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH203" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="BI203" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="BJ203" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="BK203" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="BL203" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="BM203" t="n">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="BN203" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BO203" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="BP203" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="204">
@@ -44815,7 +44815,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>8306760</v>
+        <v>8306759</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -44835,12 +44835,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -44853,179 +44853,179 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64', '72', '77']</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="R204" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S204" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T204" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U204" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V204" t="n">
         <v>2.45</v>
       </c>
       <c r="W204" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X204" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="Y204" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z204" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AA204" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AB204" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="AC204" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD204" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AE204" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF204" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="AG204" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AH204" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AI204" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AJ204" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AK204" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL204" t="n">
         <v>1.29</v>
       </c>
-      <c r="AL204" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AM204" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AN204" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO204" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AP204" t="n">
-        <v>2.15</v>
+        <v>1.23</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="AU204" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW204" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX204" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AY204" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ204" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BA204" t="n">
         <v>5</v>
       </c>
       <c r="BB204" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BC204" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD204" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BE204" t="n">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF204" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="BG204" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="BH204" t="n">
-        <v>3.58</v>
+        <v>4.85</v>
       </c>
       <c r="BI204" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="BJ204" t="n">
-        <v>2.6</v>
+        <v>3.28</v>
       </c>
       <c r="BK204" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BL204" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="BM204" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="BN204" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="BO204" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="BP204" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="205">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>8306748</v>
+        <v>8306758</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,197 +45053,197 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="I205" t="n">
         <v>2</v>
       </c>
       <c r="J205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K205" t="n">
+        <v>4</v>
+      </c>
+      <c r="L205" t="n">
+        <v>2</v>
+      </c>
+      <c r="M205" t="n">
         <v>3</v>
-      </c>
-      <c r="L205" t="n">
-        <v>4</v>
-      </c>
-      <c r="M205" t="n">
-        <v>1</v>
       </c>
       <c r="N205" t="n">
         <v>5</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>['15', '38', '65', '83']</t>
+          <t>['23', '43']</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['21', '36', '51']</t>
         </is>
       </c>
       <c r="Q205" t="n">
+        <v>9</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S205" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U205" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X205" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AO205" t="n">
         <v>1.67</v>
       </c>
-      <c r="R205" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="S205" t="n">
-        <v>7</v>
-      </c>
-      <c r="T205" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U205" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V205" t="n">
+      <c r="AP205" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK205" t="n">
         <v>1.85</v>
       </c>
-      <c r="W205" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X205" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y205" t="n">
+      <c r="BL205" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP205" t="n">
         <v>1.26</v>
-      </c>
-      <c r="Z205" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD205" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE205" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF205" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG205" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH205" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI205" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AJ205" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AK205" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AL205" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AM205" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN205" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO205" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP205" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ205" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AR205" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AS205" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT205" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU205" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV205" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW205" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX205" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY205" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ205" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA205" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB205" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC205" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD205" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF205" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG205" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BH205" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI205" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BJ205" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BK205" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BL205" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BM205" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BN205" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BO205" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BP205" t="n">
-        <v>1.57</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>8306759</v>
+        <v>8306748</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L206" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M206" t="n">
+        <v>1</v>
+      </c>
+      <c r="N206" t="n">
+        <v>5</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['15', '38', '65', '83']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="S206" t="n">
+        <v>7</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U206" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V206" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X206" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC206" t="n">
         <v>3</v>
       </c>
-      <c r="N206" t="n">
-        <v>4</v>
-      </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>['64', '72', '77']</t>
-        </is>
-      </c>
-      <c r="Q206" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R206" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S206" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T206" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U206" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V206" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="W206" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X206" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y206" t="n">
+      <c r="BD206" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z206" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA206" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD206" t="n">
+      <c r="BE206" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE206" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH206" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI206" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AN206" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO206" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP206" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ206" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR206" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS206" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT206" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU206" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV206" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW206" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX206" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ206" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA206" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB206" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC206" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD206" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BE206" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="BF206" t="n">
-        <v>2.12</v>
+        <v>6.4</v>
       </c>
       <c r="BG206" t="n">
         <v>1.15</v>
       </c>
       <c r="BH206" t="n">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="BI206" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BJ206" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="BL206" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="BM206" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="BO206" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="207">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.77</v>
@@ -4835,7 +4835,7 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.77</v>
@@ -6582,7 +6582,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR28" t="n">
         <v>1.29</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.46</v>
@@ -10503,7 +10503,7 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.15</v>
@@ -12032,7 +12032,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ53" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR53" t="n">
         <v>1.7</v>
@@ -13337,7 +13337,7 @@
         <v>2.33</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.46</v>
@@ -15953,7 +15953,7 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.85</v>
@@ -17043,7 +17043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.15</v>
@@ -17264,7 +17264,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ77" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR77" t="n">
         <v>1.1</v>
@@ -21185,7 +21185,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.83</v>
@@ -22060,7 +22060,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR99" t="n">
         <v>1.45</v>
@@ -24673,7 +24673,7 @@
         <v>2.29</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ111" t="n">
         <v>2.08</v>
@@ -24894,7 +24894,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR112" t="n">
         <v>1.3</v>
@@ -25766,7 +25766,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR116" t="n">
         <v>2.26</v>
@@ -29036,7 +29036,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR131" t="n">
         <v>1.23</v>
@@ -31216,7 +31216,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -34268,7 +34268,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ155" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -35791,7 +35791,7 @@
         <v>1.3</v>
       </c>
       <c r="AP162" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ162" t="n">
         <v>1</v>
@@ -37756,7 +37756,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ171" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR171" t="n">
         <v>1.69</v>
@@ -39061,7 +39061,7 @@
         <v>1.11</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.08</v>
@@ -42334,7 +42334,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ192" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR192" t="n">
         <v>1.56</v>
@@ -42767,7 +42767,7 @@
         <v>0.08</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.08</v>
@@ -45680,6 +45680,224 @@
       </c>
       <c r="BP207" t="n">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>8306709</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45959.625</v>
+      </c>
+      <c r="F208" t="n">
+        <v>23</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>2</v>
+      </c>
+      <c r="N208" t="n">
+        <v>3</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>['76', '86']</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R208" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S208" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U208" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="V208" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X208" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.08</v>
@@ -5928,7 +5928,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR25" t="n">
         <v>1.26</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.85</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.15</v>
@@ -10070,7 +10070,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR44" t="n">
         <v>2.09</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.46</v>
@@ -12904,7 +12904,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR57" t="n">
         <v>2.42</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.08</v>
@@ -16828,7 +16828,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR75" t="n">
         <v>1.46</v>
@@ -17479,7 +17479,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.08</v>
@@ -19659,7 +19659,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.08</v>
@@ -21188,7 +21188,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR95" t="n">
         <v>1.89</v>
@@ -23150,7 +23150,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR104" t="n">
         <v>2.3</v>
@@ -24455,7 +24455,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ110" t="n">
         <v>1</v>
@@ -27943,7 +27943,7 @@
         <v>2.29</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.77</v>
@@ -29254,7 +29254,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR132" t="n">
         <v>2.09</v>
@@ -32088,7 +32088,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR145" t="n">
         <v>1.21</v>
@@ -36448,7 +36448,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR165" t="n">
         <v>1.63</v>
@@ -37753,7 +37753,7 @@
         <v>2.3</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ171" t="n">
         <v>2.31</v>
@@ -40154,7 +40154,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR182" t="n">
         <v>1.09</v>
@@ -42113,7 +42113,7 @@
         <v>1.33</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.46</v>
@@ -43206,7 +43206,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR196" t="n">
         <v>1.74</v>
@@ -44511,7 +44511,7 @@
         <v>1.67</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.77</v>
@@ -45898,6 +45898,224 @@
       </c>
       <c r="BP208" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8306772</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45959.70833333334</v>
+      </c>
+      <c r="F209" t="n">
+        <v>19</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>1</v>
+      </c>
+      <c r="N209" t="n">
+        <v>2</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>['90+8']</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R209" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S209" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U209" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V209" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W209" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X209" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ18" t="n">
         <v>1</v>
@@ -4620,7 +4620,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR19" t="n">
         <v>1.88</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR21" t="n">
         <v>2.19</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR23" t="n">
         <v>1.19</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR24" t="n">
         <v>1.24</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR25" t="n">
         <v>1.26</v>
@@ -6143,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR26" t="n">
         <v>1.5</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR27" t="n">
         <v>1.31</v>
@@ -6579,10 +6579,10 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR28" t="n">
         <v>1.29</v>
@@ -8544,7 +8544,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR37" t="n">
         <v>2.12</v>
@@ -8762,7 +8762,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR38" t="n">
         <v>1.62</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.08</v>
@@ -9195,10 +9195,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR40" t="n">
         <v>1.88</v>
@@ -9413,10 +9413,10 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR41" t="n">
         <v>1.36</v>
@@ -9634,7 +9634,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR42" t="n">
         <v>2.53</v>
@@ -9849,10 +9849,10 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR43" t="n">
         <v>1.56</v>
@@ -10067,10 +10067,10 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR44" t="n">
         <v>2.09</v>
@@ -10506,7 +10506,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR46" t="n">
         <v>1.8</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.77</v>
@@ -11375,7 +11375,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.85</v>
@@ -11814,7 +11814,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR52" t="n">
         <v>1.1</v>
@@ -12029,10 +12029,10 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR53" t="n">
         <v>1.7</v>
@@ -12247,10 +12247,10 @@
         <v>1.4</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR54" t="n">
         <v>1.53</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.46</v>
@@ -12683,7 +12683,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.08</v>
@@ -12904,7 +12904,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR57" t="n">
         <v>2.42</v>
@@ -13122,7 +13122,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR58" t="n">
         <v>2.01</v>
@@ -13340,7 +13340,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR59" t="n">
         <v>1.82</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -13773,7 +13773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.08</v>
@@ -13994,7 +13994,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR62" t="n">
         <v>2.22</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.85</v>
@@ -14430,7 +14430,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ64" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR64" t="n">
         <v>1.33</v>
@@ -15084,7 +15084,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR67" t="n">
         <v>1.13</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ68" t="n">
         <v>1</v>
@@ -15517,10 +15517,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR69" t="n">
         <v>1.06</v>
@@ -15738,7 +15738,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ70" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR70" t="n">
         <v>2.23</v>
@@ -16171,7 +16171,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -16389,7 +16389,7 @@
         <v>1.4</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ73" t="n">
         <v>1</v>
@@ -16607,10 +16607,10 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR74" t="n">
         <v>1.05</v>
@@ -16825,10 +16825,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR75" t="n">
         <v>1.46</v>
@@ -17046,7 +17046,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR76" t="n">
         <v>1.93</v>
@@ -17264,7 +17264,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ77" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR77" t="n">
         <v>1.1</v>
@@ -17697,10 +17697,10 @@
         <v>2.4</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ79" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR79" t="n">
         <v>1.72</v>
@@ -17918,7 +17918,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR80" t="n">
         <v>2.06</v>
@@ -18133,7 +18133,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.85</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.77</v>
@@ -18572,7 +18572,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR83" t="n">
         <v>1.34</v>
@@ -18790,7 +18790,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR84" t="n">
         <v>1.74</v>
@@ -19223,7 +19223,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.77</v>
@@ -19662,7 +19662,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR88" t="n">
         <v>1.87</v>
@@ -19880,7 +19880,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR89" t="n">
         <v>1.13</v>
@@ -20095,7 +20095,7 @@
         <v>0.8</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ90" t="n">
         <v>1</v>
@@ -20316,7 +20316,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR91" t="n">
         <v>2.06</v>
@@ -20531,7 +20531,7 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.77</v>
@@ -20749,7 +20749,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.08</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ94" t="n">
         <v>1</v>
@@ -21188,7 +21188,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR95" t="n">
         <v>1.89</v>
@@ -21403,10 +21403,10 @@
         <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR96" t="n">
         <v>1.25</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.08</v>
@@ -22060,7 +22060,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR99" t="n">
         <v>1.45</v>
@@ -22275,7 +22275,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.85</v>
@@ -22496,7 +22496,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR101" t="n">
         <v>1.72</v>
@@ -22711,7 +22711,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.46</v>
@@ -22932,7 +22932,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR103" t="n">
         <v>1.62</v>
@@ -23150,7 +23150,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR104" t="n">
         <v>2.3</v>
@@ -23365,7 +23365,7 @@
         <v>1.43</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.85</v>
@@ -23583,7 +23583,7 @@
         <v>1.43</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ106" t="n">
         <v>1</v>
@@ -24019,7 +24019,7 @@
         <v>2.17</v>
       </c>
       <c r="AP108" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.77</v>
@@ -24240,7 +24240,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR109" t="n">
         <v>1.37</v>
@@ -24676,7 +24676,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR111" t="n">
         <v>1.99</v>
@@ -24891,10 +24891,10 @@
         <v>1.6</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR112" t="n">
         <v>1.3</v>
@@ -25112,7 +25112,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25327,10 +25327,10 @@
         <v>1.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR114" t="n">
         <v>1.32</v>
@@ -25545,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.77</v>
@@ -25766,7 +25766,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR116" t="n">
         <v>2.26</v>
@@ -25981,10 +25981,10 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR117" t="n">
         <v>1.9</v>
@@ -26202,7 +26202,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR118" t="n">
         <v>1.71</v>
@@ -26417,7 +26417,7 @@
         <v>0.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.46</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.08</v>
@@ -26853,7 +26853,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.77</v>
@@ -27074,7 +27074,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR122" t="n">
         <v>1.71</v>
@@ -28161,10 +28161,10 @@
         <v>2</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR127" t="n">
         <v>1.55</v>
@@ -28597,7 +28597,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.08</v>
@@ -28818,7 +28818,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR130" t="n">
         <v>1.75</v>
@@ -29033,10 +29033,10 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR131" t="n">
         <v>1.23</v>
@@ -29251,10 +29251,10 @@
         <v>0.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR132" t="n">
         <v>2.09</v>
@@ -29469,10 +29469,10 @@
         <v>1.38</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR133" t="n">
         <v>1.3</v>
@@ -29687,10 +29687,10 @@
         <v>0</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR134" t="n">
         <v>1.52</v>
@@ -29905,7 +29905,7 @@
         <v>0.71</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.46</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ136" t="n">
         <v>1</v>
@@ -30559,7 +30559,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.08</v>
@@ -30780,7 +30780,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR139" t="n">
         <v>1.16</v>
@@ -30998,7 +30998,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ140" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR140" t="n">
         <v>1.8</v>
@@ -31213,10 +31213,10 @@
         <v>2.13</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31431,10 +31431,10 @@
         <v>1.63</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR142" t="n">
         <v>1.56</v>
@@ -31649,7 +31649,7 @@
         <v>1.25</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.85</v>
@@ -31867,7 +31867,7 @@
         <v>0.63</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.46</v>
@@ -32088,7 +32088,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR145" t="n">
         <v>1.21</v>
@@ -32303,10 +32303,10 @@
         <v>1.44</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR146" t="n">
         <v>2.04</v>
@@ -32521,7 +32521,7 @@
         <v>0.89</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ147" t="n">
         <v>1</v>
@@ -32957,7 +32957,7 @@
         <v>0.67</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.77</v>
@@ -33175,7 +33175,7 @@
         <v>1.89</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.77</v>
@@ -33396,7 +33396,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR151" t="n">
         <v>1.7</v>
@@ -33611,7 +33611,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.46</v>
@@ -33832,7 +33832,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR153" t="n">
         <v>1.28</v>
@@ -34047,10 +34047,10 @@
         <v>1.3</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR154" t="n">
         <v>1.23</v>
@@ -34268,7 +34268,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ155" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -34483,7 +34483,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.08</v>
@@ -34704,7 +34704,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR157" t="n">
         <v>2.16</v>
@@ -34919,10 +34919,10 @@
         <v>0</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR158" t="n">
         <v>1.37</v>
@@ -35137,7 +35137,7 @@
         <v>1.22</v>
       </c>
       <c r="AP159" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.85</v>
@@ -35358,7 +35358,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR160" t="n">
         <v>2.28</v>
@@ -35573,7 +35573,7 @@
         <v>0.88</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.08</v>
@@ -36009,7 +36009,7 @@
         <v>1.7</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.77</v>
@@ -36227,10 +36227,10 @@
         <v>2.2</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR164" t="n">
         <v>1.39</v>
@@ -36448,7 +36448,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR165" t="n">
         <v>1.63</v>
@@ -36663,7 +36663,7 @@
         <v>0.7</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.77</v>
@@ -36884,7 +36884,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR167" t="n">
         <v>1.15</v>
@@ -37099,7 +37099,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.46</v>
@@ -37320,7 +37320,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR169" t="n">
         <v>1.61</v>
@@ -37535,7 +37535,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.08</v>
@@ -37756,7 +37756,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ171" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR171" t="n">
         <v>1.69</v>
@@ -37971,7 +37971,7 @@
         <v>0.9</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ172" t="n">
         <v>1</v>
@@ -38189,10 +38189,10 @@
         <v>1.45</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR173" t="n">
         <v>1.53</v>
@@ -38410,7 +38410,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR174" t="n">
         <v>1.25</v>
@@ -38846,7 +38846,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ176" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR176" t="n">
         <v>1.59</v>
@@ -39279,7 +39279,7 @@
         <v>0.91</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.77</v>
@@ -39497,10 +39497,10 @@
         <v>1.27</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR179" t="n">
         <v>1.25</v>
@@ -39715,10 +39715,10 @@
         <v>1.27</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR180" t="n">
         <v>1.48</v>
@@ -39933,7 +39933,7 @@
         <v>1.18</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ181" t="n">
         <v>1</v>
@@ -40154,7 +40154,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR182" t="n">
         <v>1.09</v>
@@ -40369,7 +40369,7 @@
         <v>1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.08</v>
@@ -40587,7 +40587,7 @@
         <v>1.82</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.77</v>
@@ -41244,7 +41244,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR187" t="n">
         <v>2.14</v>
@@ -41459,7 +41459,7 @@
         <v>1.18</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.08</v>
@@ -41680,7 +41680,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR189" t="n">
         <v>2.27</v>
@@ -41895,7 +41895,7 @@
         <v>0.82</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ190" t="n">
         <v>1</v>
@@ -42116,7 +42116,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR191" t="n">
         <v>1.67</v>
@@ -42334,7 +42334,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ192" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR192" t="n">
         <v>1.56</v>
@@ -42549,10 +42549,10 @@
         <v>1.17</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR193" t="n">
         <v>1.48</v>
@@ -42770,7 +42770,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.08</v>
+        <v>0.29</v>
       </c>
       <c r="AR194" t="n">
         <v>2</v>
@@ -42985,10 +42985,10 @@
         <v>2</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ195" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AR195" t="n">
         <v>1.51</v>
@@ -43203,10 +43203,10 @@
         <v>0.64</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR196" t="n">
         <v>1.74</v>
@@ -43421,7 +43421,7 @@
         <v>1.08</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ197" t="n">
         <v>1</v>
@@ -43639,10 +43639,10 @@
         <v>1.17</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR198" t="n">
         <v>1.37</v>
@@ -43857,7 +43857,7 @@
         <v>0.91</v>
       </c>
       <c r="AP199" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.08</v>
@@ -44514,7 +44514,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR202" t="n">
         <v>1.71</v>
@@ -45601,7 +45601,7 @@
         <v>0.83</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.77</v>
@@ -45822,7 +45822,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ208" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AR208" t="n">
         <v>2.02</v>
@@ -46040,7 +46040,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR209" t="n">
         <v>1.69</v>
@@ -46116,6 +46116,1750 @@
       </c>
       <c r="BP209" t="n">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>8306723</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45962.5</v>
+      </c>
+      <c r="F210" t="n">
+        <v>27</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>2</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>2</v>
+      </c>
+      <c r="L210" t="n">
+        <v>3</v>
+      </c>
+      <c r="M210" t="n">
+        <v>1</v>
+      </c>
+      <c r="N210" t="n">
+        <v>4</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>['32', '45+1', '47']</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R210" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S210" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U210" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V210" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X210" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8306711</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>45962.58333333334</v>
+      </c>
+      <c r="F211" t="n">
+        <v>27</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>3</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>4</v>
+      </c>
+      <c r="L211" t="n">
+        <v>4</v>
+      </c>
+      <c r="M211" t="n">
+        <v>2</v>
+      </c>
+      <c r="N211" t="n">
+        <v>6</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['11', '24', '33', '90+3']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>['14', '77']</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S211" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U211" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X211" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8306708</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>45963.4375</v>
+      </c>
+      <c r="F212" t="n">
+        <v>27</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>2</v>
+      </c>
+      <c r="K212" t="n">
+        <v>3</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>2</v>
+      </c>
+      <c r="N212" t="n">
+        <v>3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['38', '45+2']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S212" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U212" t="n">
+        <v>4</v>
+      </c>
+      <c r="V212" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X212" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8306749</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>45963.54166666666</v>
+      </c>
+      <c r="F213" t="n">
+        <v>27</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>2</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>2</v>
+      </c>
+      <c r="L213" t="n">
+        <v>3</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['5', '8', '54']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S213" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U213" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V213" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X213" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8306763</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45963.54166666666</v>
+      </c>
+      <c r="F214" t="n">
+        <v>27</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>2</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>2</v>
+      </c>
+      <c r="L214" t="n">
+        <v>2</v>
+      </c>
+      <c r="M214" t="n">
+        <v>1</v>
+      </c>
+      <c r="N214" t="n">
+        <v>3</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['1', '18']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S214" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X214" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8306764</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>45963.54166666666</v>
+      </c>
+      <c r="F215" t="n">
+        <v>27</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>2</v>
+      </c>
+      <c r="L215" t="n">
+        <v>3</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>4</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['24', '56', '74']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S215" t="n">
+        <v>4</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X215" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8306754</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>45963.54166666666</v>
+      </c>
+      <c r="F216" t="n">
+        <v>27</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>2</v>
+      </c>
+      <c r="K216" t="n">
+        <v>2</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>4</v>
+      </c>
+      <c r="N216" t="n">
+        <v>5</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['10', '29', '46', '50']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S216" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X216" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8306762</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>45963.63541666666</v>
+      </c>
+      <c r="F217" t="n">
+        <v>27</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>3</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>3</v>
+      </c>
+      <c r="L217" t="n">
+        <v>4</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>4</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['15', '24', '26', '67']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S217" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U217" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X217" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -46924,7 +46924,7 @@
         <v>3.04</v>
       </c>
       <c r="AU213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV213" t="n">
         <v>7</v>
@@ -46936,7 +46936,7 @@
         <v>12</v>
       </c>
       <c r="AY213" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ213" t="n">
         <v>19</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -46709,19 +46709,19 @@
         <v>6</v>
       </c>
       <c r="AV212" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW212" t="n">
         <v>8</v>
       </c>
       <c r="AX212" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY212" t="n">
         <v>14</v>
       </c>
       <c r="AZ212" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA212" t="n">
         <v>7</v>
@@ -46933,13 +46933,13 @@
         <v>9</v>
       </c>
       <c r="AX213" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY213" t="n">
         <v>15</v>
       </c>
       <c r="AZ213" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA213" t="n">
         <v>8</v>
@@ -47363,7 +47363,7 @@
         <v>5</v>
       </c>
       <c r="AV215" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW215" t="n">
         <v>9</v>
@@ -47375,7 +47375,7 @@
         <v>14</v>
       </c>
       <c r="AZ215" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA215" t="n">
         <v>2</v>
@@ -47581,7 +47581,7 @@
         <v>8</v>
       </c>
       <c r="AV216" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW216" t="n">
         <v>19</v>
@@ -47593,7 +47593,7 @@
         <v>27</v>
       </c>
       <c r="AZ216" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA216" t="n">
         <v>16</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ14" t="n">
         <v>1</v>
@@ -7015,7 +7015,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.77</v>
@@ -8108,7 +8108,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR35" t="n">
         <v>1.33</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ48" t="n">
         <v>1</v>
@@ -11160,7 +11160,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR49" t="n">
         <v>1.53</v>
@@ -13776,7 +13776,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR61" t="n">
         <v>1.23</v>
@@ -14645,7 +14645,7 @@
         <v>1.33</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.77</v>
@@ -19005,7 +19005,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.46</v>
@@ -19444,7 +19444,7 @@
         <v>2.46</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR87" t="n">
         <v>2.39</v>
@@ -21842,7 +21842,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR98" t="n">
         <v>1.94</v>
@@ -22929,7 +22929,7 @@
         <v>0</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.29</v>
@@ -25109,7 +25109,7 @@
         <v>1.43</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.07</v>
@@ -26638,7 +26638,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR120" t="n">
         <v>1.24</v>
@@ -28600,7 +28600,7 @@
         <v>2</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR129" t="n">
         <v>1.56</v>
@@ -28815,7 +28815,7 @@
         <v>1.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.64</v>
@@ -33393,7 +33393,7 @@
         <v>1.22</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.07</v>
@@ -35576,7 +35576,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR161" t="n">
         <v>1.58</v>
@@ -36445,7 +36445,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.79</v>
@@ -38843,7 +38843,7 @@
         <v>2.09</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ176" t="n">
         <v>2.14</v>
@@ -39064,7 +39064,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR177" t="n">
         <v>1.99</v>
@@ -40372,7 +40372,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR183" t="n">
         <v>1.37</v>
@@ -42331,7 +42331,7 @@
         <v>2.18</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ192" t="n">
         <v>2.14</v>
@@ -43860,7 +43860,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR199" t="n">
         <v>1.5</v>
@@ -44293,7 +44293,7 @@
         <v>1.17</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.08</v>
@@ -44732,7 +44732,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR203" t="n">
         <v>1.56</v>
@@ -47860,6 +47860,224 @@
       </c>
       <c r="BP217" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8306707</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>45969.41666666666</v>
+      </c>
+      <c r="F218" t="n">
+        <v>28</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>2</v>
+      </c>
+      <c r="N218" t="n">
+        <v>2</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>['53', '87']</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R218" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S218" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U218" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V218" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X218" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP218"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2658,7 +2658,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.08</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.07</v>
@@ -7672,7 +7672,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR33" t="n">
         <v>1.67</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.77</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.29</v>
@@ -9631,7 +9631,7 @@
         <v>3</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.36</v>
@@ -10942,7 +10942,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR48" t="n">
         <v>1.78</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.79</v>
@@ -13558,7 +13558,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR60" t="n">
         <v>1.96</v>
@@ -16174,7 +16174,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR72" t="n">
         <v>1.75</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.21</v>
@@ -20098,7 +20098,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR90" t="n">
         <v>1.47</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.77</v>
@@ -24458,7 +24458,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR110" t="n">
         <v>1.79</v>
@@ -25763,7 +25763,7 @@
         <v>1.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ116" t="n">
         <v>2.14</v>
@@ -27510,7 +27510,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR124" t="n">
         <v>1.14</v>
@@ -30126,7 +30126,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR136" t="n">
         <v>1.59</v>
@@ -32524,7 +32524,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR147" t="n">
         <v>1.38</v>
@@ -34701,7 +34701,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.07</v>
@@ -37974,7 +37974,7 @@
         <v>2</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR172" t="n">
         <v>1.48</v>
@@ -38625,7 +38625,7 @@
         <v>1.1</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.85</v>
@@ -41241,7 +41241,7 @@
         <v>1.82</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.64</v>
@@ -41898,7 +41898,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR190" t="n">
         <v>1.41</v>
@@ -44075,7 +44075,7 @@
         <v>0.5</v>
       </c>
       <c r="AP200" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.46</v>
@@ -44950,7 +44950,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR204" t="n">
         <v>1.35</v>
@@ -48078,6 +48078,224 @@
       </c>
       <c r="BP218" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8306907</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>45969.58333333334</v>
+      </c>
+      <c r="F219" t="n">
+        <v>28</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>3</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>3</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>['55', '75', '82']</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S219" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U219" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V219" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X219" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.93</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.21</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR18" t="n">
         <v>1.22</v>
@@ -4835,10 +4835,10 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR20" t="n">
         <v>1.69</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>1.92</v>
@@ -7018,7 +7018,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR30" t="n">
         <v>1.62</v>
@@ -7233,10 +7233,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR31" t="n">
         <v>1.74</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR32" t="n">
         <v>1.72</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.93</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR34" t="n">
         <v>2.73</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.21</v>
@@ -8326,7 +8326,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR36" t="n">
         <v>1.91</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.07</v>
@@ -8980,7 +8980,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR45" t="n">
         <v>2.05</v>
@@ -10503,7 +10503,7 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.07</v>
@@ -10724,7 +10724,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR47" t="n">
         <v>1.08</v>
@@ -11157,7 +11157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.21</v>
@@ -11378,7 +11378,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR50" t="n">
         <v>1.34</v>
@@ -11593,10 +11593,10 @@
         <v>1.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR51" t="n">
         <v>1.69</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ52" t="n">
         <v>2.14</v>
@@ -12468,7 +12468,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR55" t="n">
         <v>1.66</v>
@@ -12686,7 +12686,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR56" t="n">
         <v>1.17</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.29</v>
@@ -13337,7 +13337,7 @@
         <v>2.33</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.36</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.07</v>
@@ -14212,7 +14212,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR63" t="n">
         <v>1.12</v>
@@ -14427,7 +14427,7 @@
         <v>2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ64" t="n">
         <v>2.14</v>
@@ -14648,7 +14648,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR65" t="n">
         <v>1.86</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR66" t="n">
         <v>1.54</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.64</v>
@@ -15302,7 +15302,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR68" t="n">
         <v>0.97</v>
@@ -15735,7 +15735,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.14</v>
@@ -15953,10 +15953,10 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR71" t="n">
         <v>1.86</v>
@@ -16392,7 +16392,7 @@
         <v>2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR73" t="n">
         <v>1.61</v>
@@ -17043,7 +17043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.07</v>
@@ -17261,7 +17261,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ77" t="n">
         <v>2.14</v>
@@ -17479,10 +17479,10 @@
         <v>0.25</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR78" t="n">
         <v>2.11</v>
@@ -17915,7 +17915,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.64</v>
@@ -18136,7 +18136,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR81" t="n">
         <v>2.04</v>
@@ -18354,7 +18354,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR82" t="n">
         <v>1.05</v>
@@ -18569,7 +18569,7 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.07</v>
@@ -18787,7 +18787,7 @@
         <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.29</v>
@@ -19008,7 +19008,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR85" t="n">
         <v>1.77</v>
@@ -19226,7 +19226,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR86" t="n">
         <v>1.23</v>
@@ -19659,7 +19659,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.14</v>
@@ -19877,7 +19877,7 @@
         <v>1.43</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.07</v>
@@ -20313,7 +20313,7 @@
         <v>1.8</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.36</v>
@@ -20534,7 +20534,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR92" t="n">
         <v>1.2</v>
@@ -20752,7 +20752,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR93" t="n">
         <v>1.58</v>
@@ -20970,7 +20970,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR94" t="n">
         <v>1.81</v>
@@ -21185,7 +21185,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.79</v>
@@ -21624,7 +21624,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR97" t="n">
         <v>2.24</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ99" t="n">
         <v>2.14</v>
@@ -22278,7 +22278,7 @@
         <v>2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR100" t="n">
         <v>1.6</v>
@@ -22493,7 +22493,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.07</v>
@@ -22714,7 +22714,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR102" t="n">
         <v>1.22</v>
@@ -23147,7 +23147,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.79</v>
@@ -23368,7 +23368,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR105" t="n">
         <v>1.24</v>
@@ -23586,7 +23586,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR106" t="n">
         <v>1.52</v>
@@ -23801,10 +23801,10 @@
         <v>0.83</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR107" t="n">
         <v>1.13</v>
@@ -24022,7 +24022,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR108" t="n">
         <v>1.59</v>
@@ -24237,7 +24237,7 @@
         <v>2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.36</v>
@@ -24455,7 +24455,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.93</v>
@@ -24673,7 +24673,7 @@
         <v>2.29</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ111" t="n">
         <v>2.14</v>
@@ -25548,7 +25548,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR115" t="n">
         <v>1.53</v>
@@ -26199,7 +26199,7 @@
         <v>1.38</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.07</v>
@@ -26420,7 +26420,7 @@
         <v>2</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR119" t="n">
         <v>1.56</v>
@@ -26856,7 +26856,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR121" t="n">
         <v>1.28</v>
@@ -27071,7 +27071,7 @@
         <v>1.86</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.36</v>
@@ -27289,10 +27289,10 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR123" t="n">
         <v>1.28</v>
@@ -27507,7 +27507,7 @@
         <v>0.71</v>
       </c>
       <c r="AP124" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.93</v>
@@ -27725,10 +27725,10 @@
         <v>1.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR125" t="n">
         <v>2.33</v>
@@ -27943,10 +27943,10 @@
         <v>2.29</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR126" t="n">
         <v>1.74</v>
@@ -28379,10 +28379,10 @@
         <v>0.75</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR128" t="n">
         <v>2.42</v>
@@ -29908,7 +29908,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR135" t="n">
         <v>1.54</v>
@@ -30341,10 +30341,10 @@
         <v>2</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR137" t="n">
         <v>2.4</v>
@@ -30562,7 +30562,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR138" t="n">
         <v>1.54</v>
@@ -30777,7 +30777,7 @@
         <v>1.63</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.36</v>
@@ -30995,7 +30995,7 @@
         <v>2.11</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ140" t="n">
         <v>2.14</v>
@@ -31652,7 +31652,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR143" t="n">
         <v>1.32</v>
@@ -31870,7 +31870,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR144" t="n">
         <v>1.2</v>
@@ -32085,7 +32085,7 @@
         <v>0.38</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.79</v>
@@ -32739,10 +32739,10 @@
         <v>1.11</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR148" t="n">
         <v>1.14</v>
@@ -32960,7 +32960,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR149" t="n">
         <v>1.46</v>
@@ -33178,7 +33178,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR150" t="n">
         <v>1.67</v>
@@ -33614,7 +33614,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR152" t="n">
         <v>2.06</v>
@@ -33829,7 +33829,7 @@
         <v>1.78</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.64</v>
@@ -34265,7 +34265,7 @@
         <v>2.22</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ155" t="n">
         <v>2.14</v>
@@ -34486,7 +34486,7 @@
         <v>2</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR156" t="n">
         <v>1.54</v>
@@ -35140,7 +35140,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR159" t="n">
         <v>1.49</v>
@@ -35355,7 +35355,7 @@
         <v>1.4</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.07</v>
@@ -35791,10 +35791,10 @@
         <v>1.3</v>
       </c>
       <c r="AP162" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR162" t="n">
         <v>1.95</v>
@@ -36012,7 +36012,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR163" t="n">
         <v>1.56</v>
@@ -36666,7 +36666,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR166" t="n">
         <v>1.24</v>
@@ -36881,7 +36881,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ167" t="n">
         <v>1.07</v>
@@ -37102,7 +37102,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR168" t="n">
         <v>1.42</v>
@@ -37317,7 +37317,7 @@
         <v>1.7</v>
       </c>
       <c r="AP169" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.64</v>
@@ -37538,7 +37538,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR170" t="n">
         <v>2.03</v>
@@ -37753,7 +37753,7 @@
         <v>2.3</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ171" t="n">
         <v>2.14</v>
@@ -38407,7 +38407,7 @@
         <v>0.1</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.29</v>
@@ -38628,7 +38628,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR175" t="n">
         <v>2.08</v>
@@ -39061,7 +39061,7 @@
         <v>1.11</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.21</v>
@@ -39282,7 +39282,7 @@
         <v>2</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR178" t="n">
         <v>1.48</v>
@@ -39936,7 +39936,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR181" t="n">
         <v>1.7</v>
@@ -40151,7 +40151,7 @@
         <v>0.4</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.79</v>
@@ -40590,7 +40590,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR184" t="n">
         <v>1.92</v>
@@ -40805,10 +40805,10 @@
         <v>0.55</v>
       </c>
       <c r="AP185" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR185" t="n">
         <v>1.59</v>
@@ -41023,10 +41023,10 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR186" t="n">
         <v>1.34</v>
@@ -41462,7 +41462,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR188" t="n">
         <v>1.51</v>
@@ -41677,7 +41677,7 @@
         <v>0.09</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.29</v>
@@ -42113,7 +42113,7 @@
         <v>1.33</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.36</v>
@@ -42767,7 +42767,7 @@
         <v>0.08</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.29</v>
@@ -43424,7 +43424,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR197" t="n">
         <v>1.44</v>
@@ -44078,7 +44078,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR200" t="n">
         <v>2.09</v>
@@ -44296,7 +44296,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AR201" t="n">
         <v>1.59</v>
@@ -44511,7 +44511,7 @@
         <v>1.67</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.64</v>
@@ -44729,7 +44729,7 @@
         <v>1.08</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.21</v>
@@ -44947,7 +44947,7 @@
         <v>0.83</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ204" t="n">
         <v>0.93</v>
@@ -45165,10 +45165,10 @@
         <v>1.67</v>
       </c>
       <c r="AP205" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AR205" t="n">
         <v>1.1</v>
@@ -45383,10 +45383,10 @@
         <v>0.92</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR206" t="n">
         <v>2.44</v>
@@ -45604,7 +45604,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR207" t="n">
         <v>1.86</v>
@@ -45819,7 +45819,7 @@
         <v>2.25</v>
       </c>
       <c r="AP208" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ208" t="n">
         <v>2.14</v>
@@ -46037,7 +46037,7 @@
         <v>0.83</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ209" t="n">
         <v>0.79</v>
@@ -48014,7 +48014,7 @@
         <v>2.85</v>
       </c>
       <c r="AU218" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV218" t="n">
         <v>5</v>
@@ -48023,13 +48023,13 @@
         <v>9</v>
       </c>
       <c r="AX218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY218" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ218" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA218" t="n">
         <v>7</v>
@@ -48232,7 +48232,7 @@
         <v>3.33</v>
       </c>
       <c r="AU219" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV219" t="n">
         <v>3</v>
@@ -48244,7 +48244,7 @@
         <v>9</v>
       </c>
       <c r="AY219" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ219" t="n">
         <v>12</v>
@@ -48296,6 +48296,1314 @@
       </c>
       <c r="BP219" t="n">
         <v>1.77</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8306750</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>45970.4375</v>
+      </c>
+      <c r="F220" t="n">
+        <v>28</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S220" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U220" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V220" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X220" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8306791</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>45970.54166666666</v>
+      </c>
+      <c r="F221" t="n">
+        <v>28</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>5</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>5</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>['16', '68', '71', '84', '87']</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R221" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S221" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U221" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V221" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X221" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>8306766</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>45970.54166666666</v>
+      </c>
+      <c r="F222" t="n">
+        <v>28</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>2</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>2</v>
+      </c>
+      <c r="L222" t="n">
+        <v>2</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1</v>
+      </c>
+      <c r="N222" t="n">
+        <v>3</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>['29', '45+1']</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="S222" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U222" t="n">
+        <v>4</v>
+      </c>
+      <c r="V222" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X222" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>8306712</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>45970.54166666666</v>
+      </c>
+      <c r="F223" t="n">
+        <v>28</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" t="n">
+        <v>1</v>
+      </c>
+      <c r="N223" t="n">
+        <v>2</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R223" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S223" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U223" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X223" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP223" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>8306825</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>45970.54166666666</v>
+      </c>
+      <c r="F224" t="n">
+        <v>28</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>1</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>1</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S224" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U224" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V224" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X224" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>8306765</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>45970.63541666666</v>
+      </c>
+      <c r="F225" t="n">
+        <v>28</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>2</v>
+      </c>
+      <c r="N225" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>['52', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>7</v>
+      </c>
+      <c r="R225" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S225" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U225" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V225" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X225" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -48674,13 +48674,13 @@
         <v>0</v>
       </c>
       <c r="AW221" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX221" t="n">
         <v>7</v>
       </c>
       <c r="AY221" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ221" t="n">
         <v>7</v>
@@ -48895,13 +48895,13 @@
         <v>4</v>
       </c>
       <c r="AX222" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY222" t="n">
         <v>9</v>
       </c>
       <c r="AZ222" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA222" t="n">
         <v>3</v>
@@ -49113,13 +49113,13 @@
         <v>6</v>
       </c>
       <c r="AX223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY223" t="n">
         <v>9</v>
       </c>
       <c r="AZ223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA223" t="n">
         <v>7</v>
@@ -49331,13 +49331,13 @@
         <v>4</v>
       </c>
       <c r="AX224" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY224" t="n">
         <v>5</v>
       </c>
       <c r="AZ224" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA224" t="n">
         <v>2</v>
@@ -49546,16 +49546,16 @@
         <v>3</v>
       </c>
       <c r="AW225" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX225" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY225" t="n">
         <v>10</v>
       </c>
-      <c r="AY225" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ225" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA225" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -48569,7 +48569,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>['16', '68', '71', '84', '87']</t>
+          <t>['16', '68', '70', '84', '87']</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -48886,7 +48886,7 @@
         <v>2.55</v>
       </c>
       <c r="AU222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV222" t="n">
         <v>1</v>
@@ -48898,7 +48898,7 @@
         <v>13</v>
       </c>
       <c r="AY222" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ222" t="n">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.79</v>
@@ -2440,7 +2440,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.36</v>
@@ -6582,7 +6582,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR28" t="n">
         <v>1.29</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.64</v>
@@ -12032,7 +12032,7 @@
         <v>2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR53" t="n">
         <v>1.7</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.93</v>
@@ -17264,7 +17264,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ77" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR77" t="n">
         <v>1.1</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.71</v>
@@ -22060,7 +22060,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR99" t="n">
         <v>1.45</v>
@@ -22711,7 +22711,7 @@
         <v>0.8</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.43</v>
@@ -24894,7 +24894,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR112" t="n">
         <v>1.3</v>
@@ -25327,7 +25327,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.64</v>
@@ -25766,7 +25766,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ116" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR116" t="n">
         <v>2.26</v>
@@ -29036,7 +29036,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR131" t="n">
         <v>1.23</v>
@@ -29469,7 +29469,7 @@
         <v>1.38</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.07</v>
@@ -31216,7 +31216,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31649,7 +31649,7 @@
         <v>1.25</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ143" t="n">
         <v>1</v>
@@ -32521,7 +32521,7 @@
         <v>0.89</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.93</v>
@@ -34268,7 +34268,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ155" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -36227,7 +36227,7 @@
         <v>2.2</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ164" t="n">
         <v>2.14</v>
@@ -37756,7 +37756,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ171" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR171" t="n">
         <v>1.69</v>
@@ -40369,7 +40369,7 @@
         <v>1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.21</v>
@@ -42334,7 +42334,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ192" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR192" t="n">
         <v>1.56</v>
@@ -43639,7 +43639,7 @@
         <v>1.17</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.07</v>
@@ -45822,7 +45822,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ208" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR208" t="n">
         <v>2.02</v>
@@ -46258,7 +46258,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ210" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR210" t="n">
         <v>1.92</v>
@@ -47563,7 +47563,7 @@
         <v>0.08</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.29</v>
@@ -49604,6 +49604,224 @@
       </c>
       <c r="BP225" t="n">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>8306716</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>45982.625</v>
+      </c>
+      <c r="F226" t="n">
+        <v>29</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="n">
+        <v>1</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>2</v>
+      </c>
+      <c r="N226" t="n">
+        <v>3</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>['30', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>6</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S226" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U226" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X226" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.07</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ9" t="n">
         <v>2.2</v>
@@ -4399,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.93</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.07</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR23" t="n">
         <v>1.19</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR24" t="n">
         <v>1.24</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR25" t="n">
         <v>1.26</v>
@@ -6146,7 +6146,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR26" t="n">
         <v>1.5</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR27" t="n">
         <v>1.31</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ28" t="n">
         <v>2.2</v>
@@ -8544,7 +8544,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR37" t="n">
         <v>2.12</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.07</v>
@@ -9195,10 +9195,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR40" t="n">
         <v>1.88</v>
@@ -9413,10 +9413,10 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR41" t="n">
         <v>1.36</v>
@@ -9634,7 +9634,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR42" t="n">
         <v>2.53</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.07</v>
@@ -10067,10 +10067,10 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR44" t="n">
         <v>2.09</v>
@@ -10506,7 +10506,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR46" t="n">
         <v>1.8</v>
@@ -11375,7 +11375,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ50" t="n">
         <v>1</v>
@@ -11814,7 +11814,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR52" t="n">
         <v>1.1</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ53" t="n">
         <v>2.2</v>
@@ -12247,7 +12247,7 @@
         <v>1.4</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.07</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.43</v>
@@ -12683,7 +12683,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.07</v>
@@ -12904,7 +12904,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR57" t="n">
         <v>2.42</v>
@@ -13122,7 +13122,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR58" t="n">
         <v>2.01</v>
@@ -13340,7 +13340,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR59" t="n">
         <v>1.82</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.93</v>
@@ -13773,7 +13773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.21</v>
@@ -13994,7 +13994,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR62" t="n">
         <v>2.22</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ63" t="n">
         <v>1</v>
@@ -14430,7 +14430,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ64" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR64" t="n">
         <v>1.33</v>
@@ -15084,7 +15084,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR67" t="n">
         <v>1.13</v>
@@ -15517,10 +15517,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR69" t="n">
         <v>1.06</v>
@@ -15738,7 +15738,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ70" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR70" t="n">
         <v>2.23</v>
@@ -16171,7 +16171,7 @@
         <v>0.25</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.93</v>
@@ -16389,7 +16389,7 @@
         <v>1.4</v>
       </c>
       <c r="AP73" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.93</v>
@@ -16607,10 +16607,10 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR74" t="n">
         <v>1.05</v>
@@ -16825,10 +16825,10 @@
         <v>0.75</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR75" t="n">
         <v>1.46</v>
@@ -17697,10 +17697,10 @@
         <v>2.4</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ79" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR79" t="n">
         <v>1.72</v>
@@ -17918,7 +17918,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR80" t="n">
         <v>2.06</v>
@@ -18133,7 +18133,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ81" t="n">
         <v>1</v>
@@ -18572,7 +18572,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR83" t="n">
         <v>1.34</v>
@@ -18790,7 +18790,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR84" t="n">
         <v>1.74</v>
@@ -19223,7 +19223,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.64</v>
@@ -19662,7 +19662,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR88" t="n">
         <v>1.87</v>
@@ -20095,7 +20095,7 @@
         <v>0.8</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.93</v>
@@ -20316,7 +20316,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR91" t="n">
         <v>2.06</v>
@@ -20531,7 +20531,7 @@
         <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.64</v>
@@ -20749,7 +20749,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.07</v>
@@ -20967,7 +20967,7 @@
         <v>1.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.93</v>
@@ -21188,7 +21188,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR95" t="n">
         <v>1.89</v>
@@ -21403,10 +21403,10 @@
         <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR96" t="n">
         <v>1.25</v>
@@ -21839,7 +21839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.21</v>
@@ -22275,7 +22275,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ100" t="n">
         <v>1</v>
@@ -22496,7 +22496,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR101" t="n">
         <v>1.72</v>
@@ -22932,7 +22932,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR103" t="n">
         <v>1.62</v>
@@ -23150,7 +23150,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR104" t="n">
         <v>2.3</v>
@@ -23365,7 +23365,7 @@
         <v>1.43</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -23583,7 +23583,7 @@
         <v>1.43</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.93</v>
@@ -24019,7 +24019,7 @@
         <v>2.17</v>
       </c>
       <c r="AP108" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.64</v>
@@ -24240,7 +24240,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR109" t="n">
         <v>1.37</v>
@@ -24676,7 +24676,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR111" t="n">
         <v>1.99</v>
@@ -24891,7 +24891,7 @@
         <v>1.6</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ112" t="n">
         <v>2.2</v>
@@ -25112,7 +25112,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25330,7 +25330,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR114" t="n">
         <v>1.32</v>
@@ -25545,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.71</v>
@@ -25981,10 +25981,10 @@
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR117" t="n">
         <v>1.9</v>
@@ -26417,7 +26417,7 @@
         <v>0.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.43</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.21</v>
@@ -26853,7 +26853,7 @@
         <v>0.86</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.71</v>
@@ -27074,7 +27074,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR122" t="n">
         <v>1.71</v>
@@ -28161,10 +28161,10 @@
         <v>2</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ127" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR127" t="n">
         <v>1.55</v>
@@ -28597,7 +28597,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.21</v>
@@ -28818,7 +28818,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR130" t="n">
         <v>1.75</v>
@@ -29033,7 +29033,7 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ131" t="n">
         <v>2.2</v>
@@ -29251,10 +29251,10 @@
         <v>0.43</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR132" t="n">
         <v>2.09</v>
@@ -29472,7 +29472,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR133" t="n">
         <v>1.3</v>
@@ -29687,10 +29687,10 @@
         <v>0</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR134" t="n">
         <v>1.52</v>
@@ -29905,7 +29905,7 @@
         <v>0.71</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.43</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.93</v>
@@ -30559,7 +30559,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.07</v>
@@ -30780,7 +30780,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR139" t="n">
         <v>1.16</v>
@@ -30998,7 +30998,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ140" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR140" t="n">
         <v>1.8</v>
@@ -31213,7 +31213,7 @@
         <v>2.13</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ141" t="n">
         <v>2.2</v>
@@ -31431,10 +31431,10 @@
         <v>1.63</v>
       </c>
       <c r="AP142" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR142" t="n">
         <v>1.56</v>
@@ -31867,7 +31867,7 @@
         <v>0.63</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.43</v>
@@ -32088,7 +32088,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR145" t="n">
         <v>1.21</v>
@@ -32303,10 +32303,10 @@
         <v>1.44</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR146" t="n">
         <v>2.04</v>
@@ -32957,7 +32957,7 @@
         <v>0.67</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.71</v>
@@ -33175,7 +33175,7 @@
         <v>1.89</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.64</v>
@@ -33611,7 +33611,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.43</v>
@@ -33832,7 +33832,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR153" t="n">
         <v>1.28</v>
@@ -34047,10 +34047,10 @@
         <v>1.3</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR154" t="n">
         <v>1.23</v>
@@ -34483,7 +34483,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.07</v>
@@ -34704,7 +34704,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR157" t="n">
         <v>2.16</v>
@@ -34919,10 +34919,10 @@
         <v>0</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR158" t="n">
         <v>1.37</v>
@@ -35137,7 +35137,7 @@
         <v>1.22</v>
       </c>
       <c r="AP159" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ159" t="n">
         <v>1</v>
@@ -35573,7 +35573,7 @@
         <v>0.88</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.21</v>
@@ -36009,7 +36009,7 @@
         <v>1.7</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.64</v>
@@ -36230,7 +36230,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ164" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR164" t="n">
         <v>1.39</v>
@@ -36448,7 +36448,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR165" t="n">
         <v>1.63</v>
@@ -36663,7 +36663,7 @@
         <v>0.7</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.71</v>
@@ -36884,7 +36884,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR167" t="n">
         <v>1.15</v>
@@ -37099,7 +37099,7 @@
         <v>0.5</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.43</v>
@@ -37320,7 +37320,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR169" t="n">
         <v>1.61</v>
@@ -37535,7 +37535,7 @@
         <v>1.2</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.07</v>
@@ -37971,7 +37971,7 @@
         <v>0.9</v>
       </c>
       <c r="AP172" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.93</v>
@@ -38189,10 +38189,10 @@
         <v>1.45</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR173" t="n">
         <v>1.53</v>
@@ -38410,7 +38410,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR174" t="n">
         <v>1.25</v>
@@ -38846,7 +38846,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ176" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR176" t="n">
         <v>1.59</v>
@@ -39279,7 +39279,7 @@
         <v>0.91</v>
       </c>
       <c r="AP178" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.71</v>
@@ -39497,10 +39497,10 @@
         <v>1.27</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR179" t="n">
         <v>1.25</v>
@@ -39715,7 +39715,7 @@
         <v>1.27</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.07</v>
@@ -39933,7 +39933,7 @@
         <v>1.18</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.93</v>
@@ -40154,7 +40154,7 @@
         <v>0.36</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR182" t="n">
         <v>1.09</v>
@@ -40587,7 +40587,7 @@
         <v>1.82</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.64</v>
@@ -41244,7 +41244,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR187" t="n">
         <v>2.14</v>
@@ -41459,7 +41459,7 @@
         <v>1.18</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.07</v>
@@ -41680,7 +41680,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR189" t="n">
         <v>2.27</v>
@@ -41895,7 +41895,7 @@
         <v>0.82</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.93</v>
@@ -42116,7 +42116,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR191" t="n">
         <v>1.67</v>
@@ -42549,10 +42549,10 @@
         <v>1.17</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR193" t="n">
         <v>1.48</v>
@@ -42770,7 +42770,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR194" t="n">
         <v>2</v>
@@ -42985,10 +42985,10 @@
         <v>2</v>
       </c>
       <c r="AP195" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ195" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR195" t="n">
         <v>1.51</v>
@@ -43203,10 +43203,10 @@
         <v>0.64</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR196" t="n">
         <v>1.74</v>
@@ -43421,7 +43421,7 @@
         <v>1.08</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.93</v>
@@ -43857,7 +43857,7 @@
         <v>0.91</v>
       </c>
       <c r="AP199" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.21</v>
@@ -44514,7 +44514,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR202" t="n">
         <v>1.71</v>
@@ -45601,7 +45601,7 @@
         <v>0.83</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.71</v>
@@ -46040,7 +46040,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR209" t="n">
         <v>1.69</v>
@@ -46255,7 +46255,7 @@
         <v>2.31</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AQ210" t="n">
         <v>2.2</v>
@@ -46473,10 +46473,10 @@
         <v>1.15</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR211" t="n">
         <v>1.79</v>
@@ -46691,10 +46691,10 @@
         <v>2.08</v>
       </c>
       <c r="AP212" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ212" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AR212" t="n">
         <v>1.55</v>
@@ -46909,10 +46909,10 @@
         <v>0.85</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR213" t="n">
         <v>1.46</v>
@@ -47127,10 +47127,10 @@
         <v>1.77</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR214" t="n">
         <v>1.48</v>
@@ -47345,7 +47345,7 @@
         <v>1.15</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.07</v>
@@ -47566,7 +47566,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR216" t="n">
         <v>1.43</v>
@@ -47781,10 +47781,10 @@
         <v>1.46</v>
       </c>
       <c r="AP217" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ217" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR217" t="n">
         <v>1.49</v>
@@ -49764,16 +49764,16 @@
         <v>7</v>
       </c>
       <c r="AW226" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="AX226" t="n">
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="AY226" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AZ226" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA226" t="n">
         <v>4</v>
@@ -49822,6 +49822,1532 @@
       </c>
       <c r="BP226" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>8306787</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>45983.41666666666</v>
+      </c>
+      <c r="F227" t="n">
+        <v>29</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>1</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>1</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R227" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S227" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U227" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V227" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X227" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>8306793</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>45983.5</v>
+      </c>
+      <c r="F228" t="n">
+        <v>29</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" t="n">
+        <v>1</v>
+      </c>
+      <c r="L228" t="n">
+        <v>3</v>
+      </c>
+      <c r="M228" t="n">
+        <v>3</v>
+      </c>
+      <c r="N228" t="n">
+        <v>6</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>['85', '86', '90']</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>['23', '64', '70']</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R228" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S228" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U228" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V228" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X228" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>8306722</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>45983.58333333334</v>
+      </c>
+      <c r="F229" t="n">
+        <v>29</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>2</v>
+      </c>
+      <c r="J229" t="n">
+        <v>3</v>
+      </c>
+      <c r="K229" t="n">
+        <v>5</v>
+      </c>
+      <c r="L229" t="n">
+        <v>2</v>
+      </c>
+      <c r="M229" t="n">
+        <v>6</v>
+      </c>
+      <c r="N229" t="n">
+        <v>8</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>['17', '45+4']</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>['1', '27', '33', '71', '79', '81']</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R229" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S229" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U229" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V229" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X229" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>8306869</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>45983.58333333334</v>
+      </c>
+      <c r="F230" t="n">
+        <v>29</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>4</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="n">
+        <v>4</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>['54', '65', '75', '90+3']</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R230" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S230" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U230" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X230" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>8306837</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>45984.4375</v>
+      </c>
+      <c r="F231" t="n">
+        <v>29</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
+        <v>3</v>
+      </c>
+      <c r="N231" t="n">
+        <v>3</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>['5', '56', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R231" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S231" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U231" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V231" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X231" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>8306792</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>45984.4375</v>
+      </c>
+      <c r="F232" t="n">
+        <v>29</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>5</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>5</v>
+      </c>
+      <c r="L232" t="n">
+        <v>5</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="n">
+        <v>5</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>['6', '17', '28', '33', '44']</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R232" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S232" t="n">
+        <v>6</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U232" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V232" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X232" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC232" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BE232" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH232" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BI232" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ232" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BO232" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BP232" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>8306789</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>45984.63541666666</v>
+      </c>
+      <c r="F233" t="n">
+        <v>29</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
+        <v>1</v>
+      </c>
+      <c r="N233" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R233" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S233" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T233" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U233" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V233" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W233" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X233" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE233" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI233" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO233" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP233" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -50854,16 +50854,16 @@
         <v>8</v>
       </c>
       <c r="AW231" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY231" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ231" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA231" t="n">
         <v>5</v>
@@ -51072,13 +51072,13 @@
         <v>2</v>
       </c>
       <c r="AW232" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX232" t="n">
         <v>8</v>
       </c>
       <c r="AY232" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ232" t="n">
         <v>10</v>
@@ -51290,13 +51290,13 @@
         <v>8</v>
       </c>
       <c r="AW233" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX233" t="n">
         <v>8</v>
       </c>
       <c r="AY233" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ233" t="n">
         <v>16</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -49761,28 +49761,28 @@
         <v>3</v>
       </c>
       <c r="AV226" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW226" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX226" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY226" t="n">
         <v>8</v>
       </c>
-      <c r="AY226" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ226" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA226" t="n">
         <v>4</v>
       </c>
       <c r="BB226" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC226" t="n">
         <v>10</v>
-      </c>
-      <c r="BC226" t="n">
-        <v>14</v>
       </c>
       <c r="BD226" t="n">
         <v>3.8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -50851,28 +50851,28 @@
         <v>4</v>
       </c>
       <c r="AV231" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW231" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX231" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY231" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ231" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BA231" t="n">
         <v>5</v>
       </c>
       <c r="BB231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD231" t="n">
         <v>2.1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Norway Eliteserien_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR18" t="n">
         <v>1.22</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.07</v>
@@ -4835,10 +4835,10 @@
         <v>3</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR20" t="n">
         <v>1.69</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR29" t="n">
         <v>1.92</v>
@@ -7015,10 +7015,10 @@
         <v>1.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR30" t="n">
         <v>1.62</v>
@@ -7233,10 +7233,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR31" t="n">
         <v>1.74</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR32" t="n">
         <v>1.72</v>
@@ -7669,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR33" t="n">
         <v>1.67</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
         <v>2.73</v>
@@ -8105,10 +8105,10 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR35" t="n">
         <v>1.33</v>
@@ -8323,10 +8323,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR36" t="n">
         <v>1.91</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.27</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.07</v>
@@ -8980,7 +8980,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -9631,7 +9631,7 @@
         <v>3</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.47</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR45" t="n">
         <v>2.05</v>
@@ -10503,7 +10503,7 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ46" t="n">
         <v>1</v>
@@ -10724,7 +10724,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR47" t="n">
         <v>1.08</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR48" t="n">
         <v>1.78</v>
@@ -11157,10 +11157,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR49" t="n">
         <v>1.53</v>
@@ -11378,7 +11378,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR50" t="n">
         <v>1.34</v>
@@ -11593,10 +11593,10 @@
         <v>1.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR51" t="n">
         <v>1.69</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ52" t="n">
         <v>2.2</v>
@@ -12468,7 +12468,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR55" t="n">
         <v>1.66</v>
@@ -12686,7 +12686,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR56" t="n">
         <v>1.17</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.93</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.27</v>
@@ -13337,7 +13337,7 @@
         <v>2.33</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.47</v>
@@ -13558,7 +13558,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR60" t="n">
         <v>1.96</v>
@@ -13776,7 +13776,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR61" t="n">
         <v>1.23</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ62" t="n">
         <v>1</v>
@@ -14212,7 +14212,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR63" t="n">
         <v>1.12</v>
@@ -14427,7 +14427,7 @@
         <v>2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ64" t="n">
         <v>2.2</v>
@@ -14645,10 +14645,10 @@
         <v>1.33</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR65" t="n">
         <v>1.86</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR66" t="n">
         <v>1.54</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.53</v>
@@ -15302,7 +15302,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR68" t="n">
         <v>0.97</v>
@@ -15735,7 +15735,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.2</v>
@@ -15953,10 +15953,10 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR71" t="n">
         <v>1.86</v>
@@ -16174,7 +16174,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR72" t="n">
         <v>1.75</v>
@@ -16392,7 +16392,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR73" t="n">
         <v>1.61</v>
@@ -17043,7 +17043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.07</v>
@@ -17261,7 +17261,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ77" t="n">
         <v>2.2</v>
@@ -17479,10 +17479,10 @@
         <v>0.25</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
         <v>2.11</v>
@@ -17915,7 +17915,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.53</v>
@@ -18136,7 +18136,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR81" t="n">
         <v>2.04</v>
@@ -18354,7 +18354,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR82" t="n">
         <v>1.05</v>
@@ -18569,7 +18569,7 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ83" t="n">
         <v>1</v>
@@ -18787,7 +18787,7 @@
         <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.27</v>
@@ -19005,10 +19005,10 @@
         <v>0.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR85" t="n">
         <v>1.77</v>
@@ -19226,7 +19226,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR86" t="n">
         <v>1.23</v>
@@ -19441,10 +19441,10 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR87" t="n">
         <v>2.39</v>
@@ -19659,7 +19659,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.2</v>
@@ -19877,7 +19877,7 @@
         <v>1.43</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.07</v>
@@ -20098,7 +20098,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR90" t="n">
         <v>1.47</v>
@@ -20313,7 +20313,7 @@
         <v>1.8</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.47</v>
@@ -20534,7 +20534,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR92" t="n">
         <v>1.2</v>
@@ -20752,7 +20752,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR93" t="n">
         <v>1.58</v>
@@ -20970,7 +20970,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR94" t="n">
         <v>1.81</v>
@@ -21185,7 +21185,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.93</v>
@@ -21621,10 +21621,10 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR97" t="n">
         <v>2.24</v>
@@ -21842,7 +21842,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR98" t="n">
         <v>1.94</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ99" t="n">
         <v>2.2</v>
@@ -22278,7 +22278,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR100" t="n">
         <v>1.6</v>
@@ -22493,7 +22493,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ101" t="n">
         <v>1</v>
@@ -22714,7 +22714,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR102" t="n">
         <v>1.22</v>
@@ -22929,7 +22929,7 @@
         <v>0</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.27</v>
@@ -23147,7 +23147,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.93</v>
@@ -23368,7 +23368,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR105" t="n">
         <v>1.24</v>
@@ -23586,7 +23586,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR106" t="n">
         <v>1.52</v>
@@ -23801,10 +23801,10 @@
         <v>0.83</v>
       </c>
       <c r="AP107" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR107" t="n">
         <v>1.13</v>
@@ -24022,7 +24022,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR108" t="n">
         <v>1.59</v>
@@ -24237,7 +24237,7 @@
         <v>2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.47</v>
@@ -24455,10 +24455,10 @@
         <v>0.83</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR110" t="n">
         <v>1.79</v>
@@ -24673,7 +24673,7 @@
         <v>2.29</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ111" t="n">
         <v>2.2</v>
@@ -25109,7 +25109,7 @@
         <v>1.43</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ113" t="n">
         <v>1</v>
@@ -25548,7 +25548,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR115" t="n">
         <v>1.53</v>
@@ -25763,7 +25763,7 @@
         <v>1.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ116" t="n">
         <v>2.2</v>
@@ -26199,7 +26199,7 @@
         <v>1.38</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.07</v>
@@ -26420,7 +26420,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR119" t="n">
         <v>1.56</v>
@@ -26638,7 +26638,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR120" t="n">
         <v>1.24</v>
@@ -26856,7 +26856,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR121" t="n">
         <v>1.28</v>
@@ -27071,7 +27071,7 @@
         <v>1.86</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.47</v>
@@ -27289,10 +27289,10 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR123" t="n">
         <v>1.28</v>
@@ -27507,10 +27507,10 @@
         <v>0.71</v>
       </c>
       <c r="AP124" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR124" t="n">
         <v>1.14</v>
@@ -27725,10 +27725,10 @@
         <v>1.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR125" t="n">
         <v>2.33</v>
@@ -27943,10 +27943,10 @@
         <v>2.29</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR126" t="n">
         <v>1.74</v>
@@ -28379,10 +28379,10 @@
         <v>0.75</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR128" t="n">
         <v>2.42</v>
@@ -28600,7 +28600,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR129" t="n">
         <v>1.56</v>
@@ -28815,7 +28815,7 @@
         <v>1.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.53</v>
@@ -29908,7 +29908,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR135" t="n">
         <v>1.54</v>
@@ -30126,7 +30126,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR136" t="n">
         <v>1.59</v>
@@ -30341,10 +30341,10 @@
         <v>2</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR137" t="n">
         <v>2.4</v>
@@ -30562,7 +30562,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
         <v>1.54</v>
@@ -30777,7 +30777,7 @@
         <v>1.63</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.47</v>
@@ -30995,7 +30995,7 @@
         <v>2.11</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ140" t="n">
         <v>2.2</v>
@@ -31652,7 +31652,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR143" t="n">
         <v>1.32</v>
@@ -31870,7 +31870,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR144" t="n">
         <v>1.2</v>
@@ -32085,7 +32085,7 @@
         <v>0.38</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.93</v>
@@ -32524,7 +32524,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR147" t="n">
         <v>1.38</v>
@@ -32739,10 +32739,10 @@
         <v>1.11</v>
       </c>
       <c r="AP148" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR148" t="n">
         <v>1.14</v>
@@ -32960,7 +32960,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR149" t="n">
         <v>1.46</v>
@@ -33178,7 +33178,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR150" t="n">
         <v>1.67</v>
@@ -33393,7 +33393,7 @@
         <v>1.22</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.07</v>
@@ -33614,7 +33614,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR152" t="n">
         <v>2.06</v>
@@ -33829,7 +33829,7 @@
         <v>1.78</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.53</v>
@@ -34265,7 +34265,7 @@
         <v>2.22</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ155" t="n">
         <v>2.2</v>
@@ -34486,7 +34486,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR156" t="n">
         <v>1.54</v>
@@ -34701,7 +34701,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
@@ -35140,7 +35140,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR159" t="n">
         <v>1.49</v>
@@ -35355,7 +35355,7 @@
         <v>1.4</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.07</v>
@@ -35576,7 +35576,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR161" t="n">
         <v>1.58</v>
@@ -35791,10 +35791,10 @@
         <v>1.3</v>
       </c>
       <c r="AP162" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR162" t="n">
         <v>1.95</v>
@@ -36012,7 +36012,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR163" t="n">
         <v>1.56</v>
@@ -36445,7 +36445,7 @@
         <v>0.44</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.93</v>
@@ -36666,7 +36666,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR166" t="n">
         <v>1.24</v>
@@ -36881,7 +36881,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ167" t="n">
         <v>1</v>
@@ -37102,7 +37102,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR168" t="n">
         <v>1.42</v>
@@ -37317,7 +37317,7 @@
         <v>1.7</v>
       </c>
       <c r="AP169" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.53</v>
@@ -37538,7 +37538,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR170" t="n">
         <v>2.03</v>
@@ -37753,7 +37753,7 @@
         <v>2.3</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ171" t="n">
         <v>2.2</v>
@@ -37974,7 +37974,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR172" t="n">
         <v>1.48</v>
@@ -38407,7 +38407,7 @@
         <v>0.1</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.27</v>
@@ -38625,10 +38625,10 @@
         <v>1.1</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR175" t="n">
         <v>2.08</v>
@@ -38843,7 +38843,7 @@
         <v>2.09</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ176" t="n">
         <v>2.2</v>
@@ -39061,10 +39061,10 @@
         <v>1.11</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR177" t="n">
         <v>1.99</v>
@@ -39282,7 +39282,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR178" t="n">
         <v>1.48</v>
@@ -39936,7 +39936,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR181" t="n">
         <v>1.7</v>
@@ -40151,7 +40151,7 @@
         <v>0.4</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.93</v>
@@ -40372,7 +40372,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR183" t="n">
         <v>1.37</v>
@@ -40590,7 +40590,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR184" t="n">
         <v>1.92</v>
@@ -40805,10 +40805,10 @@
         <v>0.55</v>
       </c>
       <c r="AP185" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR185" t="n">
         <v>1.59</v>
@@ -41023,10 +41023,10 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR186" t="n">
         <v>1.34</v>
@@ -41241,7 +41241,7 @@
         <v>1.82</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.53</v>
@@ -41462,7 +41462,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR188" t="n">
         <v>1.51</v>
@@ -41677,7 +41677,7 @@
         <v>0.09</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.27</v>
@@ -41898,7 +41898,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR190" t="n">
         <v>1.41</v>
@@ -42113,7 +42113,7 @@
         <v>1.33</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.47</v>
@@ -42331,7 +42331,7 @@
         <v>2.18</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ192" t="n">
         <v>2.2</v>
@@ -42767,7 +42767,7 @@
         <v>0.08</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.27</v>
@@ -43424,7 +43424,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR197" t="n">
         <v>1.44</v>
@@ -43860,7 +43860,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR199" t="n">
         <v>1.5</v>
@@ -44075,10 +44075,10 @@
         <v>0.5</v>
       </c>
       <c r="AP200" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR200" t="n">
         <v>2.09</v>
@@ -44293,10 +44293,10 @@
         <v>1.17</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR201" t="n">
         <v>1.59</v>
@@ -44511,7 +44511,7 @@
         <v>1.67</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.53</v>
@@ -44729,10 +44729,10 @@
         <v>1.08</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR203" t="n">
         <v>1.56</v>
@@ -44947,10 +44947,10 @@
         <v>0.83</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR204" t="n">
         <v>1.35</v>
@@ -45165,10 +45165,10 @@
         <v>1.67</v>
       </c>
       <c r="AP205" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR205" t="n">
         <v>1.1</v>
@@ -45383,10 +45383,10 @@
         <v>0.92</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR206" t="n">
         <v>2.44</v>
@@ -45604,7 +45604,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR207" t="n">
         <v>1.86</v>
@@ -45819,7 +45819,7 @@
         <v>2.25</v>
       </c>
       <c r="AP208" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ208" t="n">
         <v>2.2</v>
@@ -46037,7 +46037,7 @@
         <v>0.83</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ209" t="n">
         <v>0.93</v>
@@ -47999,10 +47999,10 @@
         <v>1.08</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AR218" t="n">
         <v>1.55</v>
@@ -48217,10 +48217,10 @@
         <v>1</v>
       </c>
       <c r="AP219" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR219" t="n">
         <v>2.06</v>
@@ -48435,10 +48435,10 @@
         <v>1</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ220" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR220" t="n">
         <v>1.62</v>
@@ -48653,10 +48653,10 @@
         <v>0.46</v>
       </c>
       <c r="AP221" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AQ221" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR221" t="n">
         <v>2.41</v>
@@ -48871,10 +48871,10 @@
         <v>0.77</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ222" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR222" t="n">
         <v>1.38</v>
@@ -49089,10 +49089,10 @@
         <v>1.08</v>
       </c>
       <c r="AP223" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR223" t="n">
         <v>1.98</v>
@@ -49307,10 +49307,10 @@
         <v>1.77</v>
       </c>
       <c r="AP224" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR224" t="n">
         <v>1.55</v>
@@ -49525,10 +49525,10 @@
         <v>0.85</v>
       </c>
       <c r="AP225" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR225" t="n">
         <v>1.08</v>
@@ -51348,6 +51348,1750 @@
       </c>
       <c r="BP233" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>8306705</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F234" t="n">
+        <v>30</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>3</v>
+      </c>
+      <c r="L234" t="n">
+        <v>5</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>5</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>['37', '42', '45+2', '61', '73']</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R234" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U234" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V234" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W234" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X234" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY234" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB234" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC234" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE234" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH234" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI234" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ234" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BK234" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN234" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BO234" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BP234" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>8306795</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F235" t="n">
+        <v>30</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Strømsgodset</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>2</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>2</v>
+      </c>
+      <c r="L235" t="n">
+        <v>6</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="n">
+        <v>6</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>['33', '37', '55', '59', '67', '90+5']</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R235" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S235" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U235" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="V235" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W235" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X235" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC235" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE235" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI235" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL235" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM235" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN235" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BO235" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BP235" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>8306700</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F236" t="n">
+        <v>30</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>KFUM</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>2</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>2</v>
+      </c>
+      <c r="L236" t="n">
+        <v>2</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>['37', '45+3']</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R236" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S236" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T236" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U236" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V236" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W236" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X236" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI236" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ236" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK236" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL236" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM236" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN236" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO236" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BP236" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>8306786</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F237" t="n">
+        <v>30</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Tromsø</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>3</v>
+      </c>
+      <c r="K237" t="n">
+        <v>3</v>
+      </c>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="n">
+        <v>3</v>
+      </c>
+      <c r="N237" t="n">
+        <v>4</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>['8', '14', '45+4']</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>6</v>
+      </c>
+      <c r="R237" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S237" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T237" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U237" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V237" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W237" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X237" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT237" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV237" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX237" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA237" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB237" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC237" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE237" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF237" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH237" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI237" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ237" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK237" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM237" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN237" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO237" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP237" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>8306794</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F238" t="n">
+        <v>30</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>HamKam</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>2</v>
+      </c>
+      <c r="J238" t="n">
+        <v>1</v>
+      </c>
+      <c r="K238" t="n">
+        <v>3</v>
+      </c>
+      <c r="L238" t="n">
+        <v>3</v>
+      </c>
+      <c r="M238" t="n">
+        <v>1</v>
+      </c>
+      <c r="N238" t="n">
+        <v>4</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>['33', '45+4', '60']</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R238" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S238" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T238" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U238" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V238" t="n">
+        <v>2</v>
+      </c>
+      <c r="W238" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X238" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA238" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB238" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC238" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE238" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF238" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG238" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH238" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BI238" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ238" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BK238" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL238" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM238" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BN238" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BO238" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BP238" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>8306790</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F239" t="n">
+        <v>30</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>1</v>
+      </c>
+      <c r="J239" t="n">
+        <v>2</v>
+      </c>
+      <c r="K239" t="n">
+        <v>3</v>
+      </c>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="n">
+        <v>4</v>
+      </c>
+      <c r="N239" t="n">
+        <v>5</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>['3', '6', '73', '80']</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R239" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S239" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T239" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U239" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V239" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W239" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X239" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA239" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB239" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ239" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BK239" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM239" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN239" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO239" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP239" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>8306699</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F240" t="n">
+        <v>30</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Vålerenga</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>3</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>3</v>
+      </c>
+      <c r="L240" t="n">
+        <v>5</v>
+      </c>
+      <c r="M240" t="n">
+        <v>1</v>
+      </c>
+      <c r="N240" t="n">
+        <v>6</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>['10', '15', '45+4', '54', '72']</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R240" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="S240" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T240" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="U240" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V240" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W240" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X240" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY240" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA240" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB240" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BO240" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BP240" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>8306701</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="F241" t="n">
+        <v>30</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>1</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R241" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S241" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T241" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U241" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V241" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W241" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X241" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM241" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ241" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR241" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS241" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT241" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU241" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW241" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX241" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ241" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA241" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB241" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC241" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD241" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE241" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF241" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BG241" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH241" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI241" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ241" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK241" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL241" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BM241" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN241" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BO241" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BP241" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
